--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +472,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n">
+        <v>306250</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -486,35 +502,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="43" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="48" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="45" customWidth="1" min="25" max="25"/>
-    <col width="29" customWidth="1" min="26" max="26"/>
+    <col width="55" customWidth="1" min="25" max="25"/>
+    <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -526,132 +542,132 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Units)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Rev USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -737,6 +753,91 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>231000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -832,15 +933,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2427</v>
+      </c>
+      <c r="F2" t="n">
         <v>2429</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>-2</v>
+      </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="3">
@@ -863,15 +968,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>941</v>
+      </c>
+      <c r="F3" t="n">
         <v>942</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4">
@@ -892,8 +1001,12 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -919,8 +1032,12 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -948,15 +1065,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>438</v>
+      </c>
+      <c r="F6" t="n">
         <v>439</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
@@ -979,15 +1100,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>262</v>
+      </c>
+      <c r="F7" t="n">
         <v>265</v>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>-3</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -1012,8 +1137,12 @@
       <c r="E8" t="n">
         <v>826</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>826</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1043,8 +1172,12 @@
       <c r="E9" t="n">
         <v>968</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>968</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1074,8 +1207,12 @@
       <c r="E10" t="n">
         <v>962</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>962</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1105,8 +1242,12 @@
       <c r="E11" t="n">
         <v>367</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>367</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -1136,8 +1277,12 @@
       <c r="E12" t="n">
         <v>481</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1167,8 +1312,12 @@
       <c r="E13" t="n">
         <v>485</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>485</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -1198,8 +1347,12 @@
       <c r="E14" t="n">
         <v>388</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>388</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
@@ -1229,8 +1382,12 @@
       <c r="E15" t="n">
         <v>481</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>481</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -1260,8 +1417,12 @@
       <c r="E16" t="n">
         <v>483</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>483</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -1291,8 +1452,12 @@
       <c r="E17" t="n">
         <v>374</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>374</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -1322,8 +1487,12 @@
       <c r="E18" t="n">
         <v>497</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>497</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -1353,8 +1522,12 @@
       <c r="E19" t="n">
         <v>478</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>478</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -1384,8 +1557,12 @@
       <c r="E20" t="n">
         <v>702</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>702</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -1415,8 +1592,12 @@
       <c r="E21" t="n">
         <v>944</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>944</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -1446,8 +1627,12 @@
       <c r="E22" t="n">
         <v>956</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>956</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
@@ -1477,8 +1662,12 @@
       <c r="E23" t="n">
         <v>-1</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -1506,15 +1695,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>319</v>
+      </c>
+      <c r="F24" t="n">
         <v>320</v>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>-1</v>
+      </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -1537,15 +1730,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>198</v>
+      </c>
+      <c r="F25" t="n">
         <v>199</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>-1</v>
+      </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -1568,15 +1765,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>319</v>
+      </c>
+      <c r="F26" t="n">
         <v>320</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>-1</v>
+      </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -1601,8 +1802,12 @@
       <c r="E27" t="n">
         <v>878</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>878</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -1630,15 +1835,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>332</v>
+      </c>
+      <c r="F28" t="n">
         <v>333</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>-1</v>
+      </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="29">
@@ -1661,15 +1870,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>442</v>
+      </c>
+      <c r="F29" t="n">
         <v>444</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>-2</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="30">
@@ -1692,15 +1905,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>601</v>
+      </c>
+      <c r="F30" t="n">
         <v>603</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-2</v>
+      </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="31">
@@ -1723,15 +1940,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>601</v>
+      </c>
+      <c r="F31" t="n">
         <v>603</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>-2</v>
+      </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="32">
@@ -1756,8 +1977,12 @@
       <c r="E32" t="n">
         <v>878</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>878</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -1785,15 +2010,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>332</v>
+      </c>
+      <c r="F33" t="n">
         <v>333</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>-1</v>
+      </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="34">
@@ -1816,15 +2045,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>442</v>
+      </c>
+      <c r="F34" t="n">
         <v>444</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>-2</v>
+      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="35">
@@ -1847,15 +2080,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>601</v>
+      </c>
+      <c r="F35" t="n">
         <v>603</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-2</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="36">
@@ -1878,15 +2115,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>601</v>
+      </c>
+      <c r="F36" t="n">
         <v>603</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-2</v>
+      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
   </sheetData>
@@ -1900,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3178,6 +3419,1293 @@
         <v>0</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2427</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F38" t="n">
+        <v>941</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F41" t="n">
+        <v>438</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F42" t="n">
+        <v>262</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>826</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>968</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" t="n">
+        <v>962</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F46" t="n">
+        <v>367</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>481</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>485</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F49" t="n">
+        <v>388</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>481</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F51" t="n">
+        <v>483</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>900</v>
+      </c>
+      <c r="F52" t="n">
+        <v>374</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>900</v>
+      </c>
+      <c r="F53" t="n">
+        <v>497</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>900</v>
+      </c>
+      <c r="F54" t="n">
+        <v>478</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>900</v>
+      </c>
+      <c r="F55" t="n">
+        <v>702</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>900</v>
+      </c>
+      <c r="F56" t="n">
+        <v>944</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>900</v>
+      </c>
+      <c r="F57" t="n">
+        <v>956</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>319</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>198</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>319</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F62" t="n">
+        <v>878</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F63" t="n">
+        <v>332</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F64" t="n">
+        <v>442</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
+      <c r="I64" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F65" t="n">
+        <v>601</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F66" t="n">
+        <v>601</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F67" t="n">
+        <v>878</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F68" t="n">
+        <v>332</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F69" t="n">
+        <v>442</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F70" t="n">
+        <v>601</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F71" t="n">
+        <v>601</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>33000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,22 @@
         <v>306250</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>337200</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -502,17 +518,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -520,12 +536,12 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
@@ -547,64 +563,64 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -612,62 +628,62 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -766,31 +782,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -805,39 +821,124 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>19000</v>
-      </c>
       <c r="R3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="X3" t="n">
         <v>6750</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>198000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W4" t="n">
         <v>2500</v>
       </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,16 +1037,16 @@
         <v>2427</v>
       </c>
       <c r="F2" t="n">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="G2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -968,19 +1069,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>938</v>
+      </c>
+      <c r="F3" t="n">
         <v>941</v>
       </c>
-      <c r="F3" t="n">
-        <v>942</v>
-      </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>15000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="4">
@@ -1065,10 +1166,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>437</v>
+      </c>
+      <c r="F6" t="n">
         <v>438</v>
-      </c>
-      <c r="F6" t="n">
-        <v>439</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
@@ -1103,16 +1204,16 @@
         <v>262</v>
       </c>
       <c r="F7" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1135,19 +1236,19 @@
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F8" t="n">
         <v>826</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -1170,19 +1271,19 @@
         <v>1000</v>
       </c>
       <c r="E9" t="n">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F9" t="n">
         <v>968</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1205,19 +1306,19 @@
         <v>1000</v>
       </c>
       <c r="E10" t="n">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F10" t="n">
         <v>962</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -1240,19 +1341,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F11" t="n">
         <v>367</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -1275,19 +1376,19 @@
         <v>1000</v>
       </c>
       <c r="E12" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F12" t="n">
         <v>481</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -1310,19 +1411,19 @@
         <v>1000</v>
       </c>
       <c r="E13" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F13" t="n">
         <v>485</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -1450,19 +1551,19 @@
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F17" t="n">
         <v>374</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18">
@@ -1485,19 +1586,19 @@
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F18" t="n">
         <v>497</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19">
@@ -1520,19 +1621,19 @@
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F19" t="n">
         <v>478</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20">
@@ -1695,19 +1796,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>315</v>
+      </c>
+      <c r="F24" t="n">
         <v>319</v>
       </c>
-      <c r="F24" t="n">
-        <v>320</v>
-      </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="25">
@@ -1730,19 +1831,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>195</v>
+      </c>
+      <c r="F25" t="n">
         <v>198</v>
       </c>
-      <c r="F25" t="n">
-        <v>199</v>
-      </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -1765,19 +1866,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>315</v>
+      </c>
+      <c r="F26" t="n">
         <v>319</v>
       </c>
-      <c r="F26" t="n">
-        <v>320</v>
-      </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>19000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="27">
@@ -1838,16 +1939,16 @@
         <v>332</v>
       </c>
       <c r="F28" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1873,16 +1974,16 @@
         <v>442</v>
       </c>
       <c r="F29" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G29" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1905,19 +2006,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>598</v>
+      </c>
+      <c r="F30" t="n">
         <v>601</v>
       </c>
-      <c r="F30" t="n">
-        <v>603</v>
-      </c>
       <c r="G30" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="31">
@@ -1940,19 +2041,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>598</v>
+      </c>
+      <c r="F31" t="n">
         <v>601</v>
       </c>
-      <c r="F31" t="n">
-        <v>603</v>
-      </c>
       <c r="G31" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="32">
@@ -2013,16 +2114,16 @@
         <v>332</v>
       </c>
       <c r="F33" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2048,16 +2149,16 @@
         <v>442</v>
       </c>
       <c r="F34" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G34" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2080,19 +2181,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>598</v>
+      </c>
+      <c r="F35" t="n">
         <v>601</v>
       </c>
-      <c r="F35" t="n">
-        <v>603</v>
-      </c>
       <c r="G35" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="36">
@@ -2115,19 +2216,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>598</v>
+      </c>
+      <c r="F36" t="n">
         <v>601</v>
       </c>
-      <c r="F36" t="n">
-        <v>603</v>
-      </c>
       <c r="G36" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
   </sheetData>
@@ -2141,7 +2242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4706,6 +4807,1293 @@
         <v>33000</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2427</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F73" t="n">
+        <v>938</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F76" t="n">
+        <v>437</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F77" t="n">
+        <v>262</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F78" t="n">
+        <v>825</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F79" t="n">
+        <v>967</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F80" t="n">
+        <v>961</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F81" t="n">
+        <v>366</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F82" t="n">
+        <v>480</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F83" t="n">
+        <v>484</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F84" t="n">
+        <v>388</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F85" t="n">
+        <v>481</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F86" t="n">
+        <v>483</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>900</v>
+      </c>
+      <c r="F87" t="n">
+        <v>373</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>900</v>
+      </c>
+      <c r="F88" t="n">
+        <v>496</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>900</v>
+      </c>
+      <c r="F89" t="n">
+        <v>477</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>900</v>
+      </c>
+      <c r="F90" t="n">
+        <v>702</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>900</v>
+      </c>
+      <c r="F91" t="n">
+        <v>944</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>900</v>
+      </c>
+      <c r="F92" t="n">
+        <v>956</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F94" t="n">
+        <v>315</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4</v>
+      </c>
+      <c r="I94" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>195</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F96" t="n">
+        <v>315</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F97" t="n">
+        <v>878</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F98" t="n">
+        <v>332</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F99" t="n">
+        <v>442</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F100" t="n">
+        <v>598</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F101" t="n">
+        <v>598</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F102" t="n">
+        <v>878</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F103" t="n">
+        <v>332</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F104" t="n">
+        <v>442</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F105" t="n">
+        <v>598</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F106" t="n">
+        <v>598</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>49500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -504,6 +504,22 @@
         <v>337200</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C5" t="n">
+        <v>644750</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -518,36 +534,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="55" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="55" customWidth="1" min="27" max="27"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -563,64 +579,64 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -628,62 +644,62 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -782,70 +798,70 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>45000</v>
-      </c>
       <c r="R3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="T3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W3" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -854,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -867,16 +883,16 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -885,14 +901,14 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
@@ -900,22 +916,22 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>76000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>45000</v>
-      </c>
       <c r="R4" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="S4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
@@ -924,21 +940,106 @@
         <v>3000</v>
       </c>
       <c r="V4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>2700</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R5" t="n">
         <v>2500</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="S5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,19 +1135,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
-        <v>2427</v>
+        <v>2423</v>
       </c>
       <c r="F2" t="n">
         <v>2427</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1170,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>936</v>
+      </c>
+      <c r="F3" t="n">
         <v>938</v>
       </c>
-      <c r="F3" t="n">
-        <v>941</v>
-      </c>
       <c r="G3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -1166,10 +1267,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>436</v>
+      </c>
+      <c r="F6" t="n">
         <v>437</v>
-      </c>
-      <c r="F6" t="n">
-        <v>438</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
@@ -1201,19 +1302,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F7" t="n">
         <v>262</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -1239,16 +1340,16 @@
         <v>825</v>
       </c>
       <c r="F8" t="n">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1274,16 +1375,16 @@
         <v>967</v>
       </c>
       <c r="F9" t="n">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1306,10 +1407,10 @@
         <v>1000</v>
       </c>
       <c r="E10" t="n">
+        <v>960</v>
+      </c>
+      <c r="F10" t="n">
         <v>961</v>
-      </c>
-      <c r="F10" t="n">
-        <v>962</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
@@ -1341,10 +1442,10 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
+        <v>365</v>
+      </c>
+      <c r="F11" t="n">
         <v>366</v>
-      </c>
-      <c r="F11" t="n">
-        <v>367</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
@@ -1379,16 +1480,16 @@
         <v>480</v>
       </c>
       <c r="F12" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1414,16 +1515,16 @@
         <v>484</v>
       </c>
       <c r="F13" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1554,16 +1655,16 @@
         <v>373</v>
       </c>
       <c r="F17" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1589,16 +1690,16 @@
         <v>496</v>
       </c>
       <c r="F18" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1624,16 +1725,16 @@
         <v>477</v>
       </c>
       <c r="F19" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1796,19 +1897,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>314</v>
+      </c>
+      <c r="F24" t="n">
         <v>315</v>
       </c>
-      <c r="F24" t="n">
-        <v>319</v>
-      </c>
       <c r="G24" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -1834,16 +1935,16 @@
         <v>195</v>
       </c>
       <c r="F25" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1866,19 +1967,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>314</v>
+      </c>
+      <c r="F26" t="n">
         <v>315</v>
       </c>
-      <c r="F26" t="n">
-        <v>319</v>
-      </c>
       <c r="G26" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>76000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -1901,19 +2002,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F27" t="n">
         <v>878</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="28">
@@ -1971,19 +2072,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F29" t="n">
         <v>442</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="30">
@@ -2006,19 +2107,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>592</v>
+      </c>
+      <c r="F30" t="n">
         <v>598</v>
       </c>
-      <c r="F30" t="n">
-        <v>601</v>
-      </c>
       <c r="G30" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="31">
@@ -2041,19 +2142,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>592</v>
+      </c>
+      <c r="F31" t="n">
         <v>598</v>
       </c>
-      <c r="F31" t="n">
-        <v>601</v>
-      </c>
       <c r="G31" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="32">
@@ -2076,19 +2177,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F32" t="n">
         <v>878</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="33">
@@ -2146,19 +2247,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F34" t="n">
         <v>442</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="35">
@@ -2181,19 +2282,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>592</v>
+      </c>
+      <c r="F35" t="n">
         <v>598</v>
       </c>
-      <c r="F35" t="n">
-        <v>601</v>
-      </c>
       <c r="G35" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="36">
@@ -2216,19 +2317,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>592</v>
+      </c>
+      <c r="F36" t="n">
         <v>598</v>
       </c>
-      <c r="F36" t="n">
-        <v>601</v>
-      </c>
       <c r="G36" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
   </sheetData>
@@ -2242,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6094,6 +6195,1293 @@
         <v>49500</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2423</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>936</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F111" t="n">
+        <v>436</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F112" t="n">
+        <v>261</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F113" t="n">
+        <v>825</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F114" t="n">
+        <v>967</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F115" t="n">
+        <v>960</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F116" t="n">
+        <v>365</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F117" t="n">
+        <v>480</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F118" t="n">
+        <v>484</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F119" t="n">
+        <v>388</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F120" t="n">
+        <v>481</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F121" t="n">
+        <v>483</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>900</v>
+      </c>
+      <c r="F122" t="n">
+        <v>373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>900</v>
+      </c>
+      <c r="F123" t="n">
+        <v>496</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>900</v>
+      </c>
+      <c r="F124" t="n">
+        <v>477</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>900</v>
+      </c>
+      <c r="F125" t="n">
+        <v>702</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>900</v>
+      </c>
+      <c r="F126" t="n">
+        <v>944</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>900</v>
+      </c>
+      <c r="F127" t="n">
+        <v>956</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F129" t="n">
+        <v>314</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F130" t="n">
+        <v>195</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F131" t="n">
+        <v>314</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F132" t="n">
+        <v>877</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F133" t="n">
+        <v>332</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F134" t="n">
+        <v>439</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F135" t="n">
+        <v>592</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H135" t="n">
+        <v>6</v>
+      </c>
+      <c r="I135" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F136" t="n">
+        <v>592</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H136" t="n">
+        <v>6</v>
+      </c>
+      <c r="I136" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F137" t="n">
+        <v>877</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F138" t="n">
+        <v>332</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F139" t="n">
+        <v>439</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F140" t="n">
+        <v>592</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H140" t="n">
+        <v>6</v>
+      </c>
+      <c r="I140" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F141" t="n">
+        <v>592</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H141" t="n">
+        <v>6</v>
+      </c>
+      <c r="I141" t="n">
+        <v>99000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,22 @@
         <v>644750</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C6" t="n">
+        <v>563100</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -534,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -543,27 +559,27 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="55" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="48" customWidth="1" min="27" max="27"/>
+    <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,54 +605,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -654,52 +670,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -804,23 +820,23 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
@@ -831,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
@@ -843,22 +859,22 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S3" t="n">
         <v>2500</v>
       </c>
-      <c r="S3" t="n">
-        <v>6750</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -870,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -889,22 +905,22 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -913,10 +929,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -928,22 +944,22 @@
         <v>76000</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>2500</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>3000</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>4000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>2700</v>
@@ -952,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -980,16 +996,16 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -998,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1013,22 +1029,22 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S5" t="n">
         <v>2500</v>
       </c>
-      <c r="S5" t="n">
-        <v>2250</v>
-      </c>
       <c r="T5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>1000</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1037,9 +1053,94 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>396000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>900</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1135,19 +1236,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2418</v>
+      </c>
+      <c r="F2" t="n">
         <v>2423</v>
       </c>
-      <c r="F2" t="n">
-        <v>2427</v>
-      </c>
       <c r="G2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="3">
@@ -1170,19 +1271,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>933</v>
+      </c>
+      <c r="F3" t="n">
         <v>936</v>
       </c>
-      <c r="F3" t="n">
-        <v>938</v>
-      </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="4">
@@ -1267,19 +1368,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>434</v>
+      </c>
+      <c r="F6" t="n">
         <v>436</v>
       </c>
-      <c r="F6" t="n">
-        <v>437</v>
-      </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7">
@@ -1302,19 +1403,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>255</v>
+      </c>
+      <c r="F7" t="n">
         <v>261</v>
       </c>
-      <c r="F7" t="n">
-        <v>262</v>
-      </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>2250</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="8">
@@ -1337,19 +1438,19 @@
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F8" t="n">
         <v>825</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -1372,19 +1473,19 @@
         <v>1000</v>
       </c>
       <c r="E9" t="n">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F9" t="n">
         <v>967</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1410,16 +1511,16 @@
         <v>960</v>
       </c>
       <c r="F10" t="n">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1445,16 +1546,16 @@
         <v>365</v>
       </c>
       <c r="F11" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1652,19 +1753,19 @@
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F17" t="n">
         <v>373</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18">
@@ -1757,19 +1858,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F20" t="n">
         <v>702</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -1792,19 +1893,19 @@
         <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F21" t="n">
         <v>944</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22">
@@ -1827,19 +1928,19 @@
         <v>900</v>
       </c>
       <c r="E22" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F22" t="n">
         <v>956</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23">
@@ -1897,10 +1998,10 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>313</v>
+      </c>
+      <c r="F24" t="n">
         <v>314</v>
-      </c>
-      <c r="F24" t="n">
-        <v>315</v>
       </c>
       <c r="G24" t="n">
         <v>-1</v>
@@ -1932,19 +2033,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F25" t="n">
         <v>195</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -1967,10 +2068,10 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>313</v>
+      </c>
+      <c r="F26" t="n">
         <v>314</v>
-      </c>
-      <c r="F26" t="n">
-        <v>315</v>
       </c>
       <c r="G26" t="n">
         <v>-1</v>
@@ -2002,10 +2103,10 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>876</v>
+      </c>
+      <c r="F27" t="n">
         <v>877</v>
-      </c>
-      <c r="F27" t="n">
-        <v>878</v>
       </c>
       <c r="G27" t="n">
         <v>-1</v>
@@ -2072,19 +2173,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>435</v>
+      </c>
+      <c r="F29" t="n">
         <v>439</v>
       </c>
-      <c r="F29" t="n">
-        <v>442</v>
-      </c>
       <c r="G29" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>49500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="30">
@@ -2107,19 +2208,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>588</v>
+      </c>
+      <c r="F30" t="n">
         <v>592</v>
       </c>
-      <c r="F30" t="n">
-        <v>598</v>
-      </c>
       <c r="G30" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="31">
@@ -2142,19 +2243,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>588</v>
+      </c>
+      <c r="F31" t="n">
         <v>592</v>
       </c>
-      <c r="F31" t="n">
-        <v>598</v>
-      </c>
       <c r="G31" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="32">
@@ -2177,10 +2278,10 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>876</v>
+      </c>
+      <c r="F32" t="n">
         <v>877</v>
-      </c>
-      <c r="F32" t="n">
-        <v>878</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
@@ -2247,19 +2348,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>437</v>
+      </c>
+      <c r="F34" t="n">
         <v>439</v>
       </c>
-      <c r="F34" t="n">
-        <v>442</v>
-      </c>
       <c r="G34" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>49500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="35">
@@ -2282,19 +2383,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>588</v>
+      </c>
+      <c r="F35" t="n">
         <v>592</v>
       </c>
-      <c r="F35" t="n">
-        <v>598</v>
-      </c>
       <c r="G35" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="36">
@@ -2317,19 +2418,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>588</v>
+      </c>
+      <c r="F36" t="n">
         <v>592</v>
       </c>
-      <c r="F36" t="n">
-        <v>598</v>
-      </c>
       <c r="G36" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
   </sheetData>
@@ -2343,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7482,6 +7583,1293 @@
         <v>99000</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2418</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H142" t="n">
+        <v>5</v>
+      </c>
+      <c r="I142" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F143" t="n">
+        <v>933</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H143" t="n">
+        <v>3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F146" t="n">
+        <v>434</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F147" t="n">
+        <v>255</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H147" t="n">
+        <v>6</v>
+      </c>
+      <c r="I147" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F148" t="n">
+        <v>824</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F149" t="n">
+        <v>966</v>
+      </c>
+      <c r="G149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F150" t="n">
+        <v>960</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F151" t="n">
+        <v>365</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F152" t="n">
+        <v>480</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F153" t="n">
+        <v>484</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F154" t="n">
+        <v>388</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F155" t="n">
+        <v>481</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F156" t="n">
+        <v>483</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>900</v>
+      </c>
+      <c r="F157" t="n">
+        <v>372</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>900</v>
+      </c>
+      <c r="F158" t="n">
+        <v>496</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>900</v>
+      </c>
+      <c r="F159" t="n">
+        <v>477</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>900</v>
+      </c>
+      <c r="F160" t="n">
+        <v>701</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>900</v>
+      </c>
+      <c r="F161" t="n">
+        <v>943</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>900</v>
+      </c>
+      <c r="F162" t="n">
+        <v>955</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F164" t="n">
+        <v>313</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F165" t="n">
+        <v>192</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H165" t="n">
+        <v>3</v>
+      </c>
+      <c r="I165" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F166" t="n">
+        <v>313</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F167" t="n">
+        <v>876</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F168" t="n">
+        <v>332</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F169" t="n">
+        <v>435</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H169" t="n">
+        <v>4</v>
+      </c>
+      <c r="I169" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F170" t="n">
+        <v>588</v>
+      </c>
+      <c r="G170" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F171" t="n">
+        <v>588</v>
+      </c>
+      <c r="G171" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H171" t="n">
+        <v>4</v>
+      </c>
+      <c r="I171" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F172" t="n">
+        <v>876</v>
+      </c>
+      <c r="G172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F173" t="n">
+        <v>332</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F174" t="n">
+        <v>437</v>
+      </c>
+      <c r="G174" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F175" t="n">
+        <v>588</v>
+      </c>
+      <c r="G175" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H175" t="n">
+        <v>4</v>
+      </c>
+      <c r="I175" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F176" t="n">
+        <v>588</v>
+      </c>
+      <c r="G176" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H176" t="n">
+        <v>4</v>
+      </c>
+      <c r="I176" t="n">
+        <v>66000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,6 +536,22 @@
         <v>563100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>211</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2471200</v>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -550,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -559,11 +575,11 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="43" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
@@ -572,11 +588,11 @@
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="55" customWidth="1" min="24" max="24"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
@@ -605,54 +621,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -670,52 +686,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -820,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -829,16 +845,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -859,7 +875,7 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>2500</v>
@@ -868,16 +884,16 @@
         <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -911,22 +927,22 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
@@ -950,25 +966,25 @@
         <v>2500</v>
       </c>
       <c r="T4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>3000</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>3000</v>
       </c>
-      <c r="W4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2700</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -990,19 +1006,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1011,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1029,19 +1045,19 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>2500</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>1000</v>
@@ -1050,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1075,31 +1091,31 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1114,33 +1130,118 @@
         <v>19000</v>
       </c>
       <c r="R6" t="n">
-        <v>13500</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>5000</v>
       </c>
       <c r="T6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>3000</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>44</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1782000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="V7" t="n">
         <v>2700</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W7" t="n">
         <v>2000</v>
       </c>
-      <c r="W6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X6" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1236,19 +1337,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2393</v>
+      </c>
+      <c r="F2" t="n">
         <v>2418</v>
       </c>
-      <c r="F2" t="n">
-        <v>2423</v>
-      </c>
       <c r="G2" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I2" t="n">
-        <v>75000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="3">
@@ -1271,19 +1372,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>927</v>
+      </c>
+      <c r="F3" t="n">
         <v>933</v>
       </c>
-      <c r="F3" t="n">
-        <v>936</v>
-      </c>
       <c r="G3" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>45000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="4">
@@ -1368,19 +1469,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>430</v>
+      </c>
+      <c r="F6" t="n">
         <v>434</v>
       </c>
-      <c r="F6" t="n">
-        <v>436</v>
-      </c>
       <c r="G6" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7">
@@ -1403,19 +1504,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>253</v>
+      </c>
+      <c r="F7" t="n">
         <v>255</v>
       </c>
-      <c r="F7" t="n">
-        <v>261</v>
-      </c>
       <c r="G7" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>13500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -1441,16 +1542,16 @@
         <v>824</v>
       </c>
       <c r="F8" t="n">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1476,16 +1577,16 @@
         <v>966</v>
       </c>
       <c r="F9" t="n">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1543,19 +1644,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F11" t="n">
         <v>365</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
@@ -1648,19 +1749,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="F14" t="n">
         <v>388</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="15">
@@ -1756,16 +1857,16 @@
         <v>372</v>
       </c>
       <c r="F17" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1858,19 +1959,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
+        <v>698</v>
+      </c>
+      <c r="F20" t="n">
         <v>701</v>
       </c>
-      <c r="F20" t="n">
-        <v>702</v>
-      </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="21">
@@ -1896,16 +1997,16 @@
         <v>943</v>
       </c>
       <c r="F21" t="n">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1931,16 +2032,16 @@
         <v>955</v>
       </c>
       <c r="F22" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1998,19 +2099,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>305</v>
+      </c>
+      <c r="F24" t="n">
         <v>313</v>
       </c>
-      <c r="F24" t="n">
-        <v>314</v>
-      </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="25">
@@ -2033,19 +2134,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>191</v>
+      </c>
+      <c r="F25" t="n">
         <v>192</v>
       </c>
-      <c r="F25" t="n">
-        <v>195</v>
-      </c>
       <c r="G25" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -2068,19 +2169,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>305</v>
+      </c>
+      <c r="F26" t="n">
         <v>313</v>
       </c>
-      <c r="F26" t="n">
-        <v>314</v>
-      </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>19000</v>
+        <v>152000</v>
       </c>
     </row>
     <row r="27">
@@ -2103,19 +2204,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>858</v>
+      </c>
+      <c r="F27" t="n">
         <v>876</v>
       </c>
-      <c r="F27" t="n">
-        <v>877</v>
-      </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I27" t="n">
-        <v>16500</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="28">
@@ -2138,19 +2239,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F28" t="n">
         <v>332</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="29">
@@ -2173,19 +2274,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>428</v>
+      </c>
+      <c r="F29" t="n">
         <v>435</v>
       </c>
-      <c r="F29" t="n">
-        <v>439</v>
-      </c>
       <c r="G29" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="30">
@@ -2208,19 +2309,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>575</v>
+      </c>
+      <c r="F30" t="n">
         <v>588</v>
       </c>
-      <c r="F30" t="n">
-        <v>592</v>
-      </c>
       <c r="G30" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>66000</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="31">
@@ -2243,19 +2344,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>575</v>
+      </c>
+      <c r="F31" t="n">
         <v>588</v>
       </c>
-      <c r="F31" t="n">
-        <v>592</v>
-      </c>
       <c r="G31" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>66000</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="32">
@@ -2278,19 +2379,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>858</v>
+      </c>
+      <c r="F32" t="n">
         <v>876</v>
       </c>
-      <c r="F32" t="n">
-        <v>877</v>
-      </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I32" t="n">
-        <v>16500</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="33">
@@ -2313,19 +2414,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F33" t="n">
         <v>332</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="34">
@@ -2348,19 +2449,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>428</v>
+      </c>
+      <c r="F34" t="n">
         <v>437</v>
       </c>
-      <c r="F34" t="n">
-        <v>439</v>
-      </c>
       <c r="G34" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>33000</v>
+        <v>148500</v>
       </c>
     </row>
     <row r="35">
@@ -2383,19 +2484,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>575</v>
+      </c>
+      <c r="F35" t="n">
         <v>588</v>
       </c>
-      <c r="F35" t="n">
-        <v>592</v>
-      </c>
       <c r="G35" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I35" t="n">
-        <v>66000</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="36">
@@ -2418,19 +2519,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>575</v>
+      </c>
+      <c r="F36" t="n">
         <v>588</v>
       </c>
-      <c r="F36" t="n">
-        <v>592</v>
-      </c>
       <c r="G36" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I36" t="n">
-        <v>66000</v>
+        <v>214500</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8870,6 +8971,1293 @@
         <v>66000</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F177" t="n">
+        <v>2393</v>
+      </c>
+      <c r="G177" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H177" t="n">
+        <v>25</v>
+      </c>
+      <c r="I177" t="n">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F178" t="n">
+        <v>927</v>
+      </c>
+      <c r="G178" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H178" t="n">
+        <v>6</v>
+      </c>
+      <c r="I178" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F181" t="n">
+        <v>430</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H181" t="n">
+        <v>4</v>
+      </c>
+      <c r="I181" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F182" t="n">
+        <v>253</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2</v>
+      </c>
+      <c r="I182" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F183" t="n">
+        <v>824</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F184" t="n">
+        <v>966</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F185" t="n">
+        <v>960</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F186" t="n">
+        <v>363</v>
+      </c>
+      <c r="G186" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F187" t="n">
+        <v>480</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F188" t="n">
+        <v>484</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F189" t="n">
+        <v>344</v>
+      </c>
+      <c r="G189" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H189" t="n">
+        <v>44</v>
+      </c>
+      <c r="I189" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F190" t="n">
+        <v>481</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F191" t="n">
+        <v>483</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>900</v>
+      </c>
+      <c r="F192" t="n">
+        <v>372</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>900</v>
+      </c>
+      <c r="F193" t="n">
+        <v>496</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>900</v>
+      </c>
+      <c r="F194" t="n">
+        <v>477</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>900</v>
+      </c>
+      <c r="F195" t="n">
+        <v>698</v>
+      </c>
+      <c r="G195" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H195" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>900</v>
+      </c>
+      <c r="F196" t="n">
+        <v>943</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>900</v>
+      </c>
+      <c r="F197" t="n">
+        <v>955</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F199" t="n">
+        <v>305</v>
+      </c>
+      <c r="G199" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H199" t="n">
+        <v>8</v>
+      </c>
+      <c r="I199" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F200" t="n">
+        <v>191</v>
+      </c>
+      <c r="G200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H200" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F201" t="n">
+        <v>305</v>
+      </c>
+      <c r="G201" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H201" t="n">
+        <v>8</v>
+      </c>
+      <c r="I201" t="n">
+        <v>152000</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F202" t="n">
+        <v>858</v>
+      </c>
+      <c r="G202" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H202" t="n">
+        <v>18</v>
+      </c>
+      <c r="I202" t="n">
+        <v>297000</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F203" t="n">
+        <v>330</v>
+      </c>
+      <c r="G203" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H203" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F204" t="n">
+        <v>428</v>
+      </c>
+      <c r="G204" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H204" t="n">
+        <v>7</v>
+      </c>
+      <c r="I204" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F205" t="n">
+        <v>575</v>
+      </c>
+      <c r="G205" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H205" t="n">
+        <v>13</v>
+      </c>
+      <c r="I205" t="n">
+        <v>214500</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F206" t="n">
+        <v>575</v>
+      </c>
+      <c r="G206" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H206" t="n">
+        <v>13</v>
+      </c>
+      <c r="I206" t="n">
+        <v>214500</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F207" t="n">
+        <v>858</v>
+      </c>
+      <c r="G207" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H207" t="n">
+        <v>18</v>
+      </c>
+      <c r="I207" t="n">
+        <v>297000</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F208" t="n">
+        <v>330</v>
+      </c>
+      <c r="G208" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F209" t="n">
+        <v>428</v>
+      </c>
+      <c r="G209" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H209" t="n">
+        <v>9</v>
+      </c>
+      <c r="I209" t="n">
+        <v>148500</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F210" t="n">
+        <v>575</v>
+      </c>
+      <c r="G210" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H210" t="n">
+        <v>13</v>
+      </c>
+      <c r="I210" t="n">
+        <v>214500</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F211" t="n">
+        <v>575</v>
+      </c>
+      <c r="G211" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H211" t="n">
+        <v>13</v>
+      </c>
+      <c r="I211" t="n">
+        <v>214500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -552,6 +552,22 @@
         <v>2471200</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>66</v>
+      </c>
+      <c r="C8" t="n">
+        <v>914250</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -574,12 +590,12 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
@@ -587,12 +603,12 @@
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
-    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
@@ -621,54 +637,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -686,52 +702,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -836,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -854,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -875,10 +891,10 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="n">
         <v>1000</v>
@@ -893,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -921,34 +937,34 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -960,34 +976,34 @@
         <v>76000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S4" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="W4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1006,34 +1022,34 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
@@ -1045,34 +1061,34 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S5" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>2250</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1091,31 +1107,31 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1130,31 +1146,31 @@
         <v>19000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="U6" t="n">
         <v>13500</v>
       </c>
       <c r="V6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>900</v>
+      </c>
+      <c r="X6" t="n">
         <v>2700</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3000</v>
-      </c>
       <c r="Y6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1176,34 +1192,34 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1215,33 +1231,118 @@
         <v>152000</v>
       </c>
       <c r="R7" t="n">
-        <v>44000</v>
+        <v>10000</v>
       </c>
       <c r="S7" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="T7" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="U7" t="n">
         <v>4500</v>
       </c>
       <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2700</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2000</v>
       </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>594000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,19 +1438,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2383</v>
+      </c>
+      <c r="F2" t="n">
         <v>2393</v>
       </c>
-      <c r="F2" t="n">
-        <v>2418</v>
-      </c>
       <c r="G2" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>375000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3">
@@ -1372,19 +1473,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>923</v>
+      </c>
+      <c r="F3" t="n">
         <v>927</v>
       </c>
-      <c r="F3" t="n">
-        <v>933</v>
-      </c>
       <c r="G3" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>90000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4">
@@ -1469,19 +1570,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>428</v>
+      </c>
+      <c r="F6" t="n">
         <v>430</v>
       </c>
-      <c r="F6" t="n">
-        <v>434</v>
-      </c>
       <c r="G6" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7">
@@ -1504,19 +1605,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>252</v>
+      </c>
+      <c r="F7" t="n">
         <v>253</v>
       </c>
-      <c r="F7" t="n">
-        <v>255</v>
-      </c>
       <c r="G7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -1647,16 +1748,16 @@
         <v>363</v>
       </c>
       <c r="F11" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1752,16 +1853,16 @@
         <v>344</v>
       </c>
       <c r="F14" t="n">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="G14" t="n">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1962,16 +2063,16 @@
         <v>698</v>
       </c>
       <c r="F20" t="n">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2099,19 +2200,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>300</v>
+      </c>
+      <c r="F24" t="n">
         <v>305</v>
       </c>
-      <c r="F24" t="n">
-        <v>313</v>
-      </c>
       <c r="G24" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25">
@@ -2134,19 +2235,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>188</v>
+      </c>
+      <c r="F25" t="n">
         <v>191</v>
       </c>
-      <c r="F25" t="n">
-        <v>192</v>
-      </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -2169,19 +2270,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>300</v>
+      </c>
+      <c r="F26" t="n">
         <v>305</v>
       </c>
-      <c r="F26" t="n">
-        <v>313</v>
-      </c>
       <c r="G26" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>152000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="27">
@@ -2204,19 +2305,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>853</v>
+      </c>
+      <c r="F27" t="n">
         <v>858</v>
       </c>
-      <c r="F27" t="n">
-        <v>876</v>
-      </c>
       <c r="G27" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="H27" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>297000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="28">
@@ -2239,10 +2340,10 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>328</v>
+      </c>
+      <c r="F28" t="n">
         <v>330</v>
-      </c>
-      <c r="F28" t="n">
-        <v>332</v>
       </c>
       <c r="G28" t="n">
         <v>-2</v>
@@ -2274,19 +2375,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>425</v>
+      </c>
+      <c r="F29" t="n">
         <v>428</v>
       </c>
-      <c r="F29" t="n">
-        <v>435</v>
-      </c>
       <c r="G29" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>115500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="30">
@@ -2309,19 +2410,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>571</v>
+      </c>
+      <c r="F30" t="n">
         <v>575</v>
       </c>
-      <c r="F30" t="n">
-        <v>588</v>
-      </c>
       <c r="G30" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>214500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="31">
@@ -2344,19 +2445,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>571</v>
+      </c>
+      <c r="F31" t="n">
         <v>575</v>
       </c>
-      <c r="F31" t="n">
-        <v>588</v>
-      </c>
       <c r="G31" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>214500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="32">
@@ -2379,19 +2480,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>853</v>
+      </c>
+      <c r="F32" t="n">
         <v>858</v>
       </c>
-      <c r="F32" t="n">
-        <v>876</v>
-      </c>
       <c r="G32" t="n">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="H32" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>297000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="33">
@@ -2414,10 +2515,10 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>328</v>
+      </c>
+      <c r="F33" t="n">
         <v>330</v>
-      </c>
-      <c r="F33" t="n">
-        <v>332</v>
       </c>
       <c r="G33" t="n">
         <v>-2</v>
@@ -2449,19 +2550,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>425</v>
+      </c>
+      <c r="F34" t="n">
         <v>428</v>
       </c>
-      <c r="F34" t="n">
-        <v>437</v>
-      </c>
       <c r="G34" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>148500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="35">
@@ -2484,19 +2585,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>571</v>
+      </c>
+      <c r="F35" t="n">
         <v>575</v>
       </c>
-      <c r="F35" t="n">
-        <v>588</v>
-      </c>
       <c r="G35" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H35" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>214500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="36">
@@ -2519,19 +2620,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>571</v>
+      </c>
+      <c r="F36" t="n">
         <v>575</v>
       </c>
-      <c r="F36" t="n">
-        <v>588</v>
-      </c>
       <c r="G36" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>214500</v>
+        <v>66000</v>
       </c>
     </row>
   </sheetData>
@@ -2545,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I211"/>
+  <dimension ref="A1:I246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10258,6 +10359,1293 @@
         <v>214500</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F212" t="n">
+        <v>2383</v>
+      </c>
+      <c r="G212" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H212" t="n">
+        <v>10</v>
+      </c>
+      <c r="I212" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F213" t="n">
+        <v>923</v>
+      </c>
+      <c r="G213" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H213" t="n">
+        <v>4</v>
+      </c>
+      <c r="I213" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F216" t="n">
+        <v>428</v>
+      </c>
+      <c r="G216" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H216" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F217" t="n">
+        <v>252</v>
+      </c>
+      <c r="G217" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F218" t="n">
+        <v>824</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F219" t="n">
+        <v>966</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F220" t="n">
+        <v>960</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F221" t="n">
+        <v>363</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F222" t="n">
+        <v>480</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F223" t="n">
+        <v>484</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F224" t="n">
+        <v>344</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F225" t="n">
+        <v>481</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F226" t="n">
+        <v>483</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>900</v>
+      </c>
+      <c r="F227" t="n">
+        <v>372</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>900</v>
+      </c>
+      <c r="F228" t="n">
+        <v>496</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>900</v>
+      </c>
+      <c r="F229" t="n">
+        <v>477</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>900</v>
+      </c>
+      <c r="F230" t="n">
+        <v>698</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>900</v>
+      </c>
+      <c r="F231" t="n">
+        <v>943</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>900</v>
+      </c>
+      <c r="F232" t="n">
+        <v>955</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F234" t="n">
+        <v>300</v>
+      </c>
+      <c r="G234" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H234" t="n">
+        <v>5</v>
+      </c>
+      <c r="I234" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F235" t="n">
+        <v>188</v>
+      </c>
+      <c r="G235" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H235" t="n">
+        <v>3</v>
+      </c>
+      <c r="I235" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F236" t="n">
+        <v>300</v>
+      </c>
+      <c r="G236" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H236" t="n">
+        <v>5</v>
+      </c>
+      <c r="I236" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F237" t="n">
+        <v>853</v>
+      </c>
+      <c r="G237" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H237" t="n">
+        <v>5</v>
+      </c>
+      <c r="I237" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F238" t="n">
+        <v>328</v>
+      </c>
+      <c r="G238" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F239" t="n">
+        <v>425</v>
+      </c>
+      <c r="G239" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H239" t="n">
+        <v>3</v>
+      </c>
+      <c r="I239" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F240" t="n">
+        <v>571</v>
+      </c>
+      <c r="G240" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H240" t="n">
+        <v>4</v>
+      </c>
+      <c r="I240" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F241" t="n">
+        <v>571</v>
+      </c>
+      <c r="G241" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H241" t="n">
+        <v>4</v>
+      </c>
+      <c r="I241" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F242" t="n">
+        <v>853</v>
+      </c>
+      <c r="G242" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H242" t="n">
+        <v>5</v>
+      </c>
+      <c r="I242" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F243" t="n">
+        <v>328</v>
+      </c>
+      <c r="G243" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H243" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F244" t="n">
+        <v>425</v>
+      </c>
+      <c r="G244" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3</v>
+      </c>
+      <c r="I244" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F245" t="n">
+        <v>571</v>
+      </c>
+      <c r="G245" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H245" t="n">
+        <v>4</v>
+      </c>
+      <c r="I245" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F246" t="n">
+        <v>571</v>
+      </c>
+      <c r="G246" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H246" t="n">
+        <v>4</v>
+      </c>
+      <c r="I246" t="n">
+        <v>66000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,22 @@
         <v>914250</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1149650</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -582,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -590,9 +606,9 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -603,9 +619,9 @@
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
@@ -642,49 +658,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -707,47 +723,47 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -855,13 +871,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -894,13 +910,13 @@
         <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="T3" t="n">
         <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -940,16 +956,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -958,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -979,25 +995,25 @@
         <v>2500</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>4000</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>3000</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>3000</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2700</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1028,16 +1044,16 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1064,19 +1080,19 @@
         <v>2500</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1110,31 +1126,31 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1149,31 +1165,31 @@
         <v>5000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="T6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U6" t="n">
         <v>3000</v>
       </c>
-      <c r="U6" t="n">
-        <v>13500</v>
-      </c>
       <c r="V6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>2700</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -1195,31 +1211,31 @@
         <v>4</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1234,31 +1250,31 @@
         <v>10000</v>
       </c>
       <c r="S7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T7" t="n">
         <v>8000</v>
       </c>
-      <c r="T7" t="n">
-        <v>1000</v>
-      </c>
       <c r="U7" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X7" t="n">
         <v>2700</v>
       </c>
       <c r="Y7" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1280,13 +1296,13 @@
         <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1319,14 +1335,14 @@
         <v>5000</v>
       </c>
       <c r="S8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T8" t="n">
         <v>5000</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3000</v>
       </c>
-      <c r="U8" t="n">
-        <v>2250</v>
-      </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
@@ -1343,6 +1359,91 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>792000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>900</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1438,19 +1539,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2375</v>
+      </c>
+      <c r="F2" t="n">
         <v>2383</v>
       </c>
-      <c r="F2" t="n">
-        <v>2393</v>
-      </c>
       <c r="G2" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="3">
@@ -1473,19 +1574,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>918</v>
+      </c>
+      <c r="F3" t="n">
         <v>923</v>
       </c>
-      <c r="F3" t="n">
-        <v>927</v>
-      </c>
       <c r="G3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="4">
@@ -1570,19 +1671,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>420</v>
+      </c>
+      <c r="F6" t="n">
         <v>428</v>
       </c>
-      <c r="F6" t="n">
-        <v>430</v>
-      </c>
       <c r="G6" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="7">
@@ -1605,19 +1706,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>245</v>
+      </c>
+      <c r="F7" t="n">
         <v>252</v>
       </c>
-      <c r="F7" t="n">
-        <v>253</v>
-      </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>2250</v>
+        <v>15750</v>
       </c>
     </row>
     <row r="8">
@@ -1745,19 +1846,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F11" t="n">
         <v>363</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -1850,19 +1951,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F14" t="n">
         <v>344</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -2060,19 +2161,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F20" t="n">
         <v>698</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -2200,19 +2301,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>294</v>
+      </c>
+      <c r="F24" t="n">
         <v>300</v>
       </c>
-      <c r="F24" t="n">
-        <v>305</v>
-      </c>
       <c r="G24" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="25">
@@ -2235,19 +2336,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>184</v>
+      </c>
+      <c r="F25" t="n">
         <v>188</v>
       </c>
-      <c r="F25" t="n">
-        <v>191</v>
-      </c>
       <c r="G25" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="26">
@@ -2270,19 +2371,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>294</v>
+      </c>
+      <c r="F26" t="n">
         <v>300</v>
       </c>
-      <c r="F26" t="n">
-        <v>305</v>
-      </c>
       <c r="G26" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>95000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="27">
@@ -2305,19 +2406,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>849</v>
+      </c>
+      <c r="F27" t="n">
         <v>853</v>
       </c>
-      <c r="F27" t="n">
-        <v>858</v>
-      </c>
       <c r="G27" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>82500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="28">
@@ -2343,16 +2444,16 @@
         <v>328</v>
       </c>
       <c r="F28" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2375,19 +2476,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>419</v>
+      </c>
+      <c r="F29" t="n">
         <v>425</v>
       </c>
-      <c r="F29" t="n">
-        <v>428</v>
-      </c>
       <c r="G29" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="30">
@@ -2410,19 +2511,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>564</v>
+      </c>
+      <c r="F30" t="n">
         <v>571</v>
       </c>
-      <c r="F30" t="n">
-        <v>575</v>
-      </c>
       <c r="G30" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="31">
@@ -2445,19 +2546,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>564</v>
+      </c>
+      <c r="F31" t="n">
         <v>571</v>
       </c>
-      <c r="F31" t="n">
-        <v>575</v>
-      </c>
       <c r="G31" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="32">
@@ -2480,19 +2581,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>849</v>
+      </c>
+      <c r="F32" t="n">
         <v>853</v>
       </c>
-      <c r="F32" t="n">
-        <v>858</v>
-      </c>
       <c r="G32" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>82500</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="33">
@@ -2518,16 +2619,16 @@
         <v>328</v>
       </c>
       <c r="F33" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G33" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2550,19 +2651,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>419</v>
+      </c>
+      <c r="F34" t="n">
         <v>425</v>
       </c>
-      <c r="F34" t="n">
-        <v>428</v>
-      </c>
       <c r="G34" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>49500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="35">
@@ -2585,19 +2686,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>564</v>
+      </c>
+      <c r="F35" t="n">
         <v>571</v>
       </c>
-      <c r="F35" t="n">
-        <v>575</v>
-      </c>
       <c r="G35" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="36">
@@ -2620,19 +2721,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>564</v>
+      </c>
+      <c r="F36" t="n">
         <v>571</v>
       </c>
-      <c r="F36" t="n">
-        <v>575</v>
-      </c>
       <c r="G36" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
   </sheetData>
@@ -2646,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:I281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11646,6 +11747,1293 @@
         <v>66000</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2375</v>
+      </c>
+      <c r="G247" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H247" t="n">
+        <v>8</v>
+      </c>
+      <c r="I247" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F248" t="n">
+        <v>918</v>
+      </c>
+      <c r="G248" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H248" t="n">
+        <v>5</v>
+      </c>
+      <c r="I248" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F251" t="n">
+        <v>420</v>
+      </c>
+      <c r="G251" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H251" t="n">
+        <v>8</v>
+      </c>
+      <c r="I251" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F252" t="n">
+        <v>245</v>
+      </c>
+      <c r="G252" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H252" t="n">
+        <v>7</v>
+      </c>
+      <c r="I252" t="n">
+        <v>15750</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F253" t="n">
+        <v>824</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F254" t="n">
+        <v>966</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F255" t="n">
+        <v>960</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F256" t="n">
+        <v>362</v>
+      </c>
+      <c r="G256" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F257" t="n">
+        <v>480</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F258" t="n">
+        <v>484</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F259" t="n">
+        <v>343</v>
+      </c>
+      <c r="G259" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F260" t="n">
+        <v>481</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F261" t="n">
+        <v>483</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>900</v>
+      </c>
+      <c r="F262" t="n">
+        <v>372</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>900</v>
+      </c>
+      <c r="F263" t="n">
+        <v>496</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>900</v>
+      </c>
+      <c r="F264" t="n">
+        <v>477</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>900</v>
+      </c>
+      <c r="F265" t="n">
+        <v>697</v>
+      </c>
+      <c r="G265" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>900</v>
+      </c>
+      <c r="F266" t="n">
+        <v>943</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>900</v>
+      </c>
+      <c r="F267" t="n">
+        <v>955</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F268" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F269" t="n">
+        <v>294</v>
+      </c>
+      <c r="G269" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H269" t="n">
+        <v>6</v>
+      </c>
+      <c r="I269" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F270" t="n">
+        <v>184</v>
+      </c>
+      <c r="G270" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H270" t="n">
+        <v>4</v>
+      </c>
+      <c r="I270" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F271" t="n">
+        <v>294</v>
+      </c>
+      <c r="G271" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H271" t="n">
+        <v>6</v>
+      </c>
+      <c r="I271" t="n">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F272" t="n">
+        <v>849</v>
+      </c>
+      <c r="G272" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H272" t="n">
+        <v>4</v>
+      </c>
+      <c r="I272" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F273" t="n">
+        <v>328</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F274" t="n">
+        <v>419</v>
+      </c>
+      <c r="G274" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H274" t="n">
+        <v>6</v>
+      </c>
+      <c r="I274" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F275" t="n">
+        <v>564</v>
+      </c>
+      <c r="G275" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H275" t="n">
+        <v>7</v>
+      </c>
+      <c r="I275" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F276" t="n">
+        <v>564</v>
+      </c>
+      <c r="G276" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H276" t="n">
+        <v>7</v>
+      </c>
+      <c r="I276" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F277" t="n">
+        <v>849</v>
+      </c>
+      <c r="G277" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H277" t="n">
+        <v>4</v>
+      </c>
+      <c r="I277" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F278" t="n">
+        <v>328</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F279" t="n">
+        <v>419</v>
+      </c>
+      <c r="G279" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H279" t="n">
+        <v>6</v>
+      </c>
+      <c r="I279" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F280" t="n">
+        <v>564</v>
+      </c>
+      <c r="G280" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H280" t="n">
+        <v>7</v>
+      </c>
+      <c r="I280" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F281" t="n">
+        <v>564</v>
+      </c>
+      <c r="G281" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H281" t="n">
+        <v>7</v>
+      </c>
+      <c r="I281" t="n">
+        <v>115500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -584,6 +584,22 @@
         <v>1149650</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>206</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3196100</v>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,36 +614,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="55" customWidth="1" min="27" max="27"/>
+    <col width="29" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,59 +664,59 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -713,57 +729,57 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -865,13 +881,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -895,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
@@ -904,37 +920,37 @@
         <v>45000</v>
       </c>
       <c r="Q3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
         <v>19000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6750</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -950,37 +966,37 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -989,37 +1005,37 @@
         <v>45000</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA4" t="n">
         <v>76000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -1038,31 +1054,31 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -1074,37 +1090,37 @@
         <v>90000</v>
       </c>
       <c r="Q5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
         <v>19000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1120,37 +1136,37 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1159,37 +1175,37 @@
         <v>120000</v>
       </c>
       <c r="Q6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>900</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AA6" t="n">
         <v>19000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>13500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>900</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -1205,37 +1221,37 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>44</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1244,37 +1260,37 @@
         <v>465000</v>
       </c>
       <c r="Q7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>152000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>44000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1290,37 +1306,37 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>594000</v>
@@ -1329,37 +1345,37 @@
         <v>210000</v>
       </c>
       <c r="Q8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>95000</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2250</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1375,37 +1391,37 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1414,36 +1430,121 @@
         <v>195000</v>
       </c>
       <c r="Q9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="R9" t="n">
+        <v>900</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>114000</v>
       </c>
-      <c r="R9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X9" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>143</v>
+      </c>
+      <c r="C10" t="n">
+        <v>55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2359500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>825000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1539,19 +1640,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2328</v>
+      </c>
+      <c r="F2" t="n">
         <v>2375</v>
       </c>
-      <c r="F2" t="n">
-        <v>2383</v>
-      </c>
       <c r="G2" t="n">
-        <v>-8</v>
+        <v>-47</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="I2" t="n">
-        <v>120000</v>
+        <v>705000</v>
       </c>
     </row>
     <row r="3">
@@ -1574,19 +1675,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>910</v>
+      </c>
+      <c r="F3" t="n">
         <v>918</v>
       </c>
-      <c r="F3" t="n">
-        <v>923</v>
-      </c>
       <c r="G3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="4">
@@ -1671,19 +1772,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>419</v>
+      </c>
+      <c r="F6" t="n">
         <v>420</v>
       </c>
-      <c r="F6" t="n">
-        <v>428</v>
-      </c>
       <c r="G6" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>20000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
@@ -1706,19 +1807,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>243</v>
+      </c>
+      <c r="F7" t="n">
         <v>245</v>
       </c>
-      <c r="F7" t="n">
-        <v>252</v>
-      </c>
       <c r="G7" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>15750</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -1849,16 +1950,16 @@
         <v>362</v>
       </c>
       <c r="F11" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1954,16 +2055,16 @@
         <v>343</v>
       </c>
       <c r="F14" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2161,19 +2262,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
+        <v>695</v>
+      </c>
+      <c r="F20" t="n">
         <v>697</v>
       </c>
-      <c r="F20" t="n">
-        <v>698</v>
-      </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="21">
@@ -2196,19 +2297,19 @@
         <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F21" t="n">
         <v>943</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22">
@@ -2231,19 +2332,19 @@
         <v>900</v>
       </c>
       <c r="E22" t="n">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F22" t="n">
         <v>955</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23">
@@ -2304,16 +2405,16 @@
         <v>294</v>
       </c>
       <c r="F24" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G24" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2336,19 +2437,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>183</v>
+      </c>
+      <c r="F25" t="n">
         <v>184</v>
       </c>
-      <c r="F25" t="n">
-        <v>188</v>
-      </c>
       <c r="G25" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -2374,16 +2475,16 @@
         <v>294</v>
       </c>
       <c r="F26" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G26" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2406,19 +2507,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>807</v>
+      </c>
+      <c r="F27" t="n">
         <v>849</v>
       </c>
-      <c r="F27" t="n">
-        <v>853</v>
-      </c>
       <c r="G27" t="n">
-        <v>-4</v>
+        <v>-42</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="I27" t="n">
-        <v>66000</v>
+        <v>693000</v>
       </c>
     </row>
     <row r="28">
@@ -2441,19 +2542,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F28" t="n">
         <v>328</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="29">
@@ -2476,19 +2577,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>414</v>
+      </c>
+      <c r="F29" t="n">
         <v>419</v>
       </c>
-      <c r="F29" t="n">
-        <v>425</v>
-      </c>
       <c r="G29" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="30">
@@ -2511,19 +2612,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>553</v>
+      </c>
+      <c r="F30" t="n">
         <v>564</v>
       </c>
-      <c r="F30" t="n">
-        <v>571</v>
-      </c>
       <c r="G30" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>115500</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="31">
@@ -2546,19 +2647,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>553</v>
+      </c>
+      <c r="F31" t="n">
         <v>564</v>
       </c>
-      <c r="F31" t="n">
-        <v>571</v>
-      </c>
       <c r="G31" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>115500</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="32">
@@ -2581,19 +2682,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>806</v>
+      </c>
+      <c r="F32" t="n">
         <v>849</v>
       </c>
-      <c r="F32" t="n">
-        <v>853</v>
-      </c>
       <c r="G32" t="n">
-        <v>-4</v>
+        <v>-43</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="I32" t="n">
-        <v>66000</v>
+        <v>709500</v>
       </c>
     </row>
     <row r="33">
@@ -2616,19 +2717,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F33" t="n">
         <v>328</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="34">
@@ -2651,19 +2752,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>414</v>
+      </c>
+      <c r="F34" t="n">
         <v>419</v>
       </c>
-      <c r="F34" t="n">
-        <v>425</v>
-      </c>
       <c r="G34" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>99000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="35">
@@ -2686,19 +2787,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>553</v>
+      </c>
+      <c r="F35" t="n">
         <v>564</v>
       </c>
-      <c r="F35" t="n">
-        <v>571</v>
-      </c>
       <c r="G35" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I35" t="n">
-        <v>115500</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="36">
@@ -2721,19 +2822,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>553</v>
+      </c>
+      <c r="F36" t="n">
         <v>564</v>
       </c>
-      <c r="F36" t="n">
-        <v>571</v>
-      </c>
       <c r="G36" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I36" t="n">
-        <v>115500</v>
+        <v>181500</v>
       </c>
     </row>
   </sheetData>
@@ -2747,7 +2848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I281"/>
+  <dimension ref="A1:I316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13034,6 +13135,1293 @@
         <v>115500</v>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2328</v>
+      </c>
+      <c r="G282" t="n">
+        <v>-47</v>
+      </c>
+      <c r="H282" t="n">
+        <v>47</v>
+      </c>
+      <c r="I282" t="n">
+        <v>705000</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F283" t="n">
+        <v>910</v>
+      </c>
+      <c r="G283" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H283" t="n">
+        <v>8</v>
+      </c>
+      <c r="I283" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F286" t="n">
+        <v>419</v>
+      </c>
+      <c r="G286" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H286" t="n">
+        <v>1</v>
+      </c>
+      <c r="I286" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F287" t="n">
+        <v>243</v>
+      </c>
+      <c r="G287" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H287" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F288" t="n">
+        <v>824</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F289" t="n">
+        <v>966</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F290" t="n">
+        <v>960</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F291" t="n">
+        <v>362</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F292" t="n">
+        <v>480</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F293" t="n">
+        <v>484</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F294" t="n">
+        <v>343</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F295" t="n">
+        <v>481</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F296" t="n">
+        <v>483</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>900</v>
+      </c>
+      <c r="F297" t="n">
+        <v>372</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>900</v>
+      </c>
+      <c r="F298" t="n">
+        <v>496</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>900</v>
+      </c>
+      <c r="F299" t="n">
+        <v>477</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>900</v>
+      </c>
+      <c r="F300" t="n">
+        <v>695</v>
+      </c>
+      <c r="G300" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H300" t="n">
+        <v>2</v>
+      </c>
+      <c r="I300" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>900</v>
+      </c>
+      <c r="F301" t="n">
+        <v>942</v>
+      </c>
+      <c r="G301" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H301" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>900</v>
+      </c>
+      <c r="F302" t="n">
+        <v>954</v>
+      </c>
+      <c r="G302" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F303" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F304" t="n">
+        <v>294</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F305" t="n">
+        <v>183</v>
+      </c>
+      <c r="G305" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H305" t="n">
+        <v>1</v>
+      </c>
+      <c r="I305" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F306" t="n">
+        <v>294</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F307" t="n">
+        <v>807</v>
+      </c>
+      <c r="G307" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H307" t="n">
+        <v>42</v>
+      </c>
+      <c r="I307" t="n">
+        <v>693000</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F308" t="n">
+        <v>326</v>
+      </c>
+      <c r="G308" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H308" t="n">
+        <v>2</v>
+      </c>
+      <c r="I308" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F309" t="n">
+        <v>414</v>
+      </c>
+      <c r="G309" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H309" t="n">
+        <v>5</v>
+      </c>
+      <c r="I309" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F310" t="n">
+        <v>553</v>
+      </c>
+      <c r="G310" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H310" t="n">
+        <v>11</v>
+      </c>
+      <c r="I310" t="n">
+        <v>181500</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F311" t="n">
+        <v>553</v>
+      </c>
+      <c r="G311" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H311" t="n">
+        <v>11</v>
+      </c>
+      <c r="I311" t="n">
+        <v>181500</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F312" t="n">
+        <v>806</v>
+      </c>
+      <c r="G312" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H312" t="n">
+        <v>43</v>
+      </c>
+      <c r="I312" t="n">
+        <v>709500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F313" t="n">
+        <v>326</v>
+      </c>
+      <c r="G313" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H313" t="n">
+        <v>2</v>
+      </c>
+      <c r="I313" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F314" t="n">
+        <v>414</v>
+      </c>
+      <c r="G314" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H314" t="n">
+        <v>5</v>
+      </c>
+      <c r="I314" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F315" t="n">
+        <v>553</v>
+      </c>
+      <c r="G315" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H315" t="n">
+        <v>11</v>
+      </c>
+      <c r="I315" t="n">
+        <v>181500</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F316" t="n">
+        <v>553</v>
+      </c>
+      <c r="G316" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H316" t="n">
+        <v>11</v>
+      </c>
+      <c r="I316" t="n">
+        <v>181500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -600,6 +600,22 @@
         <v>3196100</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>283250</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -614,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,27 +638,27 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="43" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="55" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
     <col width="29" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -664,54 +680,54 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>inq Student Kit (Units)</t>
@@ -729,52 +745,52 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -881,34 +897,34 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
@@ -920,19 +936,19 @@
         <v>45000</v>
       </c>
       <c r="Q3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R3" t="n">
         <v>6750</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -947,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>19000</v>
@@ -966,25 +982,25 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -993,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -1005,34 +1021,34 @@
         <v>45000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3000</v>
       </c>
       <c r="AA4" t="n">
         <v>76000</v>
@@ -1054,25 +1070,25 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1090,28 +1106,28 @@
         <v>90000</v>
       </c>
       <c r="Q5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R5" t="n">
         <v>2250</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1136,34 +1152,34 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
@@ -1175,34 +1191,34 @@
         <v>120000</v>
       </c>
       <c r="Q6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R6" t="n">
         <v>13500</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U6" t="n">
         <v>2700</v>
       </c>
-      <c r="S6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1000</v>
-      </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>900</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>19000</v>
@@ -1221,34 +1237,34 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>8</v>
@@ -1260,34 +1276,34 @@
         <v>465000</v>
       </c>
       <c r="Q7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R7" t="n">
         <v>4500</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>2700</v>
       </c>
-      <c r="S7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>8000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>44000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>152000</v>
@@ -1306,34 +1322,34 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>5</v>
@@ -1345,34 +1361,34 @@
         <v>210000</v>
       </c>
       <c r="Q8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R8" t="n">
         <v>2250</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>5000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>95000</v>
@@ -1391,34 +1407,34 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>6</v>
@@ -1430,34 +1446,34 @@
         <v>195000</v>
       </c>
       <c r="Q9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="R9" t="n">
         <v>15750</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>900</v>
       </c>
-      <c r="S9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
         <v>6000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>114000</v>
@@ -1476,19 +1492,19 @@
         <v>55</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1515,36 +1531,121 @@
         <v>825000</v>
       </c>
       <c r="Q10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R10" t="n">
         <v>4500</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>3600</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>247500</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2500</v>
       </c>
-      <c r="T10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="R11" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1640,19 +1741,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2326</v>
+      </c>
+      <c r="F2" t="n">
         <v>2328</v>
       </c>
-      <c r="F2" t="n">
-        <v>2375</v>
-      </c>
       <c r="G2" t="n">
-        <v>-47</v>
+        <v>-2</v>
       </c>
       <c r="H2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>705000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="3">
@@ -1678,16 +1779,16 @@
         <v>910</v>
       </c>
       <c r="F3" t="n">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="G3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1772,10 +1873,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>418</v>
+      </c>
+      <c r="F6" t="n">
         <v>419</v>
-      </c>
-      <c r="F6" t="n">
-        <v>420</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
@@ -1807,19 +1908,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>242</v>
+      </c>
+      <c r="F7" t="n">
         <v>243</v>
       </c>
-      <c r="F7" t="n">
-        <v>245</v>
-      </c>
       <c r="G7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -2265,16 +2366,16 @@
         <v>695</v>
       </c>
       <c r="F20" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2300,16 +2401,16 @@
         <v>942</v>
       </c>
       <c r="F21" t="n">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2335,16 +2436,16 @@
         <v>954</v>
       </c>
       <c r="F22" t="n">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2437,10 +2538,10 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>182</v>
+      </c>
+      <c r="F25" t="n">
         <v>183</v>
-      </c>
-      <c r="F25" t="n">
-        <v>184</v>
       </c>
       <c r="G25" t="n">
         <v>-1</v>
@@ -2507,19 +2608,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>805</v>
+      </c>
+      <c r="F27" t="n">
         <v>807</v>
       </c>
-      <c r="F27" t="n">
-        <v>849</v>
-      </c>
       <c r="G27" t="n">
-        <v>-42</v>
+        <v>-2</v>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>693000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="28">
@@ -2545,16 +2646,16 @@
         <v>326</v>
       </c>
       <c r="F28" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2577,19 +2678,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>412</v>
+      </c>
+      <c r="F29" t="n">
         <v>414</v>
       </c>
-      <c r="F29" t="n">
-        <v>419</v>
-      </c>
       <c r="G29" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>82500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="30">
@@ -2612,19 +2713,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>551</v>
+      </c>
+      <c r="F30" t="n">
         <v>553</v>
       </c>
-      <c r="F30" t="n">
-        <v>564</v>
-      </c>
       <c r="G30" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>181500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="31">
@@ -2647,19 +2748,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>551</v>
+      </c>
+      <c r="F31" t="n">
         <v>553</v>
       </c>
-      <c r="F31" t="n">
-        <v>564</v>
-      </c>
       <c r="G31" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>181500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="32">
@@ -2682,19 +2783,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>805</v>
+      </c>
+      <c r="F32" t="n">
         <v>806</v>
       </c>
-      <c r="F32" t="n">
-        <v>849</v>
-      </c>
       <c r="G32" t="n">
-        <v>-43</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>709500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="33">
@@ -2720,16 +2821,16 @@
         <v>326</v>
       </c>
       <c r="F33" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G33" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2752,19 +2853,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>412</v>
+      </c>
+      <c r="F34" t="n">
         <v>414</v>
       </c>
-      <c r="F34" t="n">
-        <v>419</v>
-      </c>
       <c r="G34" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>82500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="35">
@@ -2787,19 +2888,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>551</v>
+      </c>
+      <c r="F35" t="n">
         <v>553</v>
       </c>
-      <c r="F35" t="n">
-        <v>564</v>
-      </c>
       <c r="G35" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>181500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="36">
@@ -2822,19 +2923,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>551</v>
+      </c>
+      <c r="F36" t="n">
         <v>553</v>
       </c>
-      <c r="F36" t="n">
-        <v>564</v>
-      </c>
       <c r="G36" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>181500</v>
+        <v>33000</v>
       </c>
     </row>
   </sheetData>
@@ -2848,7 +2949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14422,6 +14523,1293 @@
         <v>181500</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F317" t="n">
+        <v>2326</v>
+      </c>
+      <c r="G317" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H317" t="n">
+        <v>2</v>
+      </c>
+      <c r="I317" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F318" t="n">
+        <v>910</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F321" t="n">
+        <v>418</v>
+      </c>
+      <c r="G321" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F322" t="n">
+        <v>242</v>
+      </c>
+      <c r="G322" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H322" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F323" t="n">
+        <v>824</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F324" t="n">
+        <v>966</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F325" t="n">
+        <v>960</v>
+      </c>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0</v>
+      </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F326" t="n">
+        <v>362</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F327" t="n">
+        <v>480</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F328" t="n">
+        <v>484</v>
+      </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F329" t="n">
+        <v>343</v>
+      </c>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F330" t="n">
+        <v>481</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F331" t="n">
+        <v>483</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>900</v>
+      </c>
+      <c r="F332" t="n">
+        <v>372</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>900</v>
+      </c>
+      <c r="F333" t="n">
+        <v>496</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>900</v>
+      </c>
+      <c r="F334" t="n">
+        <v>477</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>900</v>
+      </c>
+      <c r="F335" t="n">
+        <v>695</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>900</v>
+      </c>
+      <c r="F336" t="n">
+        <v>942</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>900</v>
+      </c>
+      <c r="F337" t="n">
+        <v>954</v>
+      </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F338" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F339" t="n">
+        <v>294</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F340" t="n">
+        <v>182</v>
+      </c>
+      <c r="G340" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H340" t="n">
+        <v>1</v>
+      </c>
+      <c r="I340" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F341" t="n">
+        <v>294</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F342" t="n">
+        <v>805</v>
+      </c>
+      <c r="G342" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H342" t="n">
+        <v>2</v>
+      </c>
+      <c r="I342" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F343" t="n">
+        <v>326</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F344" t="n">
+        <v>412</v>
+      </c>
+      <c r="G344" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H344" t="n">
+        <v>2</v>
+      </c>
+      <c r="I344" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F345" t="n">
+        <v>551</v>
+      </c>
+      <c r="G345" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H345" t="n">
+        <v>2</v>
+      </c>
+      <c r="I345" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F346" t="n">
+        <v>551</v>
+      </c>
+      <c r="G346" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H346" t="n">
+        <v>2</v>
+      </c>
+      <c r="I346" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F347" t="n">
+        <v>805</v>
+      </c>
+      <c r="G347" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
+      </c>
+      <c r="I347" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F348" t="n">
+        <v>326</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F349" t="n">
+        <v>412</v>
+      </c>
+      <c r="G349" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H349" t="n">
+        <v>2</v>
+      </c>
+      <c r="I349" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F350" t="n">
+        <v>551</v>
+      </c>
+      <c r="G350" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H350" t="n">
+        <v>2</v>
+      </c>
+      <c r="I350" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F351" t="n">
+        <v>551</v>
+      </c>
+      <c r="G351" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H351" t="n">
+        <v>2</v>
+      </c>
+      <c r="I351" t="n">
+        <v>33000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -616,6 +616,22 @@
         <v>283250</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>440550</v>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -630,36 +646,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="43" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
     <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="29" customWidth="1" min="27" max="27"/>
+    <col width="55" customWidth="1" min="26" max="26"/>
+    <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -680,59 +696,59 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -745,57 +761,57 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -900,16 +916,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -924,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
@@ -936,19 +952,19 @@
         <v>45000</v>
       </c>
       <c r="Q3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S3" t="n">
         <v>2500</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>6750</v>
       </c>
-      <c r="S3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -963,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -982,37 +998,37 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -1021,37 +1037,37 @@
         <v>45000</v>
       </c>
       <c r="Q4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S4" t="n">
         <v>2500</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>3000</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>3000</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3000</v>
       </c>
-      <c r="X4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4000</v>
-      </c>
       <c r="AA4" t="n">
-        <v>76000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1082,10 +1098,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1097,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
@@ -1106,25 +1122,25 @@
         <v>90000</v>
       </c>
       <c r="Q5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S5" t="n">
         <v>2500</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>2250</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1000</v>
-      </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1136,7 +1152,7 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1152,16 +1168,16 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1170,19 +1186,19 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1191,37 +1207,37 @@
         <v>120000</v>
       </c>
       <c r="Q6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S6" t="n">
         <v>5000</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>13500</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>3000</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>900</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2000</v>
       </c>
-      <c r="U6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA6" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1237,37 +1253,37 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>44</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1276,37 +1292,37 @@
         <v>465000</v>
       </c>
       <c r="Q7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S7" t="n">
         <v>10000</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>4500</v>
       </c>
-      <c r="S7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2700</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>44000</v>
       </c>
-      <c r="W7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z7" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>152000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1322,20 +1338,20 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1349,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>594000</v>
@@ -1361,20 +1377,20 @@
         <v>210000</v>
       </c>
       <c r="Q8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="R8" t="n">
         <v>5000</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T8" t="n">
         <v>2250</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3000</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
@@ -1388,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>95000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1407,37 +1423,37 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1446,37 +1462,37 @@
         <v>195000</v>
       </c>
       <c r="Q9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S9" t="n">
         <v>20000</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>15750</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>4000</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>900</v>
       </c>
-      <c r="V9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1492,28 +1508,28 @@
         <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1531,28 +1547,28 @@
         <v>825000</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2500</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>4500</v>
       </c>
-      <c r="S10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>3600</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1577,19 +1593,19 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1616,19 +1632,19 @@
         <v>30000</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2500</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>2250</v>
       </c>
-      <c r="S11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1646,6 +1662,91 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>297000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>900</v>
+      </c>
+      <c r="X12" t="n">
+        <v>900</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1741,19 +1842,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2323</v>
+      </c>
+      <c r="F2" t="n">
         <v>2326</v>
       </c>
-      <c r="F2" t="n">
-        <v>2328</v>
-      </c>
       <c r="G2" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="3">
@@ -1776,19 +1877,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="F3" t="n">
         <v>910</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -1873,10 +1974,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>417</v>
+      </c>
+      <c r="F6" t="n">
         <v>418</v>
-      </c>
-      <c r="F6" t="n">
-        <v>419</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
@@ -1908,10 +2009,10 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>241</v>
+      </c>
+      <c r="F7" t="n">
         <v>242</v>
-      </c>
-      <c r="F7" t="n">
-        <v>243</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
@@ -2048,19 +2149,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F11" t="n">
         <v>362</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -2258,19 +2359,19 @@
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F17" t="n">
         <v>372</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18">
@@ -2363,19 +2464,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F20" t="n">
         <v>695</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -2503,19 +2604,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F24" t="n">
         <v>294</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="25">
@@ -2538,10 +2639,10 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>181</v>
+      </c>
+      <c r="F25" t="n">
         <v>182</v>
-      </c>
-      <c r="F25" t="n">
-        <v>183</v>
       </c>
       <c r="G25" t="n">
         <v>-1</v>
@@ -2573,19 +2674,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F26" t="n">
         <v>294</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="27">
@@ -2608,19 +2709,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>804</v>
+      </c>
+      <c r="F27" t="n">
         <v>805</v>
       </c>
-      <c r="F27" t="n">
-        <v>807</v>
-      </c>
       <c r="G27" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>33000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="28">
@@ -2678,10 +2779,10 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>410</v>
+      </c>
+      <c r="F29" t="n">
         <v>412</v>
-      </c>
-      <c r="F29" t="n">
-        <v>414</v>
       </c>
       <c r="G29" t="n">
         <v>-2</v>
@@ -2713,19 +2814,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>548</v>
+      </c>
+      <c r="F30" t="n">
         <v>551</v>
       </c>
-      <c r="F30" t="n">
-        <v>553</v>
-      </c>
       <c r="G30" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="31">
@@ -2748,19 +2849,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>548</v>
+      </c>
+      <c r="F31" t="n">
         <v>551</v>
       </c>
-      <c r="F31" t="n">
-        <v>553</v>
-      </c>
       <c r="G31" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="32">
@@ -2783,10 +2884,10 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>804</v>
+      </c>
+      <c r="F32" t="n">
         <v>805</v>
-      </c>
-      <c r="F32" t="n">
-        <v>806</v>
       </c>
       <c r="G32" t="n">
         <v>-1</v>
@@ -2853,10 +2954,10 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>410</v>
+      </c>
+      <c r="F34" t="n">
         <v>412</v>
-      </c>
-      <c r="F34" t="n">
-        <v>414</v>
       </c>
       <c r="G34" t="n">
         <v>-2</v>
@@ -2888,19 +2989,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>548</v>
+      </c>
+      <c r="F35" t="n">
         <v>551</v>
       </c>
-      <c r="F35" t="n">
-        <v>553</v>
-      </c>
       <c r="G35" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="36">
@@ -2923,19 +3024,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>548</v>
+      </c>
+      <c r="F36" t="n">
         <v>551</v>
       </c>
-      <c r="F36" t="n">
-        <v>553</v>
-      </c>
       <c r="G36" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>33000</v>
+        <v>49500</v>
       </c>
     </row>
   </sheetData>
@@ -2949,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I351"/>
+  <dimension ref="A1:I386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15810,6 +15911,1293 @@
         <v>33000</v>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F352" t="n">
+        <v>2323</v>
+      </c>
+      <c r="G352" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>3</v>
+      </c>
+      <c r="I352" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F353" t="n">
+        <v>908</v>
+      </c>
+      <c r="G353" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H353" t="n">
+        <v>2</v>
+      </c>
+      <c r="I353" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F356" t="n">
+        <v>417</v>
+      </c>
+      <c r="G356" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
+      </c>
+      <c r="I356" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F357" t="n">
+        <v>241</v>
+      </c>
+      <c r="G357" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H357" t="n">
+        <v>1</v>
+      </c>
+      <c r="I357" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F358" t="n">
+        <v>824</v>
+      </c>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F359" t="n">
+        <v>966</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
+      </c>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F360" t="n">
+        <v>960</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F361" t="n">
+        <v>361</v>
+      </c>
+      <c r="G361" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>1</v>
+      </c>
+      <c r="I361" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F362" t="n">
+        <v>480</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F363" t="n">
+        <v>484</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F364" t="n">
+        <v>343</v>
+      </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+      <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F365" t="n">
+        <v>481</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F366" t="n">
+        <v>483</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>900</v>
+      </c>
+      <c r="F367" t="n">
+        <v>371</v>
+      </c>
+      <c r="G367" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H367" t="n">
+        <v>1</v>
+      </c>
+      <c r="I367" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>900</v>
+      </c>
+      <c r="F368" t="n">
+        <v>496</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>900</v>
+      </c>
+      <c r="F369" t="n">
+        <v>477</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="n">
+        <v>0</v>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>900</v>
+      </c>
+      <c r="F370" t="n">
+        <v>694</v>
+      </c>
+      <c r="G370" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H370" t="n">
+        <v>1</v>
+      </c>
+      <c r="I370" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>900</v>
+      </c>
+      <c r="F371" t="n">
+        <v>942</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>900</v>
+      </c>
+      <c r="F372" t="n">
+        <v>954</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F373" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F374" t="n">
+        <v>291</v>
+      </c>
+      <c r="G374" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H374" t="n">
+        <v>3</v>
+      </c>
+      <c r="I374" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F375" t="n">
+        <v>181</v>
+      </c>
+      <c r="G375" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H375" t="n">
+        <v>1</v>
+      </c>
+      <c r="I375" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F376" t="n">
+        <v>291</v>
+      </c>
+      <c r="G376" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H376" t="n">
+        <v>3</v>
+      </c>
+      <c r="I376" t="n">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F377" t="n">
+        <v>804</v>
+      </c>
+      <c r="G377" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H377" t="n">
+        <v>1</v>
+      </c>
+      <c r="I377" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F378" t="n">
+        <v>326</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" t="n">
+        <v>0</v>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F379" t="n">
+        <v>410</v>
+      </c>
+      <c r="G379" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H379" t="n">
+        <v>2</v>
+      </c>
+      <c r="I379" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F380" t="n">
+        <v>548</v>
+      </c>
+      <c r="G380" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H380" t="n">
+        <v>3</v>
+      </c>
+      <c r="I380" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F381" t="n">
+        <v>548</v>
+      </c>
+      <c r="G381" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H381" t="n">
+        <v>3</v>
+      </c>
+      <c r="I381" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F382" t="n">
+        <v>804</v>
+      </c>
+      <c r="G382" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H382" t="n">
+        <v>1</v>
+      </c>
+      <c r="I382" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F383" t="n">
+        <v>326</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F384" t="n">
+        <v>410</v>
+      </c>
+      <c r="G384" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H384" t="n">
+        <v>2</v>
+      </c>
+      <c r="I384" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F385" t="n">
+        <v>548</v>
+      </c>
+      <c r="G385" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H385" t="n">
+        <v>3</v>
+      </c>
+      <c r="I385" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F386" t="n">
+        <v>548</v>
+      </c>
+      <c r="G386" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H386" t="n">
+        <v>3</v>
+      </c>
+      <c r="I386" t="n">
+        <v>49500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,6 +632,22 @@
         <v>440550</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>72</v>
+      </c>
+      <c r="C13" t="n">
+        <v>876400</v>
+      </c>
+      <c r="D13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -646,31 +662,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
     <col width="45" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
     <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
-    <col width="55" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
@@ -691,14 +707,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
@@ -716,39 +732,39 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -756,14 +772,14 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
@@ -781,37 +797,37 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -910,10 +926,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -925,10 +941,10 @@
         <v>3</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -949,10 +965,10 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19000</v>
       </c>
       <c r="R3" t="n">
         <v>1000</v>
@@ -964,10 +980,10 @@
         <v>6750</v>
       </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -995,10 +1011,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -1016,7 +1032,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1028,16 +1044,16 @@
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>45000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>76000</v>
       </c>
       <c r="R4" t="n">
         <v>4000</v>
@@ -1055,19 +1071,19 @@
         <v>3000</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2700</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>3000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1080,10 +1096,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1095,34 +1111,34 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19000</v>
       </c>
       <c r="R5" t="n">
         <v>1000</v>
@@ -1134,10 +1150,10 @@
         <v>2250</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1149,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1165,10 +1181,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1180,34 +1196,34 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>120000</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19000</v>
       </c>
       <c r="R6" t="n">
         <v>1000</v>
@@ -1219,25 +1235,25 @@
         <v>13500</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>3000</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
         <v>900</v>
       </c>
-      <c r="X6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>2000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1250,10 +1266,10 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>31</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
@@ -1265,16 +1281,16 @@
         <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>44</v>
@@ -1289,10 +1305,10 @@
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>465000</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>152000</v>
       </c>
       <c r="R7" t="n">
         <v>8000</v>
@@ -1304,16 +1320,16 @@
         <v>4500</v>
       </c>
       <c r="U7" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="V7" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="X7" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>44000</v>
@@ -1335,10 +1351,10 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
         <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -1350,10 +1366,10 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1374,10 +1390,10 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>210000</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>95000</v>
       </c>
       <c r="R8" t="n">
         <v>5000</v>
@@ -1389,10 +1405,10 @@
         <v>2250</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>3000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1420,10 +1436,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
         <v>13</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -1435,16 +1451,16 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1459,10 +1475,10 @@
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>195000</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>114000</v>
       </c>
       <c r="R9" t="n">
         <v>6000</v>
@@ -1474,16 +1490,16 @@
         <v>15750</v>
       </c>
       <c r="U9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V9" t="n">
         <v>4000</v>
       </c>
-      <c r="V9" t="n">
-        <v>1000</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -1505,10 +1521,10 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>55</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1520,16 +1536,16 @@
         <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1544,10 +1560,10 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>825000</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1559,16 +1575,16 @@
         <v>4500</v>
       </c>
       <c r="U10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="X10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1590,10 +1606,10 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1605,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1629,10 +1645,10 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>30000</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1644,10 +1660,10 @@
         <v>2250</v>
       </c>
       <c r="U11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1675,10 +1691,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -1699,13 +1715,13 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1714,10 +1730,10 @@
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>75000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>57000</v>
       </c>
       <c r="R12" t="n">
         <v>3000</v>
@@ -1738,15 +1754,100 @@
         <v>900</v>
       </c>
       <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
         <v>900</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
       <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>228000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>900</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1842,19 +1943,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2319</v>
+      </c>
+      <c r="F2" t="n">
         <v>2323</v>
       </c>
-      <c r="F2" t="n">
-        <v>2326</v>
-      </c>
       <c r="G2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="3">
@@ -1877,10 +1978,10 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>906</v>
+      </c>
+      <c r="F3" t="n">
         <v>908</v>
-      </c>
-      <c r="F3" t="n">
-        <v>910</v>
       </c>
       <c r="G3" t="n">
         <v>-2</v>
@@ -1974,19 +2075,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
         <v>417</v>
       </c>
-      <c r="F6" t="n">
-        <v>418</v>
-      </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7">
@@ -2009,19 +2110,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>239</v>
+      </c>
+      <c r="F7" t="n">
         <v>241</v>
       </c>
-      <c r="F7" t="n">
-        <v>242</v>
-      </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2250</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -2149,10 +2250,10 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
+        <v>360</v>
+      </c>
+      <c r="F11" t="n">
         <v>361</v>
-      </c>
-      <c r="F11" t="n">
-        <v>362</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
@@ -2184,19 +2285,19 @@
         <v>1000</v>
       </c>
       <c r="E12" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F12" t="n">
         <v>480</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -2362,16 +2463,16 @@
         <v>371</v>
       </c>
       <c r="F17" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2467,16 +2568,16 @@
         <v>694</v>
       </c>
       <c r="F20" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2499,19 +2600,19 @@
         <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F21" t="n">
         <v>942</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22">
@@ -2604,19 +2705,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>279</v>
+      </c>
+      <c r="F24" t="n">
         <v>291</v>
       </c>
-      <c r="F24" t="n">
-        <v>294</v>
-      </c>
       <c r="G24" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="25">
@@ -2639,10 +2740,10 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>180</v>
+      </c>
+      <c r="F25" t="n">
         <v>181</v>
-      </c>
-      <c r="F25" t="n">
-        <v>182</v>
       </c>
       <c r="G25" t="n">
         <v>-1</v>
@@ -2674,19 +2775,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>279</v>
+      </c>
+      <c r="F26" t="n">
         <v>291</v>
       </c>
-      <c r="F26" t="n">
-        <v>294</v>
-      </c>
       <c r="G26" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>57000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="27">
@@ -2712,16 +2813,16 @@
         <v>804</v>
       </c>
       <c r="F27" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2744,19 +2845,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F28" t="n">
         <v>326</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="29">
@@ -2779,19 +2880,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>406</v>
+      </c>
+      <c r="F29" t="n">
         <v>410</v>
       </c>
-      <c r="F29" t="n">
-        <v>412</v>
-      </c>
       <c r="G29" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>33000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="30">
@@ -2814,19 +2915,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>543</v>
+      </c>
+      <c r="F30" t="n">
         <v>548</v>
       </c>
-      <c r="F30" t="n">
-        <v>551</v>
-      </c>
       <c r="G30" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="31">
@@ -2849,19 +2950,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>543</v>
+      </c>
+      <c r="F31" t="n">
         <v>548</v>
       </c>
-      <c r="F31" t="n">
-        <v>551</v>
-      </c>
       <c r="G31" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="32">
@@ -2887,16 +2988,16 @@
         <v>804</v>
       </c>
       <c r="F32" t="n">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2919,19 +3020,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F33" t="n">
         <v>326</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="34">
@@ -2954,19 +3055,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>406</v>
+      </c>
+      <c r="F34" t="n">
         <v>410</v>
       </c>
-      <c r="F34" t="n">
-        <v>412</v>
-      </c>
       <c r="G34" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>33000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="35">
@@ -2989,19 +3090,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>543</v>
+      </c>
+      <c r="F35" t="n">
         <v>548</v>
       </c>
-      <c r="F35" t="n">
-        <v>551</v>
-      </c>
       <c r="G35" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="36">
@@ -3024,19 +3125,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>543</v>
+      </c>
+      <c r="F36" t="n">
         <v>548</v>
       </c>
-      <c r="F36" t="n">
-        <v>551</v>
-      </c>
       <c r="G36" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>49500</v>
+        <v>82500</v>
       </c>
     </row>
   </sheetData>
@@ -3050,7 +3151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I386"/>
+  <dimension ref="A1:I421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17198,6 +17299,1293 @@
         <v>49500</v>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F387" t="n">
+        <v>2319</v>
+      </c>
+      <c r="G387" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H387" t="n">
+        <v>4</v>
+      </c>
+      <c r="I387" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F388" t="n">
+        <v>906</v>
+      </c>
+      <c r="G388" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H388" t="n">
+        <v>2</v>
+      </c>
+      <c r="I388" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="n">
+        <v>0</v>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F391" t="n">
+        <v>413</v>
+      </c>
+      <c r="G391" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H391" t="n">
+        <v>4</v>
+      </c>
+      <c r="I391" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F392" t="n">
+        <v>239</v>
+      </c>
+      <c r="G392" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H392" t="n">
+        <v>2</v>
+      </c>
+      <c r="I392" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F393" t="n">
+        <v>824</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F394" t="n">
+        <v>966</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F395" t="n">
+        <v>960</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F396" t="n">
+        <v>360</v>
+      </c>
+      <c r="G396" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H396" t="n">
+        <v>1</v>
+      </c>
+      <c r="I396" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F397" t="n">
+        <v>479</v>
+      </c>
+      <c r="G397" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F398" t="n">
+        <v>484</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F399" t="n">
+        <v>343</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F400" t="n">
+        <v>481</v>
+      </c>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F401" t="n">
+        <v>483</v>
+      </c>
+      <c r="G401" t="n">
+        <v>0</v>
+      </c>
+      <c r="H401" t="n">
+        <v>0</v>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>900</v>
+      </c>
+      <c r="F402" t="n">
+        <v>371</v>
+      </c>
+      <c r="G402" t="n">
+        <v>0</v>
+      </c>
+      <c r="H402" t="n">
+        <v>0</v>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>900</v>
+      </c>
+      <c r="F403" t="n">
+        <v>496</v>
+      </c>
+      <c r="G403" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>900</v>
+      </c>
+      <c r="F404" t="n">
+        <v>477</v>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="n">
+        <v>0</v>
+      </c>
+      <c r="I404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>900</v>
+      </c>
+      <c r="F405" t="n">
+        <v>694</v>
+      </c>
+      <c r="G405" t="n">
+        <v>0</v>
+      </c>
+      <c r="H405" t="n">
+        <v>0</v>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>900</v>
+      </c>
+      <c r="F406" t="n">
+        <v>941</v>
+      </c>
+      <c r="G406" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>1</v>
+      </c>
+      <c r="I406" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>900</v>
+      </c>
+      <c r="F407" t="n">
+        <v>954</v>
+      </c>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>0</v>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F408" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G408" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" t="n">
+        <v>0</v>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F409" t="n">
+        <v>279</v>
+      </c>
+      <c r="G409" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H409" t="n">
+        <v>12</v>
+      </c>
+      <c r="I409" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F410" t="n">
+        <v>180</v>
+      </c>
+      <c r="G410" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H410" t="n">
+        <v>1</v>
+      </c>
+      <c r="I410" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F411" t="n">
+        <v>279</v>
+      </c>
+      <c r="G411" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H411" t="n">
+        <v>12</v>
+      </c>
+      <c r="I411" t="n">
+        <v>228000</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F412" t="n">
+        <v>804</v>
+      </c>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F413" t="n">
+        <v>324</v>
+      </c>
+      <c r="G413" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H413" t="n">
+        <v>2</v>
+      </c>
+      <c r="I413" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F414" t="n">
+        <v>406</v>
+      </c>
+      <c r="G414" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H414" t="n">
+        <v>4</v>
+      </c>
+      <c r="I414" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F415" t="n">
+        <v>543</v>
+      </c>
+      <c r="G415" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H415" t="n">
+        <v>5</v>
+      </c>
+      <c r="I415" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F416" t="n">
+        <v>543</v>
+      </c>
+      <c r="G416" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H416" t="n">
+        <v>5</v>
+      </c>
+      <c r="I416" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F417" t="n">
+        <v>804</v>
+      </c>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="n">
+        <v>0</v>
+      </c>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F418" t="n">
+        <v>324</v>
+      </c>
+      <c r="G418" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H418" t="n">
+        <v>2</v>
+      </c>
+      <c r="I418" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F419" t="n">
+        <v>406</v>
+      </c>
+      <c r="G419" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H419" t="n">
+        <v>4</v>
+      </c>
+      <c r="I419" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F420" t="n">
+        <v>543</v>
+      </c>
+      <c r="G420" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H420" t="n">
+        <v>5</v>
+      </c>
+      <c r="I420" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F421" t="n">
+        <v>543</v>
+      </c>
+      <c r="G421" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H421" t="n">
+        <v>5</v>
+      </c>
+      <c r="I421" t="n">
+        <v>82500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,22 @@
         <v>876400</v>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>152</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2162750</v>
+      </c>
+      <c r="D14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -662,31 +678,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="48" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
@@ -707,39 +723,39 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
@@ -747,24 +763,24 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -772,39 +788,39 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
@@ -812,22 +828,22 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -926,25 +942,25 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -965,25 +981,25 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>45000</v>
-      </c>
       <c r="R3" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="S3" t="n">
         <v>2500</v>
       </c>
       <c r="T3" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1011,19 +1027,19 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1035,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -1050,19 +1066,19 @@
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>76000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>45000</v>
-      </c>
       <c r="R4" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2500</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="U4" t="n">
         <v>3000</v>
@@ -1074,16 +1090,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2700</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -1096,10 +1112,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1111,16 +1127,16 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1129,37 +1145,37 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>19000</v>
       </c>
-      <c r="Q5" t="n">
-        <v>90000</v>
-      </c>
       <c r="R5" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="S5" t="n">
         <v>2500</v>
       </c>
       <c r="T5" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1168,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1181,79 +1197,79 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q6" t="n">
-        <v>120000</v>
-      </c>
       <c r="R6" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="S6" t="n">
         <v>5000</v>
       </c>
       <c r="T6" t="n">
-        <v>13500</v>
+        <v>1000</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V6" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>2700</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>900</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -1266,25 +1282,25 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
-        <v>31</v>
-      </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -1293,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1305,25 +1321,25 @@
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>152000</v>
       </c>
-      <c r="Q7" t="n">
-        <v>465000</v>
-      </c>
       <c r="R7" t="n">
-        <v>8000</v>
+        <v>4500</v>
       </c>
       <c r="S7" t="n">
         <v>10000</v>
       </c>
       <c r="T7" t="n">
-        <v>4500</v>
+        <v>8000</v>
       </c>
       <c r="U7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V7" t="n">
         <v>2000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1000</v>
       </c>
       <c r="W7" t="n">
         <v>2700</v>
@@ -1332,10 +1348,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>44000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1351,25 +1367,25 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1390,25 +1406,25 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>95000</v>
       </c>
-      <c r="Q8" t="n">
-        <v>210000</v>
-      </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>2250</v>
       </c>
       <c r="S8" t="n">
         <v>5000</v>
       </c>
       <c r="T8" t="n">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1436,25 +1452,25 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>13</v>
-      </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1463,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1475,25 +1491,25 @@
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>114000</v>
       </c>
-      <c r="Q9" t="n">
-        <v>195000</v>
-      </c>
       <c r="R9" t="n">
-        <v>6000</v>
+        <v>15750</v>
       </c>
       <c r="S9" t="n">
         <v>20000</v>
       </c>
       <c r="T9" t="n">
-        <v>15750</v>
+        <v>6000</v>
       </c>
       <c r="U9" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="V9" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="W9" t="n">
         <v>900</v>
@@ -1502,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1521,25 +1537,25 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -1560,25 +1576,25 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>825000</v>
       </c>
       <c r="Q10" t="n">
-        <v>825000</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="S10" t="n">
         <v>2500</v>
       </c>
       <c r="T10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>3600</v>
@@ -1606,25 +1622,25 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1645,25 +1661,25 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Q11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="S11" t="n">
         <v>2500</v>
       </c>
       <c r="T11" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1691,19 +1707,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1721,28 +1737,28 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>57000</v>
       </c>
-      <c r="Q12" t="n">
-        <v>75000</v>
-      </c>
       <c r="R12" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="S12" t="n">
         <v>2500</v>
       </c>
       <c r="T12" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="U12" t="n">
         <v>1000</v>
@@ -1760,10 +1776,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>900</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1776,25 +1792,25 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1815,25 +1831,25 @@
         <v>528000</v>
       </c>
       <c r="P13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q13" t="n">
         <v>228000</v>
       </c>
-      <c r="Q13" t="n">
-        <v>90000</v>
-      </c>
       <c r="R13" t="n">
-        <v>12000</v>
+        <v>4500</v>
       </c>
       <c r="S13" t="n">
         <v>10000</v>
       </c>
       <c r="T13" t="n">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="U13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V13" t="n">
         <v>2000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1000</v>
       </c>
       <c r="W13" t="n">
         <v>900</v>
@@ -1848,6 +1864,91 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>285000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>190000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,19 +2044,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2304</v>
+      </c>
+      <c r="F2" t="n">
         <v>2319</v>
       </c>
-      <c r="F2" t="n">
-        <v>2323</v>
-      </c>
       <c r="G2" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>60000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="3">
@@ -1978,19 +2079,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>902</v>
+      </c>
+      <c r="F3" t="n">
         <v>906</v>
       </c>
-      <c r="F3" t="n">
-        <v>908</v>
-      </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4">
@@ -2075,10 +2176,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>409</v>
+      </c>
+      <c r="F6" t="n">
         <v>413</v>
-      </c>
-      <c r="F6" t="n">
-        <v>417</v>
       </c>
       <c r="G6" t="n">
         <v>-4</v>
@@ -2110,19 +2211,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>232</v>
+      </c>
+      <c r="F7" t="n">
         <v>239</v>
       </c>
-      <c r="F7" t="n">
-        <v>241</v>
-      </c>
       <c r="G7" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>4500</v>
+        <v>15750</v>
       </c>
     </row>
     <row r="8">
@@ -2253,16 +2354,16 @@
         <v>360</v>
       </c>
       <c r="F11" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2288,16 +2389,16 @@
         <v>479</v>
       </c>
       <c r="F12" t="n">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2603,16 +2704,16 @@
         <v>941</v>
       </c>
       <c r="F21" t="n">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2705,19 +2806,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>269</v>
+      </c>
+      <c r="F24" t="n">
         <v>279</v>
       </c>
-      <c r="F24" t="n">
-        <v>291</v>
-      </c>
       <c r="G24" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25">
@@ -2740,19 +2841,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>178</v>
+      </c>
+      <c r="F25" t="n">
         <v>180</v>
       </c>
-      <c r="F25" t="n">
-        <v>181</v>
-      </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
@@ -2775,19 +2876,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>269</v>
+      </c>
+      <c r="F26" t="n">
         <v>279</v>
       </c>
-      <c r="F26" t="n">
-        <v>291</v>
-      </c>
       <c r="G26" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>228000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="27">
@@ -2810,19 +2911,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="F27" t="n">
         <v>804</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="28">
@@ -2848,16 +2949,16 @@
         <v>324</v>
       </c>
       <c r="F28" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2880,19 +2981,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>392</v>
+      </c>
+      <c r="F29" t="n">
         <v>406</v>
       </c>
-      <c r="F29" t="n">
-        <v>410</v>
-      </c>
       <c r="G29" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I29" t="n">
-        <v>66000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="30">
@@ -2915,19 +3016,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>526</v>
+      </c>
+      <c r="F30" t="n">
         <v>543</v>
       </c>
-      <c r="F30" t="n">
-        <v>548</v>
-      </c>
       <c r="G30" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>82500</v>
+        <v>280500</v>
       </c>
     </row>
     <row r="31">
@@ -2950,19 +3051,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>527</v>
+      </c>
+      <c r="F31" t="n">
         <v>543</v>
       </c>
-      <c r="F31" t="n">
-        <v>548</v>
-      </c>
       <c r="G31" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>82500</v>
+        <v>264000</v>
       </c>
     </row>
     <row r="32">
@@ -2985,19 +3086,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="F32" t="n">
         <v>804</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="33">
@@ -3023,16 +3124,16 @@
         <v>324</v>
       </c>
       <c r="F33" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G33" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3055,19 +3156,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>392</v>
+      </c>
+      <c r="F34" t="n">
         <v>406</v>
       </c>
-      <c r="F34" t="n">
-        <v>410</v>
-      </c>
       <c r="G34" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>66000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="35">
@@ -3090,19 +3191,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>526</v>
+      </c>
+      <c r="F35" t="n">
         <v>543</v>
       </c>
-      <c r="F35" t="n">
-        <v>548</v>
-      </c>
       <c r="G35" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>82500</v>
+        <v>280500</v>
       </c>
     </row>
     <row r="36">
@@ -3125,19 +3226,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>527</v>
+      </c>
+      <c r="F36" t="n">
         <v>543</v>
       </c>
-      <c r="F36" t="n">
-        <v>548</v>
-      </c>
       <c r="G36" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>82500</v>
+        <v>264000</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I421"/>
+  <dimension ref="A1:I456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18586,6 +18687,1293 @@
         <v>82500</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F422" t="n">
+        <v>2304</v>
+      </c>
+      <c r="G422" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H422" t="n">
+        <v>15</v>
+      </c>
+      <c r="I422" t="n">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F423" t="n">
+        <v>902</v>
+      </c>
+      <c r="G423" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H423" t="n">
+        <v>4</v>
+      </c>
+      <c r="I423" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F424" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F425" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" t="n">
+        <v>0</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0</v>
+      </c>
+      <c r="I425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F426" t="n">
+        <v>409</v>
+      </c>
+      <c r="G426" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H426" t="n">
+        <v>4</v>
+      </c>
+      <c r="I426" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F427" t="n">
+        <v>232</v>
+      </c>
+      <c r="G427" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H427" t="n">
+        <v>7</v>
+      </c>
+      <c r="I427" t="n">
+        <v>15750</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F428" t="n">
+        <v>824</v>
+      </c>
+      <c r="G428" t="n">
+        <v>0</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0</v>
+      </c>
+      <c r="I428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F429" t="n">
+        <v>966</v>
+      </c>
+      <c r="G429" t="n">
+        <v>0</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0</v>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F430" t="n">
+        <v>960</v>
+      </c>
+      <c r="G430" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0</v>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F431" t="n">
+        <v>360</v>
+      </c>
+      <c r="G431" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0</v>
+      </c>
+      <c r="I431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F432" t="n">
+        <v>479</v>
+      </c>
+      <c r="G432" t="n">
+        <v>0</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F433" t="n">
+        <v>484</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0</v>
+      </c>
+      <c r="I433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F434" t="n">
+        <v>343</v>
+      </c>
+      <c r="G434" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0</v>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F435" t="n">
+        <v>481</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0</v>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F436" t="n">
+        <v>483</v>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>900</v>
+      </c>
+      <c r="F437" t="n">
+        <v>371</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0</v>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>900</v>
+      </c>
+      <c r="F438" t="n">
+        <v>496</v>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>900</v>
+      </c>
+      <c r="F439" t="n">
+        <v>477</v>
+      </c>
+      <c r="G439" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0</v>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>900</v>
+      </c>
+      <c r="F440" t="n">
+        <v>694</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>900</v>
+      </c>
+      <c r="F441" t="n">
+        <v>941</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0</v>
+      </c>
+      <c r="I441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>900</v>
+      </c>
+      <c r="F442" t="n">
+        <v>954</v>
+      </c>
+      <c r="G442" t="n">
+        <v>0</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0</v>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F443" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G443" t="n">
+        <v>0</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F444" t="n">
+        <v>269</v>
+      </c>
+      <c r="G444" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H444" t="n">
+        <v>10</v>
+      </c>
+      <c r="I444" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F445" t="n">
+        <v>178</v>
+      </c>
+      <c r="G445" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H445" t="n">
+        <v>2</v>
+      </c>
+      <c r="I445" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F446" t="n">
+        <v>269</v>
+      </c>
+      <c r="G446" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H446" t="n">
+        <v>10</v>
+      </c>
+      <c r="I446" t="n">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F447" t="n">
+        <v>801</v>
+      </c>
+      <c r="G447" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3</v>
+      </c>
+      <c r="I447" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F448" t="n">
+        <v>324</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0</v>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F449" t="n">
+        <v>392</v>
+      </c>
+      <c r="G449" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H449" t="n">
+        <v>14</v>
+      </c>
+      <c r="I449" t="n">
+        <v>231000</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F450" t="n">
+        <v>526</v>
+      </c>
+      <c r="G450" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H450" t="n">
+        <v>17</v>
+      </c>
+      <c r="I450" t="n">
+        <v>280500</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F451" t="n">
+        <v>527</v>
+      </c>
+      <c r="G451" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H451" t="n">
+        <v>16</v>
+      </c>
+      <c r="I451" t="n">
+        <v>264000</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F452" t="n">
+        <v>801</v>
+      </c>
+      <c r="G452" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H452" t="n">
+        <v>3</v>
+      </c>
+      <c r="I452" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F453" t="n">
+        <v>324</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0</v>
+      </c>
+      <c r="I453" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F454" t="n">
+        <v>392</v>
+      </c>
+      <c r="G454" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H454" t="n">
+        <v>14</v>
+      </c>
+      <c r="I454" t="n">
+        <v>231000</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F455" t="n">
+        <v>526</v>
+      </c>
+      <c r="G455" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H455" t="n">
+        <v>17</v>
+      </c>
+      <c r="I455" t="n">
+        <v>280500</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F456" t="n">
+        <v>527</v>
+      </c>
+      <c r="G456" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H456" t="n">
+        <v>16</v>
+      </c>
+      <c r="I456" t="n">
+        <v>264000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,22 @@
         <v>2162750</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>81</v>
+      </c>
+      <c r="C15" t="n">
+        <v>994500</v>
+      </c>
+      <c r="D15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -678,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -753,34 +769,34 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -818,32 +834,32 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1045,19 +1061,19 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -1084,22 +1100,22 @@
         <v>3000</v>
       </c>
       <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3000</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>3000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2700</v>
       </c>
     </row>
     <row r="5">
@@ -1130,22 +1146,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
@@ -1169,22 +1185,22 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1221,16 +1237,16 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1260,16 +1276,16 @@
         <v>2700</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>900</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2000</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1300,22 +1316,22 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1339,22 +1355,22 @@
         <v>1000</v>
       </c>
       <c r="V7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>2700</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
@@ -1470,22 +1486,22 @@
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1509,22 +1525,22 @@
         <v>4000</v>
       </c>
       <c r="V9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>900</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1725,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1734,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1764,7 +1780,7 @@
         <v>1000</v>
       </c>
       <c r="V12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>900</v>
@@ -1773,13 +1789,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -1810,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1825,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
@@ -1849,7 +1865,7 @@
         <v>1000</v>
       </c>
       <c r="V13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>900</v>
@@ -1864,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
@@ -1949,6 +1965,91 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>759000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>38000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1963,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -2044,19 +2145,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2298</v>
+      </c>
+      <c r="F2" t="n">
         <v>2304</v>
       </c>
-      <c r="F2" t="n">
-        <v>2319</v>
-      </c>
       <c r="G2" t="n">
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>225000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="3">
@@ -2079,10 +2180,10 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>898</v>
+      </c>
+      <c r="F3" t="n">
         <v>902</v>
-      </c>
-      <c r="F3" t="n">
-        <v>906</v>
       </c>
       <c r="G3" t="n">
         <v>-4</v>
@@ -2176,19 +2277,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>406</v>
+      </c>
+      <c r="F6" t="n">
         <v>409</v>
       </c>
-      <c r="F6" t="n">
-        <v>413</v>
-      </c>
       <c r="G6" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>10000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="7">
@@ -2211,19 +2312,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>216</v>
+      </c>
+      <c r="F7" t="n">
         <v>232</v>
       </c>
-      <c r="F7" t="n">
-        <v>239</v>
-      </c>
       <c r="G7" t="n">
-        <v>-7</v>
+        <v>-16</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>15750</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="8">
@@ -2649,27 +2750,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V1</t>
+          <t>INQ-RFL-BLK-05</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E20" t="n">
-        <v>694</v>
+        <v>-1</v>
       </c>
       <c r="F20" t="n">
-        <v>694</v>
+        <v>-1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2684,167 +2785,167 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V2</t>
+          <t>INQ-RFL-BLU-05</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E21" t="n">
-        <v>941</v>
+        <v>267</v>
       </c>
       <c r="F21" t="n">
-        <v>941</v>
+        <v>269</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V3</t>
+          <t>INQ-RFL-PCL-01</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E22" t="n">
-        <v>954</v>
+        <v>176</v>
       </c>
       <c r="F22" t="n">
-        <v>954</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>inq Student Kit</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLK-05</t>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="E23" t="n">
-        <v>-1</v>
+        <v>267</v>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>269</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>inq writing set</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLU-05</t>
+          <t>BINQ-A5W-BLK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1000</v>
+        <v>16500</v>
       </c>
       <c r="E24" t="n">
-        <v>269</v>
+        <v>801</v>
       </c>
       <c r="F24" t="n">
-        <v>279</v>
+        <v>801</v>
       </c>
       <c r="G24" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+          <t>inq writing set</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INQ-RFL-PCL-01</t>
+          <t>BINQ-A5W-WHT</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1000</v>
+        <v>16500</v>
       </c>
       <c r="E25" t="n">
-        <v>178</v>
+        <v>322</v>
       </c>
       <c r="F25" t="n">
-        <v>180</v>
+        <v>324</v>
       </c>
       <c r="G25" t="n">
         <v>-2</v>
@@ -2853,42 +2954,42 @@
         <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>2000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inq Student Kit</t>
+          <t>inq writing set</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+          <t>BINQ-LTR-BLK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19000</v>
+        <v>16500</v>
       </c>
       <c r="E26" t="n">
-        <v>269</v>
+        <v>386</v>
       </c>
       <c r="F26" t="n">
-        <v>279</v>
+        <v>392</v>
       </c>
       <c r="G26" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>190000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="27">
@@ -2899,31 +3000,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BINQ-A5W-BLK</t>
+          <t>BINQ-LTR-ORG</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>16500</v>
       </c>
       <c r="E27" t="n">
-        <v>801</v>
+        <v>519</v>
       </c>
       <c r="F27" t="n">
-        <v>804</v>
+        <v>526</v>
       </c>
       <c r="G27" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>49500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="28">
@@ -2934,31 +3035,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BINQ-A5W-WHT</t>
+          <t>BINQ-LTR-WHT</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>324</v>
+        <v>519</v>
       </c>
       <c r="F28" t="n">
-        <v>324</v>
+        <v>527</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="29">
@@ -2969,31 +3070,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BINQ-LTR-BLK</t>
+          <t>WINQ-A5W-BLK</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>16500</v>
       </c>
       <c r="E29" t="n">
-        <v>392</v>
+        <v>801</v>
       </c>
       <c r="F29" t="n">
-        <v>406</v>
+        <v>801</v>
       </c>
       <c r="G29" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3004,31 +3105,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BINQ-LTR-ORG</t>
+          <t>WINQ-A5W-WHT</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>16500</v>
       </c>
       <c r="E30" t="n">
-        <v>526</v>
+        <v>322</v>
       </c>
       <c r="F30" t="n">
-        <v>543</v>
+        <v>324</v>
       </c>
       <c r="G30" t="n">
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>280500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="31">
@@ -3039,31 +3140,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BINQ-LTR-WHT</t>
+          <t>WINQ-LTR-BLK</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>16500</v>
       </c>
       <c r="E31" t="n">
-        <v>527</v>
+        <v>386</v>
       </c>
       <c r="F31" t="n">
-        <v>543</v>
+        <v>392</v>
       </c>
       <c r="G31" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="H31" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>264000</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="32">
@@ -3074,31 +3175,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WINQ-A5W-BLK</t>
+          <t>WINQ-LTR-ORG</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>16500</v>
       </c>
       <c r="E32" t="n">
-        <v>801</v>
+        <v>519</v>
       </c>
       <c r="F32" t="n">
-        <v>804</v>
+        <v>526</v>
       </c>
       <c r="G32" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>49500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="33">
@@ -3109,136 +3210,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WINQ-A5W-WHT</t>
+          <t>WINQ-LTR-WHT</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>324</v>
+        <v>519</v>
       </c>
       <c r="F33" t="n">
-        <v>324</v>
+        <v>527</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Black</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-BLK</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E34" t="n">
-        <v>392</v>
-      </c>
-      <c r="F34" t="n">
-        <v>406</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H34" t="n">
-        <v>14</v>
-      </c>
-      <c r="I34" t="n">
-        <v>231000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-ORG</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E35" t="n">
-        <v>526</v>
-      </c>
-      <c r="F35" t="n">
-        <v>543</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-17</v>
-      </c>
-      <c r="H35" t="n">
-        <v>17</v>
-      </c>
-      <c r="I35" t="n">
-        <v>280500</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / White</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-WHT</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E36" t="n">
-        <v>527</v>
-      </c>
-      <c r="F36" t="n">
-        <v>543</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H36" t="n">
-        <v>16</v>
-      </c>
-      <c r="I36" t="n">
-        <v>264000</v>
+        <v>132000</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I456"/>
+  <dimension ref="A1:I488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19974,6 +19970,1182 @@
         <v>264000</v>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F457" t="n">
+        <v>2298</v>
+      </c>
+      <c r="G457" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H457" t="n">
+        <v>6</v>
+      </c>
+      <c r="I457" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F458" t="n">
+        <v>898</v>
+      </c>
+      <c r="G458" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H458" t="n">
+        <v>4</v>
+      </c>
+      <c r="I458" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F459" t="n">
+        <v>0</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0</v>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F460" t="n">
+        <v>0</v>
+      </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F461" t="n">
+        <v>406</v>
+      </c>
+      <c r="G461" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H461" t="n">
+        <v>3</v>
+      </c>
+      <c r="I461" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F462" t="n">
+        <v>216</v>
+      </c>
+      <c r="G462" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H462" t="n">
+        <v>16</v>
+      </c>
+      <c r="I462" t="n">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F463" t="n">
+        <v>824</v>
+      </c>
+      <c r="G463" t="n">
+        <v>0</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0</v>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F464" t="n">
+        <v>966</v>
+      </c>
+      <c r="G464" t="n">
+        <v>0</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F465" t="n">
+        <v>960</v>
+      </c>
+      <c r="G465" t="n">
+        <v>0</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F466" t="n">
+        <v>360</v>
+      </c>
+      <c r="G466" t="n">
+        <v>0</v>
+      </c>
+      <c r="H466" t="n">
+        <v>0</v>
+      </c>
+      <c r="I466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F467" t="n">
+        <v>479</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0</v>
+      </c>
+      <c r="H467" t="n">
+        <v>0</v>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F468" t="n">
+        <v>484</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0</v>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F469" t="n">
+        <v>343</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F470" t="n">
+        <v>481</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F471" t="n">
+        <v>483</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>900</v>
+      </c>
+      <c r="F472" t="n">
+        <v>371</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>900</v>
+      </c>
+      <c r="F473" t="n">
+        <v>496</v>
+      </c>
+      <c r="G473" t="n">
+        <v>0</v>
+      </c>
+      <c r="H473" t="n">
+        <v>0</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>900</v>
+      </c>
+      <c r="F474" t="n">
+        <v>477</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>0</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F475" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G475" t="n">
+        <v>0</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F476" t="n">
+        <v>267</v>
+      </c>
+      <c r="G476" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H476" t="n">
+        <v>2</v>
+      </c>
+      <c r="I476" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F477" t="n">
+        <v>176</v>
+      </c>
+      <c r="G477" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H477" t="n">
+        <v>2</v>
+      </c>
+      <c r="I477" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F478" t="n">
+        <v>267</v>
+      </c>
+      <c r="G478" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H478" t="n">
+        <v>2</v>
+      </c>
+      <c r="I478" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F479" t="n">
+        <v>801</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F480" t="n">
+        <v>322</v>
+      </c>
+      <c r="G480" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H480" t="n">
+        <v>2</v>
+      </c>
+      <c r="I480" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F481" t="n">
+        <v>386</v>
+      </c>
+      <c r="G481" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H481" t="n">
+        <v>6</v>
+      </c>
+      <c r="I481" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F482" t="n">
+        <v>519</v>
+      </c>
+      <c r="G482" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H482" t="n">
+        <v>7</v>
+      </c>
+      <c r="I482" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F483" t="n">
+        <v>519</v>
+      </c>
+      <c r="G483" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H483" t="n">
+        <v>8</v>
+      </c>
+      <c r="I483" t="n">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F484" t="n">
+        <v>801</v>
+      </c>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F485" t="n">
+        <v>322</v>
+      </c>
+      <c r="G485" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H485" t="n">
+        <v>2</v>
+      </c>
+      <c r="I485" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F486" t="n">
+        <v>386</v>
+      </c>
+      <c r="G486" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H486" t="n">
+        <v>6</v>
+      </c>
+      <c r="I486" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F487" t="n">
+        <v>519</v>
+      </c>
+      <c r="G487" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H487" t="n">
+        <v>7</v>
+      </c>
+      <c r="I487" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F488" t="n">
+        <v>519</v>
+      </c>
+      <c r="G488" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H488" t="n">
+        <v>8</v>
+      </c>
+      <c r="I488" t="n">
+        <v>132000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -680,6 +680,22 @@
         <v>994500</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>36</v>
+      </c>
+      <c r="C16" t="n">
+        <v>320750</v>
+      </c>
+      <c r="D16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -694,36 +710,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="55" customWidth="1" min="27" max="27"/>
+    <col width="29" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,132 +750,132 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>inq writing set (Units)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>inq writing set (Rev USD)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -955,10 +971,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -973,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -991,28 +1007,28 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>231000</v>
+        <v>45000</v>
       </c>
       <c r="P3" t="n">
-        <v>45000</v>
+        <v>19000</v>
       </c>
       <c r="Q3" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="R3" t="n">
         <v>6750</v>
       </c>
       <c r="S3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="n">
         <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1030,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="4">
@@ -1040,22 +1056,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1064,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1073,28 +1089,28 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>198000</v>
+        <v>45000</v>
       </c>
       <c r="P4" t="n">
-        <v>45000</v>
+        <v>76000</v>
       </c>
       <c r="Q4" t="n">
-        <v>76000</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="U4" t="n">
         <v>3000</v>
@@ -1103,19 +1119,19 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="5">
@@ -1125,10 +1141,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1140,11 +1156,11 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1155,34 +1171,34 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O5" t="n">
-        <v>528000</v>
+        <v>90000</v>
       </c>
       <c r="P5" t="n">
-        <v>90000</v>
+        <v>19000</v>
       </c>
       <c r="Q5" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="R5" t="n">
         <v>2250</v>
       </c>
       <c r="S5" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1194,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>528000</v>
       </c>
     </row>
     <row r="6">
@@ -1210,82 +1226,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>6</v>
       </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
-        <v>396000</v>
+        <v>120000</v>
       </c>
       <c r="P6" t="n">
-        <v>120000</v>
+        <v>19000</v>
       </c>
       <c r="Q6" t="n">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="R6" t="n">
         <v>13500</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="U6" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
+        <v>900</v>
+      </c>
+      <c r="X6" t="n">
         <v>2700</v>
       </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="7">
@@ -1295,82 +1311,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
-        <v>44</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="O7" t="n">
-        <v>1782000</v>
+        <v>465000</v>
       </c>
       <c r="P7" t="n">
-        <v>465000</v>
+        <v>152000</v>
       </c>
       <c r="Q7" t="n">
-        <v>152000</v>
+        <v>10000</v>
       </c>
       <c r="R7" t="n">
         <v>4500</v>
       </c>
       <c r="S7" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="T7" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="U7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2700</v>
       </c>
-      <c r="X7" t="n">
-        <v>44000</v>
-      </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2000</v>
+        <v>1782000</v>
       </c>
     </row>
     <row r="8">
@@ -1380,25 +1396,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1416,16 +1432,16 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O8" t="n">
-        <v>594000</v>
+        <v>210000</v>
       </c>
       <c r="P8" t="n">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="Q8" t="n">
-        <v>95000</v>
+        <v>5000</v>
       </c>
       <c r="R8" t="n">
         <v>2250</v>
@@ -1434,10 +1450,10 @@
         <v>5000</v>
       </c>
       <c r="T8" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="U8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1455,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="9">
@@ -1465,82 +1481,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O9" t="n">
-        <v>792000</v>
+        <v>195000</v>
       </c>
       <c r="P9" t="n">
-        <v>195000</v>
+        <v>114000</v>
       </c>
       <c r="Q9" t="n">
-        <v>114000</v>
+        <v>20000</v>
       </c>
       <c r="R9" t="n">
         <v>15750</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="T9" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="U9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>900</v>
       </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>792000</v>
       </c>
     </row>
     <row r="10">
@@ -1550,35 +1566,35 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -1586,38 +1602,38 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="O10" t="n">
-        <v>2359500</v>
+        <v>825000</v>
       </c>
       <c r="P10" t="n">
-        <v>825000</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="R10" t="n">
         <v>4500</v>
       </c>
       <c r="S10" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>3600</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
@@ -1625,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2359500</v>
       </c>
     </row>
     <row r="11">
@@ -1635,25 +1651,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1671,28 +1687,28 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>247500</v>
+        <v>30000</v>
       </c>
       <c r="P11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="R11" t="n">
         <v>2250</v>
       </c>
       <c r="S11" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1710,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="12">
@@ -1720,25 +1736,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1747,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1756,28 +1772,28 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
-        <v>297000</v>
+        <v>75000</v>
       </c>
       <c r="P12" t="n">
-        <v>75000</v>
+        <v>57000</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>2500</v>
       </c>
       <c r="R12" t="n">
         <v>2250</v>
       </c>
       <c r="S12" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="T12" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="U12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1786,16 +1802,16 @@
         <v>900</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="Y12" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="13">
@@ -1805,82 +1821,82 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>528000</v>
+        <v>90000</v>
       </c>
       <c r="P13" t="n">
-        <v>90000</v>
+        <v>228000</v>
       </c>
       <c r="Q13" t="n">
-        <v>228000</v>
+        <v>10000</v>
       </c>
       <c r="R13" t="n">
         <v>4500</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="T13" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="U13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>900</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2000</v>
+        <v>528000</v>
       </c>
     </row>
     <row r="14">
@@ -1890,25 +1906,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1926,16 +1942,16 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>1650000</v>
+        <v>285000</v>
       </c>
       <c r="P14" t="n">
-        <v>285000</v>
+        <v>190000</v>
       </c>
       <c r="Q14" t="n">
-        <v>190000</v>
+        <v>10000</v>
       </c>
       <c r="R14" t="n">
         <v>15750</v>
@@ -1944,10 +1960,10 @@
         <v>10000</v>
       </c>
       <c r="T14" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="U14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1965,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1650000</v>
       </c>
     </row>
     <row r="15">
@@ -1975,25 +1991,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2011,45 +2027,130 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O15" t="n">
-        <v>759000</v>
+        <v>150000</v>
       </c>
       <c r="P15" t="n">
-        <v>150000</v>
+        <v>38000</v>
       </c>
       <c r="Q15" t="n">
-        <v>38000</v>
+        <v>7500</v>
       </c>
       <c r="R15" t="n">
         <v>36000</v>
       </c>
       <c r="S15" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="n">
         <v>2000</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>759000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>195000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T16" t="n">
         <v>2000</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="U16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2064,11 +2165,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2145,19 +2246,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2291</v>
+      </c>
+      <c r="F2" t="n">
         <v>2298</v>
       </c>
-      <c r="F2" t="n">
-        <v>2304</v>
-      </c>
       <c r="G2" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>90000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="3">
@@ -2180,19 +2281,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>892</v>
+      </c>
+      <c r="F3" t="n">
         <v>898</v>
       </c>
-      <c r="F3" t="n">
-        <v>902</v>
-      </c>
       <c r="G3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>60000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="4">
@@ -2277,19 +2378,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>400</v>
+      </c>
+      <c r="F6" t="n">
         <v>406</v>
       </c>
-      <c r="F6" t="n">
-        <v>409</v>
-      </c>
       <c r="G6" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="7">
@@ -2312,19 +2413,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>213</v>
+      </c>
+      <c r="F7" t="n">
         <v>216</v>
       </c>
-      <c r="F7" t="n">
-        <v>232</v>
-      </c>
       <c r="G7" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>36000</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -2347,19 +2448,19 @@
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="F8" t="n">
         <v>824</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -2645,7 +2746,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2655,21 +2756,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V1</t>
+          <t>INQ-A5-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>371</v>
-      </c>
-      <c r="F17" t="n">
-        <v>371</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2680,7 +2777,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2690,21 +2787,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V2</t>
+          <t>INQ-A5-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>496</v>
-      </c>
-      <c r="F18" t="n">
-        <v>496</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2715,7 +2808,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2725,21 +2818,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V3</t>
+          <t>INQ-A5-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>477</v>
-      </c>
-      <c r="F19" t="n">
-        <v>477</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2802,19 +2891,19 @@
         <v>1000</v>
       </c>
       <c r="E21" t="n">
+        <v>262</v>
+      </c>
+      <c r="F21" t="n">
         <v>267</v>
       </c>
-      <c r="F21" t="n">
-        <v>269</v>
-      </c>
       <c r="G21" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="22">
@@ -2837,10 +2926,10 @@
         <v>1000</v>
       </c>
       <c r="E22" t="n">
+        <v>174</v>
+      </c>
+      <c r="F22" t="n">
         <v>176</v>
-      </c>
-      <c r="F22" t="n">
-        <v>178</v>
       </c>
       <c r="G22" t="n">
         <v>-2</v>
@@ -2872,369 +2961,19 @@
         <v>19000</v>
       </c>
       <c r="E23" t="n">
+        <v>262</v>
+      </c>
+      <c r="F23" t="n">
         <v>267</v>
       </c>
-      <c r="F23" t="n">
-        <v>269</v>
-      </c>
       <c r="G23" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BINQ-A5W-BLK</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E24" t="n">
-        <v>801</v>
-      </c>
-      <c r="F24" t="n">
-        <v>801</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BINQ-A5W-WHT</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E25" t="n">
-        <v>322</v>
-      </c>
-      <c r="F25" t="n">
-        <v>324</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-BLK</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E26" t="n">
-        <v>386</v>
-      </c>
-      <c r="F26" t="n">
-        <v>392</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>99000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-ORG</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E27" t="n">
-        <v>519</v>
-      </c>
-      <c r="F27" t="n">
-        <v>526</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H27" t="n">
-        <v>7</v>
-      </c>
-      <c r="I27" t="n">
-        <v>115500</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-WHT</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E28" t="n">
-        <v>519</v>
-      </c>
-      <c r="F28" t="n">
-        <v>527</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>WINQ-A5W-BLK</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E29" t="n">
-        <v>801</v>
-      </c>
-      <c r="F29" t="n">
-        <v>801</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>WINQ-A5W-WHT</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E30" t="n">
-        <v>322</v>
-      </c>
-      <c r="F30" t="n">
-        <v>324</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" t="n">
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Black</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-BLK</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E31" t="n">
-        <v>386</v>
-      </c>
-      <c r="F31" t="n">
-        <v>392</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>99000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-ORG</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E32" t="n">
-        <v>519</v>
-      </c>
-      <c r="F32" t="n">
-        <v>526</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>115500</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / White</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-WHT</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E33" t="n">
-        <v>519</v>
-      </c>
-      <c r="F33" t="n">
-        <v>527</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" t="n">
-        <v>132000</v>
+        <v>95000</v>
       </c>
     </row>
   </sheetData>
@@ -3248,7 +2987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I488"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21146,6 +20885,806 @@
         <v>132000</v>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F489" t="n">
+        <v>2291</v>
+      </c>
+      <c r="G489" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H489" t="n">
+        <v>7</v>
+      </c>
+      <c r="I489" t="n">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F490" t="n">
+        <v>892</v>
+      </c>
+      <c r="G490" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H490" t="n">
+        <v>6</v>
+      </c>
+      <c r="I490" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F491" t="n">
+        <v>0</v>
+      </c>
+      <c r="G491" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0</v>
+      </c>
+      <c r="G492" t="n">
+        <v>0</v>
+      </c>
+      <c r="H492" t="n">
+        <v>0</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F493" t="n">
+        <v>400</v>
+      </c>
+      <c r="G493" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H493" t="n">
+        <v>6</v>
+      </c>
+      <c r="I493" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F494" t="n">
+        <v>213</v>
+      </c>
+      <c r="G494" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H494" t="n">
+        <v>3</v>
+      </c>
+      <c r="I494" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F495" t="n">
+        <v>822</v>
+      </c>
+      <c r="G495" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H495" t="n">
+        <v>2</v>
+      </c>
+      <c r="I495" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F496" t="n">
+        <v>966</v>
+      </c>
+      <c r="G496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" t="n">
+        <v>0</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F497" t="n">
+        <v>960</v>
+      </c>
+      <c r="G497" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0</v>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F498" t="n">
+        <v>360</v>
+      </c>
+      <c r="G498" t="n">
+        <v>0</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F499" t="n">
+        <v>479</v>
+      </c>
+      <c r="G499" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F500" t="n">
+        <v>484</v>
+      </c>
+      <c r="G500" t="n">
+        <v>0</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F501" t="n">
+        <v>343</v>
+      </c>
+      <c r="G501" t="n">
+        <v>0</v>
+      </c>
+      <c r="H501" t="n">
+        <v>0</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F502" t="n">
+        <v>481</v>
+      </c>
+      <c r="G502" t="n">
+        <v>0</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F503" t="n">
+        <v>483</v>
+      </c>
+      <c r="G503" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" t="n">
+        <v>0</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>900</v>
+      </c>
+      <c r="F504" t="n">
+        <v>694</v>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="n">
+        <v>0</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>900</v>
+      </c>
+      <c r="F505" t="n">
+        <v>941</v>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="n">
+        <v>0</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>900</v>
+      </c>
+      <c r="F506" t="n">
+        <v>954</v>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="n">
+        <v>0</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F507" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G507" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F508" t="n">
+        <v>262</v>
+      </c>
+      <c r="G508" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>5</v>
+      </c>
+      <c r="I508" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F509" t="n">
+        <v>174</v>
+      </c>
+      <c r="G509" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H509" t="n">
+        <v>2</v>
+      </c>
+      <c r="I509" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F510" t="n">
+        <v>262</v>
+      </c>
+      <c r="G510" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H510" t="n">
+        <v>5</v>
+      </c>
+      <c r="I510" t="n">
+        <v>95000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -696,6 +696,22 @@
         <v>320750</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>127</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1063300</v>
+      </c>
+      <c r="D17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,17 +726,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -728,12 +744,12 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
     <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
     <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
@@ -755,54 +771,54 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
@@ -820,52 +836,52 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -974,13 +990,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -989,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1013,22 +1029,22 @@
         <v>45000</v>
       </c>
       <c r="P3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19000</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>2500</v>
       </c>
-      <c r="R3" t="n">
-        <v>6750</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1000</v>
-      </c>
       <c r="T3" t="n">
         <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1059,22 +1075,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1098,34 +1114,34 @@
         <v>45000</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>76000</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S4" t="n">
         <v>2500</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4000</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
       </c>
       <c r="U4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>3000</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2700</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1165,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1183,17 +1199,17 @@
         <v>90000</v>
       </c>
       <c r="P5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="Q5" t="n">
         <v>19000</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S5" t="n">
         <v>2500</v>
       </c>
-      <c r="R5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1000</v>
-      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -1204,13 +1220,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1229,34 +1245,34 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1268,34 +1284,34 @@
         <v>120000</v>
       </c>
       <c r="P6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="Q6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S6" t="n">
         <v>5000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>13500</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1000</v>
       </c>
       <c r="T6" t="n">
         <v>3000</v>
       </c>
       <c r="U6" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>900</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1314,34 +1330,34 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
         <v>44</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1353,34 +1369,34 @@
         <v>465000</v>
       </c>
       <c r="P7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Q7" t="n">
         <v>152000</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>10000</v>
       </c>
-      <c r="R7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U7" t="n">
         <v>8000</v>
       </c>
-      <c r="T7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X7" t="n">
         <v>44000</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2700</v>
-      </c>
       <c r="Y7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1399,22 +1415,22 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1438,13 +1454,13 @@
         <v>210000</v>
       </c>
       <c r="P8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="Q8" t="n">
         <v>95000</v>
       </c>
-      <c r="Q8" t="n">
-        <v>5000</v>
-      </c>
       <c r="R8" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>5000</v>
@@ -1453,7 +1469,7 @@
         <v>3000</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1484,34 +1500,34 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1523,34 +1539,34 @@
         <v>195000</v>
       </c>
       <c r="P9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="Q9" t="n">
         <v>114000</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>20000</v>
-      </c>
-      <c r="R9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="S9" t="n">
-        <v>6000</v>
       </c>
       <c r="T9" t="n">
         <v>4000</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="V9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1569,16 +1585,16 @@
         <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1587,13 +1603,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1608,17 +1624,17 @@
         <v>825000</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>2500</v>
       </c>
-      <c r="R10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
         <v>1000</v>
       </c>
@@ -1626,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1654,16 +1670,16 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1693,16 +1709,16 @@
         <v>30000</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2500</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2250</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>1000</v>
@@ -1739,31 +1755,31 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1778,34 +1794,34 @@
         <v>75000</v>
       </c>
       <c r="P12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="Q12" t="n">
         <v>57000</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>2500</v>
       </c>
-      <c r="R12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U12" t="n">
         <v>3000</v>
       </c>
-      <c r="T12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>900</v>
-      </c>
-      <c r="X12" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1824,34 +1840,34 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1863,34 +1879,34 @@
         <v>90000</v>
       </c>
       <c r="P13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Q13" t="n">
         <v>228000</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>10000</v>
       </c>
-      <c r="R13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U13" t="n">
         <v>12000</v>
       </c>
-      <c r="T13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1909,22 +1925,22 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1948,13 +1964,13 @@
         <v>285000</v>
       </c>
       <c r="P14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="Q14" t="n">
         <v>190000</v>
       </c>
-      <c r="Q14" t="n">
-        <v>10000</v>
-      </c>
       <c r="R14" t="n">
-        <v>15750</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>10000</v>
@@ -1963,7 +1979,7 @@
         <v>2000</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1994,22 +2010,22 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2033,22 +2049,22 @@
         <v>150000</v>
       </c>
       <c r="P15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="Q15" t="n">
         <v>38000</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>7500</v>
-      </c>
-      <c r="R15" t="n">
-        <v>36000</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2000</v>
       </c>
       <c r="T15" t="n">
         <v>2000</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2079,22 +2095,22 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2118,39 +2134,124 @@
         <v>195000</v>
       </c>
       <c r="P16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="Q16" t="n">
         <v>95000</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S16" t="n">
         <v>15000</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6750</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5000</v>
       </c>
       <c r="T16" t="n">
         <v>2000</v>
       </c>
       <c r="U16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>61</v>
+      </c>
+      <c r="C17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>915000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>38000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T17" t="n">
         <v>2000</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="U17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2165,11 +2266,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2246,19 +2347,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2232</v>
+      </c>
+      <c r="F2" t="n">
         <v>2291</v>
       </c>
-      <c r="F2" t="n">
-        <v>2298</v>
-      </c>
       <c r="G2" t="n">
-        <v>-7</v>
+        <v>-59</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="I2" t="n">
-        <v>105000</v>
+        <v>885000</v>
       </c>
     </row>
     <row r="3">
@@ -2281,19 +2382,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>890</v>
+      </c>
+      <c r="F3" t="n">
         <v>892</v>
       </c>
-      <c r="F3" t="n">
-        <v>898</v>
-      </c>
       <c r="G3" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -2378,10 +2479,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>394</v>
+      </c>
+      <c r="F6" t="n">
         <v>400</v>
-      </c>
-      <c r="F6" t="n">
-        <v>406</v>
       </c>
       <c r="G6" t="n">
         <v>-6</v>
@@ -2413,19 +2514,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>183</v>
+      </c>
+      <c r="F7" t="n">
         <v>213</v>
       </c>
-      <c r="F7" t="n">
-        <v>216</v>
-      </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>-30</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="8">
@@ -2451,16 +2552,16 @@
         <v>822</v>
       </c>
       <c r="F8" t="n">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2518,19 +2619,19 @@
         <v>1000</v>
       </c>
       <c r="E10" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="F10" t="n">
         <v>960</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="11">
@@ -2553,19 +2654,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F11" t="n">
         <v>360</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -2658,19 +2759,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F14" t="n">
         <v>343</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -2746,7 +2847,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2756,14 +2857,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V1</t>
+          <t>INQ-A5-SP01-BLK-V1</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>694</v>
+        <v>371</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -2777,7 +2878,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2787,14 +2888,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V2</t>
+          <t>INQ-A5-SP01-BLK-V2</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>941</v>
+        <v>494</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -2808,7 +2909,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2818,14 +2919,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V3</t>
+          <t>INQ-A5-SP01-BLK-V3</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>954</v>
+        <v>477</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -2839,141 +2940,556 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLK-05</t>
+          <t>INQ-A5-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E20" t="n">
+        <v>693</v>
+      </c>
+      <c r="F20" t="n">
+        <v>694</v>
+      </c>
+      <c r="G20" t="n">
         <v>-1</v>
       </c>
-      <c r="F20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLU-05</t>
+          <t>INQ-A5-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>262</v>
+        <v>941</v>
       </c>
       <c r="F21" t="n">
-        <v>267</v>
+        <v>941</v>
       </c>
       <c r="G21" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INQ-RFL-PCL-01</t>
+          <t>INQ-A5-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E22" t="n">
-        <v>174</v>
+        <v>953</v>
       </c>
       <c r="F22" t="n">
-        <v>176</v>
+        <v>954</v>
       </c>
       <c r="G22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>2000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>260</v>
+      </c>
+      <c r="F24" t="n">
+        <v>262</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>172</v>
+      </c>
+      <c r="F25" t="n">
+        <v>174</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>inq Student Kit</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>BINQ-STUDENTKIT-LTR-MX1</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D26" t="n">
         <v>19000</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E26" t="n">
+        <v>260</v>
+      </c>
+      <c r="F26" t="n">
         <v>262</v>
       </c>
-      <c r="F23" t="n">
-        <v>267</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>95000</v>
+      <c r="G26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E27" t="n">
+        <v>759</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>322</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E29" t="n">
+        <v>364</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E30" t="n">
+        <v>488</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E31" t="n">
+        <v>488</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E32" t="n">
+        <v>759</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E33" t="n">
+        <v>322</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E34" t="n">
+        <v>364</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E35" t="n">
+        <v>488</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E36" t="n">
+        <v>488</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I510"/>
+  <dimension ref="A1:I545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21685,6 +22201,1267 @@
         <v>95000</v>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F511" t="n">
+        <v>2232</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H511" t="n">
+        <v>59</v>
+      </c>
+      <c r="I511" t="n">
+        <v>885000</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F512" t="n">
+        <v>890</v>
+      </c>
+      <c r="G512" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H512" t="n">
+        <v>2</v>
+      </c>
+      <c r="I512" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" t="n">
+        <v>0</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+      <c r="E514" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0</v>
+      </c>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F515" t="n">
+        <v>394</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H515" t="n">
+        <v>6</v>
+      </c>
+      <c r="I515" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F516" t="n">
+        <v>183</v>
+      </c>
+      <c r="G516" t="n">
+        <v>-30</v>
+      </c>
+      <c r="H516" t="n">
+        <v>30</v>
+      </c>
+      <c r="I516" t="n">
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F517" t="n">
+        <v>822</v>
+      </c>
+      <c r="G517" t="n">
+        <v>0</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F518" t="n">
+        <v>966</v>
+      </c>
+      <c r="G518" t="n">
+        <v>0</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F519" t="n">
+        <v>940</v>
+      </c>
+      <c r="G519" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H519" t="n">
+        <v>20</v>
+      </c>
+      <c r="I519" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F520" t="n">
+        <v>359</v>
+      </c>
+      <c r="G520" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H520" t="n">
+        <v>1</v>
+      </c>
+      <c r="I520" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F521" t="n">
+        <v>479</v>
+      </c>
+      <c r="G521" t="n">
+        <v>0</v>
+      </c>
+      <c r="H521" t="n">
+        <v>0</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F522" t="n">
+        <v>484</v>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F523" t="n">
+        <v>342</v>
+      </c>
+      <c r="G523" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H523" t="n">
+        <v>1</v>
+      </c>
+      <c r="I523" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F524" t="n">
+        <v>481</v>
+      </c>
+      <c r="G524" t="n">
+        <v>0</v>
+      </c>
+      <c r="H524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F525" t="n">
+        <v>483</v>
+      </c>
+      <c r="G525" t="n">
+        <v>0</v>
+      </c>
+      <c r="H525" t="n">
+        <v>0</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>900</v>
+      </c>
+      <c r="F526" t="n">
+        <v>371</v>
+      </c>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>900</v>
+      </c>
+      <c r="F527" t="n">
+        <v>494</v>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>900</v>
+      </c>
+      <c r="F528" t="n">
+        <v>477</v>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>900</v>
+      </c>
+      <c r="F529" t="n">
+        <v>693</v>
+      </c>
+      <c r="G529" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H529" t="n">
+        <v>1</v>
+      </c>
+      <c r="I529" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>900</v>
+      </c>
+      <c r="F530" t="n">
+        <v>941</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" t="n">
+        <v>0</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>900</v>
+      </c>
+      <c r="F531" t="n">
+        <v>953</v>
+      </c>
+      <c r="G531" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H531" t="n">
+        <v>1</v>
+      </c>
+      <c r="I531" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F532" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G532" t="n">
+        <v>0</v>
+      </c>
+      <c r="H532" t="n">
+        <v>0</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F533" t="n">
+        <v>260</v>
+      </c>
+      <c r="G533" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H533" t="n">
+        <v>2</v>
+      </c>
+      <c r="I533" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F534" t="n">
+        <v>172</v>
+      </c>
+      <c r="G534" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H534" t="n">
+        <v>2</v>
+      </c>
+      <c r="I534" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F535" t="n">
+        <v>260</v>
+      </c>
+      <c r="G535" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H535" t="n">
+        <v>2</v>
+      </c>
+      <c r="I535" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F536" t="n">
+        <v>759</v>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="n">
+        <v>0</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F537" t="n">
+        <v>322</v>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="n">
+        <v>0</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F538" t="n">
+        <v>364</v>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="n">
+        <v>0</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F539" t="n">
+        <v>488</v>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="n">
+        <v>0</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F540" t="n">
+        <v>488</v>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="n">
+        <v>0</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F541" t="n">
+        <v>759</v>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="n">
+        <v>0</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F542" t="n">
+        <v>322</v>
+      </c>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="n">
+        <v>0</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F543" t="n">
+        <v>364</v>
+      </c>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="n">
+        <v>0</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F544" t="n">
+        <v>488</v>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F545" t="n">
+        <v>488</v>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="n">
+        <v>0</v>
+      </c>
+      <c r="I545" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -712,6 +712,22 @@
         <v>1063300</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>588250</v>
+      </c>
+      <c r="D18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -726,12 +742,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
@@ -742,9 +758,9 @@
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="27" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="55" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
@@ -755,7 +771,7 @@
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="29" customWidth="1" min="27" max="27"/>
+    <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -766,132 +782,132 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Units)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Rev USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -987,7 +1003,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -996,10 +1012,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1023,22 +1039,22 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>231000</v>
+      </c>
+      <c r="P3" t="n">
         <v>45000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6750</v>
       </c>
       <c r="Q3" t="n">
         <v>19000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>2500</v>
+        <v>6750</v>
       </c>
       <c r="T3" t="n">
         <v>1000</v>
@@ -1062,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1072,19 +1088,19 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -1096,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -1108,22 +1124,22 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
+        <v>198000</v>
+      </c>
+      <c r="P4" t="n">
         <v>45000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>76000</v>
       </c>
       <c r="R4" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="S4" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
@@ -1135,19 +1151,19 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>3000</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2700</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>198000</v>
       </c>
     </row>
     <row r="5">
@@ -1157,10 +1173,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1181,34 +1197,34 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P5" t="n">
         <v>90000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2250</v>
       </c>
       <c r="Q5" t="n">
         <v>19000</v>
       </c>
       <c r="R5" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="S5" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1220,19 +1236,19 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>528000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1242,10 +1258,10 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
         <v>8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -1254,7 +1270,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -1263,37 +1279,37 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>24</v>
-      </c>
       <c r="O6" t="n">
+        <v>396000</v>
+      </c>
+      <c r="P6" t="n">
         <v>120000</v>
-      </c>
-      <c r="P6" t="n">
-        <v>13500</v>
       </c>
       <c r="Q6" t="n">
         <v>19000</v>
       </c>
       <c r="R6" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>13500</v>
       </c>
       <c r="T6" t="n">
         <v>3000</v>
@@ -1302,22 +1318,22 @@
         <v>1000</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>2700</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>900</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>396000</v>
       </c>
     </row>
     <row r="7">
@@ -1327,19 +1343,19 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C7" t="n">
         <v>31</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1348,37 +1364,37 @@
         <v>8</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>44</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>1782000</v>
+      </c>
+      <c r="P7" t="n">
         <v>465000</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4500</v>
       </c>
       <c r="Q7" t="n">
         <v>152000</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="S7" t="n">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="T7" t="n">
         <v>1000</v>
@@ -1387,22 +1403,22 @@
         <v>8000</v>
       </c>
       <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
         <v>2700</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>2000</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>44000</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1782000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1412,19 +1428,19 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n">
         <v>14</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -1448,22 +1464,22 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>594000</v>
+      </c>
+      <c r="P8" t="n">
         <v>210000</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2250</v>
       </c>
       <c r="Q8" t="n">
         <v>95000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>5000</v>
+        <v>2250</v>
       </c>
       <c r="T8" t="n">
         <v>3000</v>
@@ -1487,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>594000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1497,19 +1513,19 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" t="n">
         <v>13</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -1518,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1530,25 +1546,25 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>792000</v>
+      </c>
+      <c r="P9" t="n">
         <v>195000</v>
-      </c>
-      <c r="P9" t="n">
-        <v>15750</v>
       </c>
       <c r="Q9" t="n">
         <v>114000</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>15750</v>
       </c>
       <c r="T9" t="n">
         <v>4000</v>
@@ -1557,11 +1573,11 @@
         <v>6000</v>
       </c>
       <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>900</v>
       </c>
-      <c r="W9" t="n">
-        <v>1000</v>
-      </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
@@ -1569,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>792000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1582,19 +1598,19 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>143</v>
+      </c>
+      <c r="C10" t="n">
         <v>55</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1603,11 +1619,11 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
@@ -1618,23 +1634,23 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2359500</v>
+      </c>
+      <c r="P10" t="n">
         <v>825000</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S10" t="n">
         <v>4500</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2500</v>
-      </c>
       <c r="T10" t="n">
         <v>1000</v>
       </c>
@@ -1642,11 +1658,11 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>3600</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -1657,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2359500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1667,16 +1683,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1703,23 +1719,23 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>247500</v>
+      </c>
+      <c r="P11" t="n">
         <v>30000</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S11" t="n">
         <v>2250</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2500</v>
-      </c>
       <c r="T11" t="n">
         <v>1000</v>
       </c>
@@ -1742,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>247500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1752,16 +1768,16 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1773,37 +1789,37 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18</v>
-      </c>
       <c r="O12" t="n">
+        <v>297000</v>
+      </c>
+      <c r="P12" t="n">
         <v>75000</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2250</v>
       </c>
       <c r="Q12" t="n">
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S12" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="T12" t="n">
         <v>1000</v>
@@ -1812,22 +1828,22 @@
         <v>3000</v>
       </c>
       <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>900</v>
       </c>
-      <c r="W12" t="n">
-        <v>1000</v>
-      </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>900</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>297000</v>
       </c>
     </row>
     <row r="13">
@@ -1837,19 +1853,19 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1858,14 +1874,14 @@
         <v>12</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -1873,22 +1889,22 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P13" t="n">
         <v>90000</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4500</v>
       </c>
       <c r="Q13" t="n">
         <v>228000</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="T13" t="n">
         <v>1000</v>
@@ -1897,14 +1913,14 @@
         <v>12000</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>900</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>2000</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
@@ -1912,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>528000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1922,19 +1938,19 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
         <v>19</v>
-      </c>
-      <c r="C14" t="n">
-        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -1958,22 +1974,22 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="P14" t="n">
         <v>285000</v>
-      </c>
-      <c r="P14" t="n">
-        <v>15750</v>
       </c>
       <c r="Q14" t="n">
         <v>190000</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="S14" t="n">
-        <v>10000</v>
+        <v>15750</v>
       </c>
       <c r="T14" t="n">
         <v>2000</v>
@@ -1997,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1650000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2007,19 +2023,19 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>46</v>
+      </c>
+      <c r="C15" t="n">
         <v>10</v>
-      </c>
-      <c r="C15" t="n">
-        <v>16</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -2043,22 +2059,22 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>759000</v>
+      </c>
+      <c r="P15" t="n">
         <v>150000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>36000</v>
       </c>
       <c r="Q15" t="n">
         <v>38000</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="S15" t="n">
-        <v>7500</v>
+        <v>36000</v>
       </c>
       <c r="T15" t="n">
         <v>2000</v>
@@ -2082,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>759000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2092,19 +2108,19 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>13</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -2122,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2131,19 +2147,19 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>195000</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6750</v>
       </c>
       <c r="Q16" t="n">
         <v>95000</v>
       </c>
       <c r="R16" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="S16" t="n">
-        <v>15000</v>
+        <v>6750</v>
       </c>
       <c r="T16" t="n">
         <v>2000</v>
@@ -2161,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2177,19 +2193,19 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
         <v>61</v>
-      </c>
-      <c r="C17" t="n">
-        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -2198,37 +2214,37 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>915000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>67500</v>
       </c>
       <c r="Q17" t="n">
         <v>38000</v>
       </c>
       <c r="R17" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="S17" t="n">
-        <v>15000</v>
+        <v>67500</v>
       </c>
       <c r="T17" t="n">
         <v>2000</v>
@@ -2237,21 +2253,106 @@
         <v>2000</v>
       </c>
       <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>1800</v>
       </c>
-      <c r="W17" t="n">
-        <v>1000</v>
-      </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>462000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2347,19 +2448,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2227</v>
+      </c>
+      <c r="F2" t="n">
         <v>2232</v>
       </c>
-      <c r="F2" t="n">
-        <v>2291</v>
-      </c>
       <c r="G2" t="n">
-        <v>-59</v>
+        <v>-5</v>
       </c>
       <c r="H2" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>885000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="3">
@@ -2382,19 +2483,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>889</v>
+      </c>
+      <c r="F3" t="n">
         <v>890</v>
       </c>
-      <c r="F3" t="n">
-        <v>892</v>
-      </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4">
@@ -2479,19 +2580,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>391</v>
+      </c>
+      <c r="F6" t="n">
         <v>394</v>
       </c>
-      <c r="F6" t="n">
-        <v>400</v>
-      </c>
       <c r="G6" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>15000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="7">
@@ -2514,19 +2615,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>180</v>
+      </c>
+      <c r="F7" t="n">
         <v>183</v>
       </c>
-      <c r="F7" t="n">
-        <v>213</v>
-      </c>
       <c r="G7" t="n">
-        <v>-30</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>67500</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -2622,16 +2723,16 @@
         <v>940</v>
       </c>
       <c r="F10" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="G10" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2657,16 +2758,16 @@
         <v>359</v>
       </c>
       <c r="F11" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2762,16 +2863,16 @@
         <v>342</v>
       </c>
       <c r="F14" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2866,8 +2967,12 @@
       <c r="E17" t="n">
         <v>371</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>371</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -2897,8 +3002,12 @@
       <c r="E18" t="n">
         <v>494</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>494</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -2928,8 +3037,12 @@
       <c r="E19" t="n">
         <v>477</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>477</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -2960,16 +3073,16 @@
         <v>693</v>
       </c>
       <c r="F20" t="n">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3030,16 +3143,16 @@
         <v>953</v>
       </c>
       <c r="F22" t="n">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3097,19 +3210,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>259</v>
+      </c>
+      <c r="F24" t="n">
         <v>260</v>
       </c>
-      <c r="F24" t="n">
-        <v>262</v>
-      </c>
       <c r="G24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -3132,10 +3245,10 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>170</v>
+      </c>
+      <c r="F25" t="n">
         <v>172</v>
-      </c>
-      <c r="F25" t="n">
-        <v>174</v>
       </c>
       <c r="G25" t="n">
         <v>-2</v>
@@ -3167,19 +3280,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>259</v>
+      </c>
+      <c r="F26" t="n">
         <v>260</v>
       </c>
-      <c r="F26" t="n">
-        <v>262</v>
-      </c>
       <c r="G26" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>38000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -3202,15 +3315,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>758</v>
+      </c>
+      <c r="F27" t="n">
         <v>759</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>-1</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="28">
@@ -3235,8 +3352,12 @@
       <c r="E28" t="n">
         <v>322</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>322</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
@@ -3264,15 +3385,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>361</v>
+      </c>
+      <c r="F29" t="n">
         <v>364</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>-3</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="30">
@@ -3295,15 +3420,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>483</v>
+      </c>
+      <c r="F30" t="n">
         <v>488</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-5</v>
+      </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="31">
@@ -3326,15 +3455,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>483</v>
+      </c>
+      <c r="F31" t="n">
         <v>488</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>-5</v>
+      </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="32">
@@ -3357,15 +3490,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>758</v>
+      </c>
+      <c r="F32" t="n">
         <v>759</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>-1</v>
+      </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="33">
@@ -3390,8 +3527,12 @@
       <c r="E33" t="n">
         <v>322</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>322</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -3419,15 +3560,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>361</v>
+      </c>
+      <c r="F34" t="n">
         <v>364</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>-3</v>
+      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="35">
@@ -3450,15 +3595,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>483</v>
+      </c>
+      <c r="F35" t="n">
         <v>488</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-5</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="36">
@@ -3481,15 +3630,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>483</v>
+      </c>
+      <c r="F36" t="n">
         <v>488</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-5</v>
+      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
   </sheetData>
@@ -3503,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I545"/>
+  <dimension ref="A1:I580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23462,6 +23615,1293 @@
         <v>0</v>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F546" t="n">
+        <v>2227</v>
+      </c>
+      <c r="G546" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H546" t="n">
+        <v>5</v>
+      </c>
+      <c r="I546" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F547" t="n">
+        <v>889</v>
+      </c>
+      <c r="G547" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H547" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" t="n">
+        <v>0</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" t="n">
+        <v>0</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F550" t="n">
+        <v>391</v>
+      </c>
+      <c r="G550" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H550" t="n">
+        <v>3</v>
+      </c>
+      <c r="I550" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F551" t="n">
+        <v>180</v>
+      </c>
+      <c r="G551" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H551" t="n">
+        <v>3</v>
+      </c>
+      <c r="I551" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F552" t="n">
+        <v>822</v>
+      </c>
+      <c r="G552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F553" t="n">
+        <v>966</v>
+      </c>
+      <c r="G553" t="n">
+        <v>0</v>
+      </c>
+      <c r="H553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F554" t="n">
+        <v>940</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H554" t="n">
+        <v>0</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F555" t="n">
+        <v>359</v>
+      </c>
+      <c r="G555" t="n">
+        <v>0</v>
+      </c>
+      <c r="H555" t="n">
+        <v>0</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F556" t="n">
+        <v>479</v>
+      </c>
+      <c r="G556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H556" t="n">
+        <v>0</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F557" t="n">
+        <v>484</v>
+      </c>
+      <c r="G557" t="n">
+        <v>0</v>
+      </c>
+      <c r="H557" t="n">
+        <v>0</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F558" t="n">
+        <v>342</v>
+      </c>
+      <c r="G558" t="n">
+        <v>0</v>
+      </c>
+      <c r="H558" t="n">
+        <v>0</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F559" t="n">
+        <v>481</v>
+      </c>
+      <c r="G559" t="n">
+        <v>0</v>
+      </c>
+      <c r="H559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F560" t="n">
+        <v>483</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>900</v>
+      </c>
+      <c r="F561" t="n">
+        <v>371</v>
+      </c>
+      <c r="G561" t="n">
+        <v>0</v>
+      </c>
+      <c r="H561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>900</v>
+      </c>
+      <c r="F562" t="n">
+        <v>494</v>
+      </c>
+      <c r="G562" t="n">
+        <v>0</v>
+      </c>
+      <c r="H562" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>900</v>
+      </c>
+      <c r="F563" t="n">
+        <v>477</v>
+      </c>
+      <c r="G563" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>900</v>
+      </c>
+      <c r="F564" t="n">
+        <v>693</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" t="n">
+        <v>0</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>900</v>
+      </c>
+      <c r="F565" t="n">
+        <v>941</v>
+      </c>
+      <c r="G565" t="n">
+        <v>0</v>
+      </c>
+      <c r="H565" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>900</v>
+      </c>
+      <c r="F566" t="n">
+        <v>953</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F567" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G567" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" t="n">
+        <v>0</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F568" t="n">
+        <v>259</v>
+      </c>
+      <c r="G568" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H568" t="n">
+        <v>1</v>
+      </c>
+      <c r="I568" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F569" t="n">
+        <v>170</v>
+      </c>
+      <c r="G569" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H569" t="n">
+        <v>2</v>
+      </c>
+      <c r="I569" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F570" t="n">
+        <v>259</v>
+      </c>
+      <c r="G570" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H570" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F571" t="n">
+        <v>758</v>
+      </c>
+      <c r="G571" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H571" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F572" t="n">
+        <v>322</v>
+      </c>
+      <c r="G572" t="n">
+        <v>0</v>
+      </c>
+      <c r="H572" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F573" t="n">
+        <v>361</v>
+      </c>
+      <c r="G573" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H573" t="n">
+        <v>3</v>
+      </c>
+      <c r="I573" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F574" t="n">
+        <v>483</v>
+      </c>
+      <c r="G574" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H574" t="n">
+        <v>5</v>
+      </c>
+      <c r="I574" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F575" t="n">
+        <v>483</v>
+      </c>
+      <c r="G575" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H575" t="n">
+        <v>5</v>
+      </c>
+      <c r="I575" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F576" t="n">
+        <v>758</v>
+      </c>
+      <c r="G576" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H576" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F577" t="n">
+        <v>322</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0</v>
+      </c>
+      <c r="H577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F578" t="n">
+        <v>361</v>
+      </c>
+      <c r="G578" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H578" t="n">
+        <v>3</v>
+      </c>
+      <c r="I578" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F579" t="n">
+        <v>483</v>
+      </c>
+      <c r="G579" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H579" t="n">
+        <v>5</v>
+      </c>
+      <c r="I579" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F580" t="n">
+        <v>483</v>
+      </c>
+      <c r="G580" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H580" t="n">
+        <v>5</v>
+      </c>
+      <c r="I580" t="n">
+        <v>82500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,22 @@
         <v>588250</v>
       </c>
       <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -742,34 +758,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="55" customWidth="1" min="22" max="22"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="55" customWidth="1" min="25" max="25"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
@@ -782,132 +798,132 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq writing set (Units)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq writing set (Rev USD)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1003,10 +1019,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -1015,26 +1031,26 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -1042,28 +1058,28 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>231000</v>
       </c>
-      <c r="P3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>6750</v>
       </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1000</v>
-      </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1072,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1088,28 +1104,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1124,31 +1140,31 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T4" t="n">
         <v>198000</v>
       </c>
-      <c r="P4" t="n">
-        <v>45000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>76000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3000</v>
-      </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>4000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1163,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1173,10 +1189,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1188,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1203,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1212,28 +1228,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
         <v>528000</v>
       </c>
-      <c r="P5" t="n">
-        <v>90000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>2250</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1000</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1242,7 +1258,7 @@
         <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1258,82 +1274,82 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>24</v>
       </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>396000</v>
       </c>
-      <c r="P6" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>13500</v>
       </c>
-      <c r="T6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1000</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W6" t="n">
         <v>2700</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y6" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1343,37 +1359,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>44</v>
@@ -1382,37 +1398,37 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T7" t="n">
         <v>1782000</v>
       </c>
-      <c r="P7" t="n">
-        <v>465000</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>152000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>4500</v>
       </c>
-      <c r="T7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>8000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>2700</v>
       </c>
       <c r="X7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>44000</v>
@@ -1428,38 +1444,38 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>36</v>
       </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1467,37 +1483,37 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>594000</v>
       </c>
-      <c r="P8" t="n">
-        <v>210000</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V8" t="n">
         <v>5000</v>
       </c>
-      <c r="S8" t="n">
-        <v>2250</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>3000</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1513,37 +1529,37 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
         <v>48</v>
       </c>
-      <c r="C9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
         <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1552,37 +1568,37 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T9" t="n">
         <v>792000</v>
       </c>
-      <c r="P9" t="n">
-        <v>195000</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>114000</v>
-      </c>
-      <c r="R9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>15750</v>
       </c>
-      <c r="T9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>6000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>900</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -1598,25 +1614,25 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>143</v>
       </c>
-      <c r="C10" t="n">
-        <v>55</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1628,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1637,25 +1653,25 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>825000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>2359500</v>
       </c>
-      <c r="P10" t="n">
-        <v>825000</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>4500</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1667,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1683,38 +1699,38 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>15</v>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1722,26 +1738,26 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>247500</v>
       </c>
-      <c r="P11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>2250</v>
       </c>
-      <c r="T11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
@@ -1752,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1768,82 +1784,82 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="R12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T12" t="n">
         <v>297000</v>
       </c>
-      <c r="P12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>57000</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>2250</v>
       </c>
-      <c r="T12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>3000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>900</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1853,37 +1869,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
         <v>12</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
         <v>12</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1892,37 +1908,37 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>228000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T13" t="n">
         <v>528000</v>
       </c>
-      <c r="P13" t="n">
-        <v>90000</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>228000</v>
-      </c>
-      <c r="R13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>4500</v>
       </c>
-      <c r="T13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>12000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>900</v>
       </c>
       <c r="X13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1938,38 +1954,38 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>19</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>100</v>
       </c>
-      <c r="C14" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1977,37 +1993,37 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>285000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>190000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>1650000</v>
       </c>
-      <c r="P14" t="n">
-        <v>285000</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>190000</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="V14" t="n">
         <v>10000</v>
       </c>
-      <c r="S14" t="n">
-        <v>15750</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2000</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2023,38 +2039,38 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>46</v>
       </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>16</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2062,37 +2078,37 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R15" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>759000</v>
       </c>
-      <c r="P15" t="n">
-        <v>150000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>38000</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7500</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>36000</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>2000</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2108,34 +2124,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -2147,34 +2163,34 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="P16" t="n">
-        <v>195000</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R16" t="n">
         <v>95000</v>
       </c>
-      <c r="R16" t="n">
-        <v>15000</v>
-      </c>
       <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>6750</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>2000</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5000</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>2000</v>
@@ -2193,37 +2209,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>6</v>
-      </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>30</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2232,37 +2248,37 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>915000</v>
       </c>
       <c r="P17" t="n">
-        <v>915000</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R17" t="n">
         <v>38000</v>
       </c>
-      <c r="R17" t="n">
-        <v>15000</v>
-      </c>
       <c r="S17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>67500</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>2000</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>1800</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="Y17" t="n">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -2278,81 +2294,166 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>28</v>
       </c>
-      <c r="C18" t="n">
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R18" t="n">
+        <v>19000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>462000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6750</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>462000</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>90000</v>
       </c>
-      <c r="Q18" t="n">
-        <v>19000</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7500</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6750</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2367,11 +2468,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2448,19 +2549,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2223</v>
+      </c>
+      <c r="F2" t="n">
         <v>2227</v>
       </c>
-      <c r="F2" t="n">
-        <v>2232</v>
-      </c>
       <c r="G2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>75000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="3">
@@ -2483,19 +2584,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>887</v>
+      </c>
+      <c r="F3" t="n">
         <v>889</v>
       </c>
-      <c r="F3" t="n">
-        <v>890</v>
-      </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -2563,7 +2664,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2573,61 +2674,61 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-MX1-V123</t>
+          <t>INQ-A5-SP01-BLK-V123</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="E6" t="n">
-        <v>391</v>
+        <v>180</v>
       </c>
       <c r="F6" t="n">
-        <v>394</v>
+        <v>180</v>
       </c>
       <c r="G6" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V123</t>
+          <t>INQ-USL-SP01-BLK-V1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>822</v>
       </c>
       <c r="F7" t="n">
-        <v>183</v>
+        <v>822</v>
       </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2638,22 +2739,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V1</t>
+          <t>INQ-USL-SP01-BLK-V2</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>822</v>
+        <v>966</v>
       </c>
       <c r="F8" t="n">
-        <v>822</v>
+        <v>966</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2673,22 +2774,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V2</t>
+          <t>INQ-USL-SP01-BLK-V3</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1000</v>
       </c>
       <c r="E9" t="n">
-        <v>966</v>
+        <v>940</v>
       </c>
       <c r="F9" t="n">
-        <v>966</v>
+        <v>940</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2703,27 +2804,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V3</t>
+          <t>INQ-USL-SP01-ORG-V1</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1000</v>
       </c>
       <c r="E10" t="n">
-        <v>940</v>
+        <v>359</v>
       </c>
       <c r="F10" t="n">
-        <v>940</v>
+        <v>359</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2743,22 +2844,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V1</t>
+          <t>INQ-USL-SP01-ORG-V2</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>359</v>
+        <v>479</v>
       </c>
       <c r="F11" t="n">
-        <v>359</v>
+        <v>479</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2778,22 +2879,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V2</t>
+          <t>INQ-USL-SP01-ORG-V3</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1000</v>
       </c>
       <c r="E12" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F12" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2808,27 +2909,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V3</t>
+          <t>INQ-USL-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1000</v>
       </c>
       <c r="E13" t="n">
-        <v>484</v>
+        <v>342</v>
       </c>
       <c r="F13" t="n">
-        <v>484</v>
+        <v>342</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2848,22 +2949,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V1</t>
+          <t>INQ-USL-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>342</v>
+        <v>481</v>
       </c>
       <c r="F14" t="n">
-        <v>342</v>
+        <v>481</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2883,22 +2984,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V2</t>
+          <t>INQ-USL-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1000</v>
       </c>
       <c r="E15" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2913,27 +3014,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V3</t>
+          <t>INQ-A5-SP01-BLK-V1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E16" t="n">
-        <v>483</v>
+        <v>371</v>
       </c>
       <c r="F16" t="n">
-        <v>483</v>
+        <v>371</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -2953,22 +3054,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V1</t>
+          <t>INQ-A5-SP01-BLK-V2</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>371</v>
+        <v>494</v>
       </c>
       <c r="F17" t="n">
-        <v>371</v>
+        <v>494</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -2988,22 +3089,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V2</t>
+          <t>INQ-A5-SP01-BLK-V3</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="F18" t="n">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3018,27 +3119,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V3</t>
+          <t>INQ-A5-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>477</v>
+        <v>693</v>
       </c>
       <c r="F19" t="n">
-        <v>477</v>
+        <v>693</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3058,22 +3159,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V1</t>
+          <t>INQ-A5-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>693</v>
+        <v>941</v>
       </c>
       <c r="F20" t="n">
-        <v>693</v>
+        <v>941</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3093,22 +3194,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V2</t>
+          <t>INQ-A5-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="F21" t="n">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3123,27 +3224,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V3</t>
+          <t>INQ-RFL-BLK-05</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E22" t="n">
-        <v>953</v>
+        <v>-1</v>
       </c>
       <c r="F22" t="n">
-        <v>953</v>
+        <v>-1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3163,22 +3264,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLK-05</t>
+          <t>INQ-RFL-BLU-05</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1000</v>
       </c>
       <c r="E23" t="n">
-        <v>-1</v>
+        <v>259</v>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>259</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3193,42 +3294,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLU-05</t>
+          <t>INQ-RFL-PCL-01</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1000</v>
       </c>
       <c r="E24" t="n">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="F24" t="n">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+          <t>inq Student Kit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3238,411 +3339,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INQ-RFL-PCL-01</t>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="E25" t="n">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="F25" t="n">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="G25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>inq Student Kit</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Default Title</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BINQ-STUDENTKIT-LTR-MX1</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>19000</v>
-      </c>
-      <c r="E26" t="n">
-        <v>259</v>
-      </c>
-      <c r="F26" t="n">
-        <v>260</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>BINQ-A5W-BLK</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E27" t="n">
-        <v>758</v>
-      </c>
-      <c r="F27" t="n">
-        <v>759</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BINQ-A5W-WHT</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E28" t="n">
-        <v>322</v>
-      </c>
-      <c r="F28" t="n">
-        <v>322</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-BLK</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E29" t="n">
-        <v>361</v>
-      </c>
-      <c r="F29" t="n">
-        <v>364</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>49500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-ORG</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E30" t="n">
-        <v>483</v>
-      </c>
-      <c r="F30" t="n">
-        <v>488</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>82500</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>BINQ-LTR-WHT</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E31" t="n">
-        <v>483</v>
-      </c>
-      <c r="F31" t="n">
-        <v>488</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>82500</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>WINQ-A5W-BLK</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E32" t="n">
-        <v>758</v>
-      </c>
-      <c r="F32" t="n">
-        <v>759</v>
-      </c>
-      <c r="G32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>WINQ-A5W-WHT</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E33" t="n">
-        <v>322</v>
-      </c>
-      <c r="F33" t="n">
-        <v>322</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Black</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-BLK</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E34" t="n">
-        <v>361</v>
-      </c>
-      <c r="F34" t="n">
-        <v>364</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" t="n">
-        <v>49500</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-ORG</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E35" t="n">
-        <v>483</v>
-      </c>
-      <c r="F35" t="n">
-        <v>488</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H35" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" t="n">
-        <v>82500</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>inq writing set</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Moon White / Letter - 8.5" x 11" / White</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>WINQ-LTR-WHT</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>16500</v>
-      </c>
-      <c r="E36" t="n">
-        <v>483</v>
-      </c>
-      <c r="F36" t="n">
-        <v>488</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5</v>
-      </c>
-      <c r="I36" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3656,7 +3372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I580"/>
+  <dimension ref="A1:I604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24902,6 +24618,886 @@
         <v>82500</v>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F581" t="n">
+        <v>2223</v>
+      </c>
+      <c r="G581" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H581" t="n">
+        <v>4</v>
+      </c>
+      <c r="I581" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F582" t="n">
+        <v>887</v>
+      </c>
+      <c r="G582" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H582" t="n">
+        <v>2</v>
+      </c>
+      <c r="I582" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0</v>
+      </c>
+      <c r="H583" t="n">
+        <v>0</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr"/>
+      <c r="E584" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0</v>
+      </c>
+      <c r="H584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F585" t="n">
+        <v>180</v>
+      </c>
+      <c r="G585" t="n">
+        <v>0</v>
+      </c>
+      <c r="H585" t="n">
+        <v>0</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F586" t="n">
+        <v>822</v>
+      </c>
+      <c r="G586" t="n">
+        <v>0</v>
+      </c>
+      <c r="H586" t="n">
+        <v>0</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F587" t="n">
+        <v>966</v>
+      </c>
+      <c r="G587" t="n">
+        <v>0</v>
+      </c>
+      <c r="H587" t="n">
+        <v>0</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F588" t="n">
+        <v>940</v>
+      </c>
+      <c r="G588" t="n">
+        <v>0</v>
+      </c>
+      <c r="H588" t="n">
+        <v>0</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F589" t="n">
+        <v>359</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0</v>
+      </c>
+      <c r="H589" t="n">
+        <v>0</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F590" t="n">
+        <v>479</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0</v>
+      </c>
+      <c r="H590" t="n">
+        <v>0</v>
+      </c>
+      <c r="I590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F591" t="n">
+        <v>484</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0</v>
+      </c>
+      <c r="H591" t="n">
+        <v>0</v>
+      </c>
+      <c r="I591" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F592" t="n">
+        <v>342</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0</v>
+      </c>
+      <c r="H592" t="n">
+        <v>0</v>
+      </c>
+      <c r="I592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F593" t="n">
+        <v>481</v>
+      </c>
+      <c r="G593" t="n">
+        <v>0</v>
+      </c>
+      <c r="H593" t="n">
+        <v>0</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F594" t="n">
+        <v>483</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0</v>
+      </c>
+      <c r="H594" t="n">
+        <v>0</v>
+      </c>
+      <c r="I594" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>900</v>
+      </c>
+      <c r="F595" t="n">
+        <v>371</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0</v>
+      </c>
+      <c r="H595" t="n">
+        <v>0</v>
+      </c>
+      <c r="I595" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>900</v>
+      </c>
+      <c r="F596" t="n">
+        <v>494</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>900</v>
+      </c>
+      <c r="F597" t="n">
+        <v>477</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0</v>
+      </c>
+      <c r="H597" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>900</v>
+      </c>
+      <c r="F598" t="n">
+        <v>693</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>900</v>
+      </c>
+      <c r="F599" t="n">
+        <v>941</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" t="n">
+        <v>0</v>
+      </c>
+      <c r="I599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>900</v>
+      </c>
+      <c r="F600" t="n">
+        <v>953</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F601" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G601" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" t="n">
+        <v>0</v>
+      </c>
+      <c r="I601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F602" t="n">
+        <v>259</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F603" t="n">
+        <v>170</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F604" t="n">
+        <v>259</v>
+      </c>
+      <c r="G604" t="n">
+        <v>0</v>
+      </c>
+      <c r="H604" t="n">
+        <v>0</v>
+      </c>
+      <c r="I604" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -745,6 +745,22 @@
       </c>
       <c r="D19" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" t="n">
+        <v>253500</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -758,35 +774,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="55" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="48" customWidth="1" min="25" max="25"/>
-    <col width="55" customWidth="1" min="26" max="26"/>
+    <col width="55" customWidth="1" min="25" max="25"/>
+    <col width="29" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -803,59 +819,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
@@ -868,57 +884,57 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -1022,22 +1038,22 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -1049,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1061,37 +1077,37 @@
         <v>45000</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="Q3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>2500</v>
       </c>
-      <c r="R3" t="n">
-        <v>19000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>231000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6750</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1107,10 +1123,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -1119,25 +1135,25 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1146,37 +1162,37 @@
         <v>45000</v>
       </c>
       <c r="P4" t="n">
-        <v>2700</v>
+        <v>76000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>76000</v>
+        <v>4000</v>
       </c>
       <c r="S4" t="n">
         <v>3000</v>
       </c>
       <c r="T4" t="n">
-        <v>198000</v>
+        <v>3000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="V4" t="n">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1192,7 +1208,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1201,13 +1217,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>32</v>
-      </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1216,13 +1232,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1231,37 +1247,37 @@
         <v>90000</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="Q5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>2500</v>
       </c>
-      <c r="R5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
         <v>528000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1280,34 +1296,34 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1316,37 +1332,37 @@
         <v>120000</v>
       </c>
       <c r="P6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>900</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
         <v>5000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>19000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>396000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13500</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1000</v>
       </c>
       <c r="W6" t="n">
         <v>2700</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2000</v>
       </c>
-      <c r="Y6" t="n">
-        <v>3000</v>
-      </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>396000</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1362,37 +1378,37 @@
         <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>108</v>
-      </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1401,37 +1417,37 @@
         <v>465000</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>152000</v>
       </c>
       <c r="Q7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>10000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>152000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1782000</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="V7" t="n">
-        <v>8000</v>
       </c>
       <c r="W7" t="n">
         <v>2700</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>44000</v>
+        <v>1782000</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1447,37 +1463,37 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>36</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1486,22 +1502,22 @@
         <v>210000</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="Q8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R8" t="n">
         <v>5000</v>
       </c>
-      <c r="R8" t="n">
-        <v>95000</v>
-      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T8" t="n">
-        <v>594000</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>5000</v>
@@ -1513,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>594000</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1532,37 +1548,37 @@
         <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
       </c>
       <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>48</v>
-      </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1571,37 +1587,37 @@
         <v>195000</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>114000</v>
       </c>
       <c r="Q9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>20000</v>
-      </c>
-      <c r="R9" t="n">
-        <v>114000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>792000</v>
-      </c>
-      <c r="U9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="V9" t="n">
-        <v>6000</v>
       </c>
       <c r="W9" t="n">
         <v>900</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>792000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1620,22 +1636,22 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -1644,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1659,22 +1675,22 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>2500</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2359500</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>3600</v>
@@ -1683,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2359500</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1711,28 +1727,28 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>15</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1744,34 +1760,34 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>2500</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
         <v>247500</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2250</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1787,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1799,13 +1815,13 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1814,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1826,25 +1842,25 @@
         <v>75000</v>
       </c>
       <c r="P12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U12" t="n">
         <v>900</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
         <v>2500</v>
-      </c>
-      <c r="R12" t="n">
-        <v>57000</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T12" t="n">
-        <v>297000</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3000</v>
       </c>
       <c r="W12" t="n">
         <v>900</v>
@@ -1853,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>297000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1872,25 +1888,25 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
       </c>
       <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>32</v>
-      </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1899,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1911,25 +1927,25 @@
         <v>90000</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="Q13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
         <v>10000</v>
-      </c>
-      <c r="R13" t="n">
-        <v>228000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T13" t="n">
-        <v>528000</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="V13" t="n">
-        <v>12000</v>
       </c>
       <c r="W13" t="n">
         <v>900</v>
@@ -1938,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>528000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1957,37 +1973,37 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>100</v>
-      </c>
-      <c r="H14" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1996,22 +2012,22 @@
         <v>285000</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="Q14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="R14" t="n">
         <v>10000</v>
       </c>
-      <c r="R14" t="n">
-        <v>190000</v>
-      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="n">
-        <v>1650000</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>15750</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>10000</v>
@@ -2023,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1650000</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2042,37 +2058,37 @@
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>46</v>
-      </c>
-      <c r="H15" t="n">
-        <v>16</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2081,37 +2097,37 @@
         <v>150000</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="Q15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
         <v>7500</v>
       </c>
-      <c r="R15" t="n">
-        <v>38000</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
         <v>759000</v>
-      </c>
-      <c r="U15" t="n">
-        <v>36000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2127,31 +2143,31 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -2166,31 +2182,31 @@
         <v>195000</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="Q16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>15000</v>
       </c>
-      <c r="R16" t="n">
-        <v>95000</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>6750</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5000</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>2000</v>
@@ -2212,37 +2228,37 @@
         <v>61</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
         <v>20</v>
       </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2251,37 +2267,37 @@
         <v>915000</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="Q17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
         <v>15000</v>
-      </c>
-      <c r="R17" t="n">
-        <v>38000</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>67500</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2000</v>
       </c>
       <c r="W17" t="n">
         <v>1800</v>
       </c>
       <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
         <v>20000</v>
       </c>
-      <c r="Y17" t="n">
-        <v>2000</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2297,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -2306,28 +2322,28 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>28</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2336,37 +2352,37 @@
         <v>90000</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="Q18" t="n">
+        <v>6750</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
         <v>7500</v>
       </c>
-      <c r="R18" t="n">
-        <v>19000</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
         <v>462000</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6750</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2454,6 +2470,91 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2468,11 +2569,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2549,19 +2650,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2214</v>
+      </c>
+      <c r="F2" t="n">
         <v>2223</v>
       </c>
-      <c r="F2" t="n">
-        <v>2227</v>
-      </c>
       <c r="G2" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>60000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="3">
@@ -2587,16 +2688,16 @@
         <v>887</v>
       </c>
       <c r="F3" t="n">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2664,7 +2765,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2674,21 +2775,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V123</t>
+          <t>INQ-USL-SP01-MX1-V123</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="E6" t="n">
-        <v>180</v>
-      </c>
-      <c r="F6" t="n">
-        <v>180</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -2699,36 +2796,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V1</t>
+          <t>INQ-A5-SP01-BLK-V123</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="E7" t="n">
-        <v>822</v>
+        <v>174</v>
       </c>
       <c r="F7" t="n">
-        <v>822</v>
+        <v>180</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="8">
@@ -2739,22 +2836,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V2</t>
+          <t>INQ-USL-SP01-BLK-V1</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>1000</v>
       </c>
       <c r="E8" t="n">
-        <v>966</v>
+        <v>822</v>
       </c>
       <c r="F8" t="n">
-        <v>966</v>
+        <v>822</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2774,22 +2871,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-BLK-V3</t>
+          <t>INQ-USL-SP01-BLK-V2</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1000</v>
       </c>
       <c r="E9" t="n">
-        <v>940</v>
+        <v>966</v>
       </c>
       <c r="F9" t="n">
-        <v>940</v>
+        <v>966</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2804,27 +2901,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V1</t>
+          <t>INQ-USL-SP01-BLK-V3</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1000</v>
       </c>
       <c r="E10" t="n">
-        <v>359</v>
+        <v>940</v>
       </c>
       <c r="F10" t="n">
-        <v>359</v>
+        <v>940</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2844,31 +2941,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V2</t>
+          <t>INQ-USL-SP01-ORG-V1</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1000</v>
       </c>
       <c r="E11" t="n">
-        <v>479</v>
+        <v>358</v>
       </c>
       <c r="F11" t="n">
-        <v>479</v>
+        <v>359</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -2879,57 +2976,57 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-ORG-V3</t>
+          <t>INQ-USL-SP01-ORG-V2</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1000</v>
       </c>
       <c r="E12" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="F12" t="n">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V1</t>
+          <t>INQ-USL-SP01-ORG-V3</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1000</v>
       </c>
       <c r="E13" t="n">
-        <v>342</v>
+        <v>484</v>
       </c>
       <c r="F13" t="n">
-        <v>342</v>
+        <v>484</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2949,22 +3046,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V2</t>
+          <t>INQ-USL-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>481</v>
+        <v>342</v>
       </c>
       <c r="F14" t="n">
-        <v>481</v>
+        <v>342</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2984,22 +3081,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INQ-USL-SP01-WHT-V3</t>
+          <t>INQ-USL-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1000</v>
       </c>
       <c r="E15" t="n">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F15" t="n">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -3014,27 +3111,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V1</t>
+          <t>INQ-USL-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E16" t="n">
-        <v>371</v>
+        <v>483</v>
       </c>
       <c r="F16" t="n">
-        <v>371</v>
+        <v>483</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -3054,22 +3151,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V2</t>
+          <t>INQ-A5-SP01-BLK-V1</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="F17" t="n">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3089,22 +3186,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-BLK-V3</t>
+          <t>INQ-A5-SP01-BLK-V2</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="F18" t="n">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3119,27 +3216,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V1</t>
+          <t>INQ-A5-SP01-BLK-V3</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>693</v>
+        <v>477</v>
       </c>
       <c r="F19" t="n">
-        <v>693</v>
+        <v>477</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3159,22 +3256,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V2</t>
+          <t>INQ-A5-SP01-WHT-V1</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>941</v>
+        <v>693</v>
       </c>
       <c r="F20" t="n">
-        <v>941</v>
+        <v>693</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3194,22 +3291,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INQ-A5-SP01-WHT-V3</t>
+          <t>INQ-A5-SP01-WHT-V2</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>900</v>
       </c>
       <c r="E21" t="n">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="F21" t="n">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3224,27 +3321,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inq PEN Kit - 5-pack D1 Refills</t>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLK-05</t>
+          <t>INQ-A5-SP01-WHT-V3</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E22" t="n">
-        <v>-1</v>
+        <v>953</v>
       </c>
       <c r="F22" t="n">
-        <v>-1</v>
+        <v>953</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3264,25 +3361,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INQ-RFL-BLU-05</t>
+          <t>INQ-RFL-BLK-05</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>1000</v>
       </c>
       <c r="E23" t="n">
-        <v>259</v>
+        <v>898</v>
       </c>
       <c r="F23" t="n">
-        <v>259</v>
+        <v>-1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3294,70 +3391,415 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INQ-RFL-PCL-01</t>
+          <t>INQ-RFL-BLU-05</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1000</v>
       </c>
       <c r="E24" t="n">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="F24" t="n">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>170</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>inq Student Kit</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>BINQ-STUDENTKIT-LTR-MX1</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>19000</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
+        <v>254</v>
+      </c>
+      <c r="F26" t="n">
         <v>259</v>
       </c>
-      <c r="F25" t="n">
-        <v>259</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="G26" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E27" t="n">
+        <v>754</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>321</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E29" t="n">
+        <v>354</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E30" t="n">
+        <v>472</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E31" t="n">
+        <v>472</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E32" t="n">
+        <v>754</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E33" t="n">
+        <v>321</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E34" t="n">
+        <v>354</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E35" t="n">
+        <v>472</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E36" t="n">
+        <v>472</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3372,7 +3814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I604"/>
+  <dimension ref="A1:I639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25498,6 +25940,1271 @@
         <v>0</v>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F605" t="n">
+        <v>2214</v>
+      </c>
+      <c r="G605" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H605" t="n">
+        <v>9</v>
+      </c>
+      <c r="I605" t="n">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F606" t="n">
+        <v>887</v>
+      </c>
+      <c r="G606" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0</v>
+      </c>
+      <c r="G607" t="n">
+        <v>0</v>
+      </c>
+      <c r="H607" t="n">
+        <v>0</v>
+      </c>
+      <c r="I607" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F609" t="n">
+        <v>381</v>
+      </c>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="n">
+        <v>0</v>
+      </c>
+      <c r="I609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F610" t="n">
+        <v>174</v>
+      </c>
+      <c r="G610" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H610" t="n">
+        <v>6</v>
+      </c>
+      <c r="I610" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F611" t="n">
+        <v>822</v>
+      </c>
+      <c r="G611" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" t="n">
+        <v>0</v>
+      </c>
+      <c r="I611" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F612" t="n">
+        <v>966</v>
+      </c>
+      <c r="G612" t="n">
+        <v>0</v>
+      </c>
+      <c r="H612" t="n">
+        <v>0</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F613" t="n">
+        <v>940</v>
+      </c>
+      <c r="G613" t="n">
+        <v>0</v>
+      </c>
+      <c r="H613" t="n">
+        <v>0</v>
+      </c>
+      <c r="I613" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F614" t="n">
+        <v>358</v>
+      </c>
+      <c r="G614" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H614" t="n">
+        <v>1</v>
+      </c>
+      <c r="I614" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F615" t="n">
+        <v>478</v>
+      </c>
+      <c r="G615" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H615" t="n">
+        <v>1</v>
+      </c>
+      <c r="I615" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F616" t="n">
+        <v>484</v>
+      </c>
+      <c r="G616" t="n">
+        <v>0</v>
+      </c>
+      <c r="H616" t="n">
+        <v>0</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F617" t="n">
+        <v>342</v>
+      </c>
+      <c r="G617" t="n">
+        <v>0</v>
+      </c>
+      <c r="H617" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F618" t="n">
+        <v>481</v>
+      </c>
+      <c r="G618" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F619" t="n">
+        <v>483</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>900</v>
+      </c>
+      <c r="F620" t="n">
+        <v>371</v>
+      </c>
+      <c r="G620" t="n">
+        <v>0</v>
+      </c>
+      <c r="H620" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>900</v>
+      </c>
+      <c r="F621" t="n">
+        <v>494</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>900</v>
+      </c>
+      <c r="F622" t="n">
+        <v>477</v>
+      </c>
+      <c r="G622" t="n">
+        <v>0</v>
+      </c>
+      <c r="H622" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>900</v>
+      </c>
+      <c r="F623" t="n">
+        <v>693</v>
+      </c>
+      <c r="G623" t="n">
+        <v>0</v>
+      </c>
+      <c r="H623" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>900</v>
+      </c>
+      <c r="F624" t="n">
+        <v>941</v>
+      </c>
+      <c r="G624" t="n">
+        <v>0</v>
+      </c>
+      <c r="H624" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>900</v>
+      </c>
+      <c r="F625" t="n">
+        <v>953</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H625" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F626" t="n">
+        <v>898</v>
+      </c>
+      <c r="G626" t="n">
+        <v>899</v>
+      </c>
+      <c r="H626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F627" t="n">
+        <v>254</v>
+      </c>
+      <c r="G627" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H627" t="n">
+        <v>5</v>
+      </c>
+      <c r="I627" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F628" t="n">
+        <v>167</v>
+      </c>
+      <c r="G628" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H628" t="n">
+        <v>3</v>
+      </c>
+      <c r="I628" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F629" t="n">
+        <v>254</v>
+      </c>
+      <c r="G629" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H629" t="n">
+        <v>5</v>
+      </c>
+      <c r="I629" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F630" t="n">
+        <v>754</v>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F631" t="n">
+        <v>321</v>
+      </c>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="n">
+        <v>0</v>
+      </c>
+      <c r="I631" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F632" t="n">
+        <v>354</v>
+      </c>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F633" t="n">
+        <v>472</v>
+      </c>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F634" t="n">
+        <v>472</v>
+      </c>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F635" t="n">
+        <v>754</v>
+      </c>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F636" t="n">
+        <v>321</v>
+      </c>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="n">
+        <v>0</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F637" t="n">
+        <v>354</v>
+      </c>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F638" t="n">
+        <v>472</v>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="n">
+        <v>0</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F639" t="n">
+        <v>472</v>
+      </c>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="n">
+        <v>0</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,22 @@
       </c>
       <c r="D20" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>106</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1523550</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -774,35 +790,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="29" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -814,64 +830,64 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Units)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Units)</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
@@ -879,62 +895,62 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>inq writing set (Rev USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>inq writing set (Rev USD)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -1035,67 +1051,67 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>231000</v>
+      </c>
+      <c r="P3" t="n">
         <v>45000</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>19000</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>6750</v>
       </c>
-      <c r="R3" t="n">
-        <v>1000</v>
-      </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1104,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>231000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1120,79 +1136,79 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>198000</v>
+      </c>
+      <c r="P4" t="n">
         <v>45000</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>76000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T4" t="n">
         <v>4000</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>3000</v>
       </c>
-      <c r="T4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>2700</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>198000</v>
+        <v>3000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1205,10 +1221,10 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1217,55 +1233,55 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>32</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P5" t="n">
         <v>90000</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>19000</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>2250</v>
       </c>
-      <c r="R5" t="n">
-        <v>1000</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="T5" t="n">
         <v>1000</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V5" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1274,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>528000</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1290,79 +1306,79 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
         <v>8</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>24</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>396000</v>
+      </c>
+      <c r="P6" t="n">
         <v>120000</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>13500</v>
       </c>
-      <c r="R6" t="n">
-        <v>1000</v>
-      </c>
       <c r="S6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>900</v>
+      </c>
+      <c r="Y6" t="n">
         <v>3000</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>900</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>396000</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1375,79 +1391,79 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C7" t="n">
         <v>31</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>44</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>1782000</v>
+      </c>
+      <c r="P7" t="n">
         <v>465000</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>152000</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>4500</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T7" t="n">
         <v>8000</v>
       </c>
-      <c r="S7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2000</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" t="n">
-        <v>10000</v>
+        <v>2700</v>
       </c>
       <c r="W7" t="n">
-        <v>2700</v>
+        <v>44000</v>
       </c>
       <c r="X7" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>1782000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1460,79 +1476,79 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n">
         <v>14</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>594000</v>
+      </c>
+      <c r="P8" t="n">
         <v>210000</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>95000</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>2250</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>5000</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>3000</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
       <c r="Z8" t="n">
-        <v>594000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1545,79 +1561,79 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C9" t="n">
         <v>13</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>792000</v>
+      </c>
+      <c r="P9" t="n">
         <v>195000</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>114000</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>15750</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T9" t="n">
         <v>6000</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>900</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>4000</v>
       </c>
-      <c r="T9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="W9" t="n">
-        <v>900</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
-        <v>792000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1630,16 +1646,16 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>143</v>
+      </c>
+      <c r="C10" t="n">
         <v>55</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1651,37 +1667,37 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>2359500</v>
+      </c>
+      <c r="P10" t="n">
         <v>825000</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>4500</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1690,19 +1706,19 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="W10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>2359500</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1715,16 +1731,16 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1736,37 +1752,37 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
+        <v>247500</v>
+      </c>
+      <c r="P11" t="n">
         <v>30000</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>2250</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1775,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1784,10 +1800,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>247500</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1800,22 +1816,22 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1824,55 +1840,55 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
+        <v>297000</v>
+      </c>
+      <c r="P12" t="n">
         <v>75000</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>57000</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>2250</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T12" t="n">
         <v>3000</v>
       </c>
-      <c r="S12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1000</v>
-      </c>
       <c r="U12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V12" t="n">
         <v>900</v>
       </c>
-      <c r="V12" t="n">
-        <v>2500</v>
-      </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
         <v>900</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>297000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1885,79 +1901,79 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
         <v>12</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4</v>
-      </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P13" t="n">
         <v>90000</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>228000</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>4500</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T13" t="n">
         <v>12000</v>
       </c>
-      <c r="S13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>2000</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
       <c r="V13" t="n">
-        <v>10000</v>
+        <v>900</v>
       </c>
       <c r="W13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>528000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -1970,79 +1986,79 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
         <v>19</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>10</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="P14" t="n">
         <v>285000</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>190000</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>15750</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>10000</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2000</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
       <c r="Z14" t="n">
-        <v>1650000</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2055,79 +2071,79 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>46</v>
+      </c>
+      <c r="C15" t="n">
         <v>10</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>16</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>759000</v>
+      </c>
+      <c r="P15" t="n">
         <v>150000</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>38000</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>36000</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T15" t="n">
         <v>2000</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2000</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7500</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
       <c r="Z15" t="n">
-        <v>759000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2140,28 +2156,28 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>13</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2173,34 +2189,34 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>195000</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>95000</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>6750</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T16" t="n">
         <v>5000</v>
       </c>
-      <c r="S16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2212,7 +2228,7 @@
         <v>2000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2225,79 +2241,79 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
         <v>61</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>30</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>20</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>915000</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>38000</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>67500</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T17" t="n">
         <v>2000</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2000</v>
       </c>
-      <c r="T17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>20000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2310,79 +2326,79 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>28</v>
+      </c>
+      <c r="C18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
+        <v>462000</v>
+      </c>
+      <c r="P18" t="n">
         <v>90000</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>19000</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>6750</v>
       </c>
-      <c r="R18" t="n">
-        <v>1000</v>
-      </c>
       <c r="S18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
         <v>2000</v>
       </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7500</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z18" t="n">
-        <v>462000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2395,11 +2411,11 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
@@ -2434,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>90000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2480,81 +2496,166 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>6</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>70</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>135000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>95000</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>13500</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1155000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>330000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S21" t="n">
         <v>5000</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T21" t="n">
         <v>3000</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U21" t="n">
         <v>2000</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="V21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2650,10 +2751,10 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2205</v>
+      </c>
+      <c r="F2" t="n">
         <v>2214</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2223</v>
       </c>
       <c r="G2" t="n">
         <v>-9</v>
@@ -2685,19 +2786,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="F3" t="n">
         <v>887</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="4">
@@ -2782,15 +2883,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>379</v>
+      </c>
+      <c r="F6" t="n">
         <v>381</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>-2</v>
+      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7">
@@ -2813,19 +2918,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>171</v>
+      </c>
+      <c r="F7" t="n">
         <v>174</v>
       </c>
-      <c r="F7" t="n">
-        <v>180</v>
-      </c>
       <c r="G7" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>13500</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -2953,19 +3058,19 @@
         <v>1000</v>
       </c>
       <c r="E11" t="n">
+        <v>356</v>
+      </c>
+      <c r="F11" t="n">
         <v>358</v>
       </c>
-      <c r="F11" t="n">
-        <v>359</v>
-      </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
@@ -2991,16 +3096,16 @@
         <v>478</v>
       </c>
       <c r="F12" t="n">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3058,19 +3163,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F14" t="n">
         <v>342</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -3268,19 +3373,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F20" t="n">
         <v>693</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="21">
@@ -3373,19 +3478,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>896</v>
+      </c>
+      <c r="F23" t="n">
         <v>898</v>
       </c>
-      <c r="F23" t="n">
-        <v>-1</v>
-      </c>
       <c r="G23" t="n">
-        <v>899</v>
+        <v>-2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24">
@@ -3408,19 +3513,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>253</v>
+      </c>
+      <c r="F24" t="n">
         <v>254</v>
       </c>
-      <c r="F24" t="n">
-        <v>259</v>
-      </c>
       <c r="G24" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -3446,16 +3551,16 @@
         <v>167</v>
       </c>
       <c r="F25" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3478,19 +3583,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>253</v>
+      </c>
+      <c r="F26" t="n">
         <v>254</v>
       </c>
-      <c r="F26" t="n">
-        <v>259</v>
-      </c>
       <c r="G26" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>95000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -3513,15 +3618,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>752</v>
+      </c>
+      <c r="F27" t="n">
         <v>754</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>-2</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="28">
@@ -3544,15 +3653,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>316</v>
+      </c>
+      <c r="F28" t="n">
         <v>321</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>-5</v>
+      </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="29">
@@ -3575,15 +3688,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>350</v>
+      </c>
+      <c r="F29" t="n">
         <v>354</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>-4</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="30">
@@ -3606,15 +3723,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>460</v>
+      </c>
+      <c r="F30" t="n">
         <v>472</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-12</v>
+      </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="31">
@@ -3637,15 +3758,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>460</v>
+      </c>
+      <c r="F31" t="n">
         <v>472</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>-12</v>
+      </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="32">
@@ -3668,15 +3793,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>752</v>
+      </c>
+      <c r="F32" t="n">
         <v>754</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>-2</v>
+      </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="33">
@@ -3699,15 +3828,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>316</v>
+      </c>
+      <c r="F33" t="n">
         <v>321</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>-5</v>
+      </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="34">
@@ -3730,15 +3863,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>350</v>
+      </c>
+      <c r="F34" t="n">
         <v>354</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>-4</v>
+      </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="35">
@@ -3761,15 +3898,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>460</v>
+      </c>
+      <c r="F35" t="n">
         <v>472</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>-12</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="36">
@@ -3792,15 +3933,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>460</v>
+      </c>
+      <c r="F36" t="n">
         <v>472</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>-12</v>
+      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>198000</v>
       </c>
     </row>
   </sheetData>
@@ -3814,7 +3959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I639"/>
+  <dimension ref="A1:I674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27205,6 +27350,1293 @@
         <v>0</v>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F640" t="n">
+        <v>2205</v>
+      </c>
+      <c r="G640" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H640" t="n">
+        <v>9</v>
+      </c>
+      <c r="I640" t="n">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F641" t="n">
+        <v>874</v>
+      </c>
+      <c r="G641" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H641" t="n">
+        <v>13</v>
+      </c>
+      <c r="I641" t="n">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" t="n">
+        <v>0</v>
+      </c>
+      <c r="H642" t="n">
+        <v>0</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr"/>
+      <c r="E643" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" t="n">
+        <v>0</v>
+      </c>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F644" t="n">
+        <v>379</v>
+      </c>
+      <c r="G644" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H644" t="n">
+        <v>2</v>
+      </c>
+      <c r="I644" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F645" t="n">
+        <v>171</v>
+      </c>
+      <c r="G645" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H645" t="n">
+        <v>3</v>
+      </c>
+      <c r="I645" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F646" t="n">
+        <v>822</v>
+      </c>
+      <c r="G646" t="n">
+        <v>0</v>
+      </c>
+      <c r="H646" t="n">
+        <v>0</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F647" t="n">
+        <v>966</v>
+      </c>
+      <c r="G647" t="n">
+        <v>0</v>
+      </c>
+      <c r="H647" t="n">
+        <v>0</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F648" t="n">
+        <v>940</v>
+      </c>
+      <c r="G648" t="n">
+        <v>0</v>
+      </c>
+      <c r="H648" t="n">
+        <v>0</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F649" t="n">
+        <v>356</v>
+      </c>
+      <c r="G649" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H649" t="n">
+        <v>2</v>
+      </c>
+      <c r="I649" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F650" t="n">
+        <v>478</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F651" t="n">
+        <v>484</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0</v>
+      </c>
+      <c r="H651" t="n">
+        <v>0</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F652" t="n">
+        <v>341</v>
+      </c>
+      <c r="G652" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H652" t="n">
+        <v>1</v>
+      </c>
+      <c r="I652" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F653" t="n">
+        <v>481</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0</v>
+      </c>
+      <c r="H653" t="n">
+        <v>0</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F654" t="n">
+        <v>483</v>
+      </c>
+      <c r="G654" t="n">
+        <v>0</v>
+      </c>
+      <c r="H654" t="n">
+        <v>0</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>900</v>
+      </c>
+      <c r="F655" t="n">
+        <v>371</v>
+      </c>
+      <c r="G655" t="n">
+        <v>0</v>
+      </c>
+      <c r="H655" t="n">
+        <v>0</v>
+      </c>
+      <c r="I655" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>900</v>
+      </c>
+      <c r="F656" t="n">
+        <v>494</v>
+      </c>
+      <c r="G656" t="n">
+        <v>0</v>
+      </c>
+      <c r="H656" t="n">
+        <v>0</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>900</v>
+      </c>
+      <c r="F657" t="n">
+        <v>477</v>
+      </c>
+      <c r="G657" t="n">
+        <v>0</v>
+      </c>
+      <c r="H657" t="n">
+        <v>0</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>900</v>
+      </c>
+      <c r="F658" t="n">
+        <v>691</v>
+      </c>
+      <c r="G658" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H658" t="n">
+        <v>2</v>
+      </c>
+      <c r="I658" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>900</v>
+      </c>
+      <c r="F659" t="n">
+        <v>941</v>
+      </c>
+      <c r="G659" t="n">
+        <v>0</v>
+      </c>
+      <c r="H659" t="n">
+        <v>0</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>900</v>
+      </c>
+      <c r="F660" t="n">
+        <v>953</v>
+      </c>
+      <c r="G660" t="n">
+        <v>0</v>
+      </c>
+      <c r="H660" t="n">
+        <v>0</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F661" t="n">
+        <v>896</v>
+      </c>
+      <c r="G661" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H661" t="n">
+        <v>2</v>
+      </c>
+      <c r="I661" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F662" t="n">
+        <v>253</v>
+      </c>
+      <c r="G662" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H662" t="n">
+        <v>1</v>
+      </c>
+      <c r="I662" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F663" t="n">
+        <v>167</v>
+      </c>
+      <c r="G663" t="n">
+        <v>0</v>
+      </c>
+      <c r="H663" t="n">
+        <v>0</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F664" t="n">
+        <v>253</v>
+      </c>
+      <c r="G664" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H664" t="n">
+        <v>1</v>
+      </c>
+      <c r="I664" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F665" t="n">
+        <v>752</v>
+      </c>
+      <c r="G665" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H665" t="n">
+        <v>2</v>
+      </c>
+      <c r="I665" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F666" t="n">
+        <v>316</v>
+      </c>
+      <c r="G666" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H666" t="n">
+        <v>5</v>
+      </c>
+      <c r="I666" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F667" t="n">
+        <v>350</v>
+      </c>
+      <c r="G667" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H667" t="n">
+        <v>4</v>
+      </c>
+      <c r="I667" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F668" t="n">
+        <v>460</v>
+      </c>
+      <c r="G668" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H668" t="n">
+        <v>12</v>
+      </c>
+      <c r="I668" t="n">
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F669" t="n">
+        <v>460</v>
+      </c>
+      <c r="G669" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H669" t="n">
+        <v>12</v>
+      </c>
+      <c r="I669" t="n">
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F670" t="n">
+        <v>752</v>
+      </c>
+      <c r="G670" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H670" t="n">
+        <v>2</v>
+      </c>
+      <c r="I670" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F671" t="n">
+        <v>316</v>
+      </c>
+      <c r="G671" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H671" t="n">
+        <v>5</v>
+      </c>
+      <c r="I671" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F672" t="n">
+        <v>350</v>
+      </c>
+      <c r="G672" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H672" t="n">
+        <v>4</v>
+      </c>
+      <c r="I672" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F673" t="n">
+        <v>460</v>
+      </c>
+      <c r="G673" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H673" t="n">
+        <v>12</v>
+      </c>
+      <c r="I673" t="n">
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F674" t="n">
+        <v>460</v>
+      </c>
+      <c r="G674" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H674" t="n">
+        <v>12</v>
+      </c>
+      <c r="I674" t="n">
+        <v>198000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,6 +776,22 @@
         <v>1523550</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>55</v>
+      </c>
+      <c r="C22" t="n">
+        <v>608300</v>
+      </c>
+      <c r="D22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,34 +806,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="55" customWidth="1" min="22" max="22"/>
+    <col width="48" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
-    <col width="48" customWidth="1" min="25" max="25"/>
+    <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
@@ -835,64 +851,64 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -900,62 +916,62 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1054,16 +1070,16 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -1072,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1081,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1093,25 +1109,25 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>19000</v>
-      </c>
       <c r="R3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S3" t="n">
         <v>6750</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>2500</v>
       </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1120,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1139,25 +1155,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>4</v>
-      </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1169,49 +1185,49 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>45000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>76000</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>2500</v>
       </c>
-      <c r="T4" t="n">
-        <v>4000</v>
-      </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>3000</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2700</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1224,10 +1240,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1239,46 +1255,46 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>90000</v>
       </c>
-      <c r="Q5" t="n">
-        <v>19000</v>
-      </c>
       <c r="R5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S5" t="n">
         <v>2250</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2500</v>
       </c>
-      <c r="T5" t="n">
-        <v>1000</v>
-      </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1287,16 +1303,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1309,22 +1325,22 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -1333,55 +1349,55 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>120000</v>
       </c>
-      <c r="Q6" t="n">
-        <v>19000</v>
-      </c>
       <c r="R6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S6" t="n">
         <v>13500</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>5000</v>
       </c>
-      <c r="T6" t="n">
-        <v>1000</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="V6" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>900</v>
       </c>
-      <c r="Y6" t="n">
-        <v>3000</v>
-      </c>
       <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1394,37 +1410,37 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>31</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
-        <v>8</v>
-      </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1433,37 +1449,37 @@
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>465000</v>
       </c>
-      <c r="Q7" t="n">
-        <v>152000</v>
-      </c>
       <c r="R7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S7" t="n">
         <v>4500</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>10000</v>
       </c>
-      <c r="T7" t="n">
-        <v>8000</v>
-      </c>
       <c r="U7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2000</v>
       </c>
-      <c r="V7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>44000</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1479,25 +1495,25 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
         <v>14</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1506,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1518,16 +1534,16 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>210000</v>
       </c>
-      <c r="Q8" t="n">
-        <v>95000</v>
-      </c>
       <c r="R8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S8" t="n">
         <v>2250</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5000</v>
       </c>
       <c r="T8" t="n">
         <v>5000</v>
@@ -1536,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1545,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1564,37 +1580,37 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
         <v>13</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1603,37 +1619,37 @@
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>195000</v>
       </c>
-      <c r="Q9" t="n">
-        <v>114000</v>
-      </c>
       <c r="R9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S9" t="n">
         <v>15750</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>20000</v>
       </c>
-      <c r="T9" t="n">
-        <v>6000</v>
-      </c>
       <c r="U9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="V9" t="n">
-        <v>900</v>
+        <v>4000</v>
       </c>
       <c r="W9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1649,25 +1665,25 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>55</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1676,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1688,25 +1704,25 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>825000</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4500</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>2500</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="V10" t="n">
-        <v>3600</v>
+        <v>1000</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1715,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1734,25 +1750,25 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1761,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1773,25 +1789,25 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>30000</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>2250</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>2500</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1800,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1819,19 +1835,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1858,34 +1874,34 @@
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>75000</v>
       </c>
-      <c r="Q12" t="n">
-        <v>57000</v>
-      </c>
       <c r="R12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S12" t="n">
         <v>2250</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2500</v>
       </c>
-      <c r="T12" t="n">
-        <v>3000</v>
-      </c>
       <c r="U12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="V12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
         <v>900</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>900</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1904,22 +1920,22 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>12</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>4</v>
       </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1928,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1943,34 +1959,34 @@
         <v>528000</v>
       </c>
       <c r="P13" t="n">
+        <v>228000</v>
+      </c>
+      <c r="Q13" t="n">
         <v>90000</v>
       </c>
-      <c r="Q13" t="n">
-        <v>228000</v>
-      </c>
       <c r="R13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S13" t="n">
         <v>4500</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>10000</v>
       </c>
-      <c r="T13" t="n">
-        <v>12000</v>
-      </c>
       <c r="U13" t="n">
+        <v>900</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>2000</v>
       </c>
-      <c r="V13" t="n">
-        <v>900</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1989,25 +2005,25 @@
         <v>100</v>
       </c>
       <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
         <v>19</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>4</v>
       </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2016,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2028,16 +2044,16 @@
         <v>1650000</v>
       </c>
       <c r="P14" t="n">
+        <v>190000</v>
+      </c>
+      <c r="Q14" t="n">
         <v>285000</v>
       </c>
-      <c r="Q14" t="n">
-        <v>190000</v>
-      </c>
       <c r="R14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S14" t="n">
         <v>15750</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10000</v>
       </c>
       <c r="T14" t="n">
         <v>10000</v>
@@ -2046,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2055,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2074,26 +2090,26 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>16</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -2101,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2113,26 +2129,26 @@
         <v>759000</v>
       </c>
       <c r="P15" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q15" t="n">
         <v>150000</v>
       </c>
-      <c r="Q15" t="n">
-        <v>38000</v>
-      </c>
       <c r="R15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S15" t="n">
         <v>36000</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>7500</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
         <v>2000</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -2140,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2159,25 +2175,25 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
         <v>13</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2186,37 +2202,37 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q16" t="n">
         <v>195000</v>
       </c>
-      <c r="Q16" t="n">
-        <v>95000</v>
-      </c>
       <c r="R16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S16" t="n">
         <v>6750</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>15000</v>
       </c>
-      <c r="T16" t="n">
-        <v>5000</v>
-      </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2225,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2244,79 +2260,79 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
         <v>61</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>30</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
         <v>20</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q17" t="n">
         <v>915000</v>
       </c>
-      <c r="Q17" t="n">
-        <v>38000</v>
-      </c>
       <c r="R17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S17" t="n">
         <v>67500</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>15000</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="V17" t="n">
         <v>2000</v>
       </c>
-      <c r="U17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1800</v>
-      </c>
       <c r="W17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
         <v>20000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2329,25 +2345,25 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2356,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2368,25 +2384,25 @@
         <v>462000</v>
       </c>
       <c r="P18" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q18" t="n">
         <v>90000</v>
       </c>
-      <c r="Q18" t="n">
-        <v>19000</v>
-      </c>
       <c r="R18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S18" t="n">
         <v>6750</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>7500</v>
       </c>
-      <c r="T18" t="n">
-        <v>1000</v>
-      </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -2395,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2414,11 +2430,11 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
@@ -2453,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2499,34 +2515,34 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
         <v>9</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2538,34 +2554,34 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q20" t="n">
         <v>135000</v>
       </c>
-      <c r="Q20" t="n">
-        <v>95000</v>
-      </c>
       <c r="R20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S20" t="n">
         <v>13500</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
       <c r="T20" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>2000</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -2584,37 +2600,37 @@
         <v>70</v>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>22</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
         <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2623,39 +2639,124 @@
         <v>1155000</v>
       </c>
       <c r="P21" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q21" t="n">
         <v>330000</v>
       </c>
-      <c r="Q21" t="n">
-        <v>19000</v>
-      </c>
       <c r="R21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S21" t="n">
         <v>6750</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5000</v>
       </c>
-      <c r="T21" t="n">
-        <v>3000</v>
-      </c>
       <c r="U21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>2000</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>363000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>114000</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>105000</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U22" t="n">
         <v>1800</v>
       </c>
-      <c r="W21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2751,19 +2852,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2202</v>
+      </c>
+      <c r="F2" t="n">
         <v>2205</v>
       </c>
-      <c r="F2" t="n">
-        <v>2214</v>
-      </c>
       <c r="G2" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>135000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="3">
@@ -2786,19 +2887,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>870</v>
+      </c>
+      <c r="F3" t="n">
         <v>874</v>
       </c>
-      <c r="F3" t="n">
-        <v>887</v>
-      </c>
       <c r="G3" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>195000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4">
@@ -2883,19 +2984,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>378</v>
+      </c>
+      <c r="F6" t="n">
         <v>379</v>
       </c>
-      <c r="F6" t="n">
-        <v>381</v>
-      </c>
       <c r="G6" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>5000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
@@ -2918,19 +3019,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
         <v>171</v>
       </c>
-      <c r="F7" t="n">
-        <v>174</v>
-      </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="8">
@@ -3061,16 +3162,16 @@
         <v>356</v>
       </c>
       <c r="F11" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3166,16 +3267,16 @@
         <v>341</v>
       </c>
       <c r="F14" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3373,10 +3474,10 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
+        <v>689</v>
+      </c>
+      <c r="F20" t="n">
         <v>691</v>
-      </c>
-      <c r="F20" t="n">
-        <v>693</v>
       </c>
       <c r="G20" t="n">
         <v>-2</v>
@@ -3478,19 +3579,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>889</v>
+      </c>
+      <c r="F23" t="n">
         <v>896</v>
       </c>
-      <c r="F23" t="n">
-        <v>898</v>
-      </c>
       <c r="G23" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>2000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="24">
@@ -3513,19 +3614,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>247</v>
+      </c>
+      <c r="F24" t="n">
         <v>253</v>
       </c>
-      <c r="F24" t="n">
-        <v>254</v>
-      </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="25">
@@ -3583,19 +3684,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>247</v>
+      </c>
+      <c r="F26" t="n">
         <v>253</v>
       </c>
-      <c r="F26" t="n">
-        <v>254</v>
-      </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>19000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="27">
@@ -3618,19 +3719,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>751</v>
+      </c>
+      <c r="F27" t="n">
         <v>752</v>
       </c>
-      <c r="F27" t="n">
-        <v>754</v>
-      </c>
       <c r="G27" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>33000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="28">
@@ -3656,16 +3757,16 @@
         <v>316</v>
       </c>
       <c r="F28" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G28" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3688,19 +3789,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>348</v>
+      </c>
+      <c r="F29" t="n">
         <v>350</v>
       </c>
-      <c r="F29" t="n">
-        <v>354</v>
-      </c>
       <c r="G29" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>66000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="30">
@@ -3723,19 +3824,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>456</v>
+      </c>
+      <c r="F30" t="n">
         <v>460</v>
       </c>
-      <c r="F30" t="n">
-        <v>472</v>
-      </c>
       <c r="G30" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>198000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="31">
@@ -3758,19 +3859,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>456</v>
+      </c>
+      <c r="F31" t="n">
         <v>460</v>
       </c>
-      <c r="F31" t="n">
-        <v>472</v>
-      </c>
       <c r="G31" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>198000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="32">
@@ -3793,19 +3894,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>751</v>
+      </c>
+      <c r="F32" t="n">
         <v>752</v>
       </c>
-      <c r="F32" t="n">
-        <v>754</v>
-      </c>
       <c r="G32" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>33000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="33">
@@ -3831,16 +3932,16 @@
         <v>316</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G33" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>82500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3863,19 +3964,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>348</v>
+      </c>
+      <c r="F34" t="n">
         <v>350</v>
       </c>
-      <c r="F34" t="n">
-        <v>354</v>
-      </c>
       <c r="G34" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>66000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="35">
@@ -3898,19 +3999,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>456</v>
+      </c>
+      <c r="F35" t="n">
         <v>460</v>
       </c>
-      <c r="F35" t="n">
-        <v>472</v>
-      </c>
       <c r="G35" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>198000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="36">
@@ -3933,19 +4034,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>456</v>
+      </c>
+      <c r="F36" t="n">
         <v>460</v>
       </c>
-      <c r="F36" t="n">
-        <v>472</v>
-      </c>
       <c r="G36" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="H36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>198000</v>
+        <v>66000</v>
       </c>
     </row>
   </sheetData>
@@ -3959,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I674"/>
+  <dimension ref="A1:I709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28637,6 +28738,1293 @@
         <v>198000</v>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F675" t="n">
+        <v>2202</v>
+      </c>
+      <c r="G675" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H675" t="n">
+        <v>3</v>
+      </c>
+      <c r="I675" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F676" t="n">
+        <v>870</v>
+      </c>
+      <c r="G676" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H676" t="n">
+        <v>4</v>
+      </c>
+      <c r="I676" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0</v>
+      </c>
+      <c r="G677" t="n">
+        <v>0</v>
+      </c>
+      <c r="H677" t="n">
+        <v>0</v>
+      </c>
+      <c r="I677" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0</v>
+      </c>
+      <c r="G678" t="n">
+        <v>0</v>
+      </c>
+      <c r="H678" t="n">
+        <v>0</v>
+      </c>
+      <c r="I678" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F679" t="n">
+        <v>378</v>
+      </c>
+      <c r="G679" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H679" t="n">
+        <v>1</v>
+      </c>
+      <c r="I679" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F680" t="n">
+        <v>167</v>
+      </c>
+      <c r="G680" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H680" t="n">
+        <v>4</v>
+      </c>
+      <c r="I680" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F681" t="n">
+        <v>822</v>
+      </c>
+      <c r="G681" t="n">
+        <v>0</v>
+      </c>
+      <c r="H681" t="n">
+        <v>0</v>
+      </c>
+      <c r="I681" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F682" t="n">
+        <v>966</v>
+      </c>
+      <c r="G682" t="n">
+        <v>0</v>
+      </c>
+      <c r="H682" t="n">
+        <v>0</v>
+      </c>
+      <c r="I682" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F683" t="n">
+        <v>940</v>
+      </c>
+      <c r="G683" t="n">
+        <v>0</v>
+      </c>
+      <c r="H683" t="n">
+        <v>0</v>
+      </c>
+      <c r="I683" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F684" t="n">
+        <v>356</v>
+      </c>
+      <c r="G684" t="n">
+        <v>0</v>
+      </c>
+      <c r="H684" t="n">
+        <v>0</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F685" t="n">
+        <v>478</v>
+      </c>
+      <c r="G685" t="n">
+        <v>0</v>
+      </c>
+      <c r="H685" t="n">
+        <v>0</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F686" t="n">
+        <v>484</v>
+      </c>
+      <c r="G686" t="n">
+        <v>0</v>
+      </c>
+      <c r="H686" t="n">
+        <v>0</v>
+      </c>
+      <c r="I686" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F687" t="n">
+        <v>341</v>
+      </c>
+      <c r="G687" t="n">
+        <v>0</v>
+      </c>
+      <c r="H687" t="n">
+        <v>0</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F688" t="n">
+        <v>481</v>
+      </c>
+      <c r="G688" t="n">
+        <v>0</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F689" t="n">
+        <v>483</v>
+      </c>
+      <c r="G689" t="n">
+        <v>0</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>900</v>
+      </c>
+      <c r="F690" t="n">
+        <v>371</v>
+      </c>
+      <c r="G690" t="n">
+        <v>0</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>900</v>
+      </c>
+      <c r="F691" t="n">
+        <v>494</v>
+      </c>
+      <c r="G691" t="n">
+        <v>0</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>900</v>
+      </c>
+      <c r="F692" t="n">
+        <v>477</v>
+      </c>
+      <c r="G692" t="n">
+        <v>0</v>
+      </c>
+      <c r="H692" t="n">
+        <v>0</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>900</v>
+      </c>
+      <c r="F693" t="n">
+        <v>689</v>
+      </c>
+      <c r="G693" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H693" t="n">
+        <v>2</v>
+      </c>
+      <c r="I693" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>900</v>
+      </c>
+      <c r="F694" t="n">
+        <v>941</v>
+      </c>
+      <c r="G694" t="n">
+        <v>0</v>
+      </c>
+      <c r="H694" t="n">
+        <v>0</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>900</v>
+      </c>
+      <c r="F695" t="n">
+        <v>953</v>
+      </c>
+      <c r="G695" t="n">
+        <v>0</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F696" t="n">
+        <v>889</v>
+      </c>
+      <c r="G696" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H696" t="n">
+        <v>7</v>
+      </c>
+      <c r="I696" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F697" t="n">
+        <v>247</v>
+      </c>
+      <c r="G697" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H697" t="n">
+        <v>6</v>
+      </c>
+      <c r="I697" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F698" t="n">
+        <v>167</v>
+      </c>
+      <c r="G698" t="n">
+        <v>0</v>
+      </c>
+      <c r="H698" t="n">
+        <v>0</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F699" t="n">
+        <v>247</v>
+      </c>
+      <c r="G699" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H699" t="n">
+        <v>6</v>
+      </c>
+      <c r="I699" t="n">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F700" t="n">
+        <v>751</v>
+      </c>
+      <c r="G700" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H700" t="n">
+        <v>1</v>
+      </c>
+      <c r="I700" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F701" t="n">
+        <v>316</v>
+      </c>
+      <c r="G701" t="n">
+        <v>0</v>
+      </c>
+      <c r="H701" t="n">
+        <v>0</v>
+      </c>
+      <c r="I701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F702" t="n">
+        <v>348</v>
+      </c>
+      <c r="G702" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H702" t="n">
+        <v>2</v>
+      </c>
+      <c r="I702" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F703" t="n">
+        <v>456</v>
+      </c>
+      <c r="G703" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H703" t="n">
+        <v>4</v>
+      </c>
+      <c r="I703" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F704" t="n">
+        <v>456</v>
+      </c>
+      <c r="G704" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H704" t="n">
+        <v>4</v>
+      </c>
+      <c r="I704" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F705" t="n">
+        <v>751</v>
+      </c>
+      <c r="G705" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H705" t="n">
+        <v>1</v>
+      </c>
+      <c r="I705" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F706" t="n">
+        <v>316</v>
+      </c>
+      <c r="G706" t="n">
+        <v>0</v>
+      </c>
+      <c r="H706" t="n">
+        <v>0</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F707" t="n">
+        <v>348</v>
+      </c>
+      <c r="G707" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H707" t="n">
+        <v>2</v>
+      </c>
+      <c r="I707" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F708" t="n">
+        <v>456</v>
+      </c>
+      <c r="G708" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H708" t="n">
+        <v>4</v>
+      </c>
+      <c r="I708" t="n">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F709" t="n">
+        <v>456</v>
+      </c>
+      <c r="G709" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H709" t="n">
+        <v>4</v>
+      </c>
+      <c r="I709" t="n">
+        <v>66000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -792,6 +792,22 @@
         <v>608300</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>144</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2064050</v>
+      </c>
+      <c r="D23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -806,31 +822,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
-    <col width="48" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
@@ -851,64 +867,64 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -916,62 +932,62 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1070,25 +1086,25 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1109,25 +1125,25 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19000</v>
       </c>
-      <c r="Q3" t="n">
-        <v>45000</v>
-      </c>
       <c r="R3" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="S3" t="n">
-        <v>6750</v>
+        <v>2500</v>
       </c>
       <c r="T3" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1155,34 +1171,34 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1194,34 +1210,34 @@
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>76000</v>
       </c>
-      <c r="Q4" t="n">
-        <v>45000</v>
-      </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T4" t="n">
         <v>4000</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2500</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="X4" t="n">
         <v>3000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1240,10 +1256,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1279,19 +1295,19 @@
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>19000</v>
       </c>
-      <c r="Q5" t="n">
-        <v>90000</v>
-      </c>
       <c r="R5" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="S5" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="T5" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1325,19 +1341,19 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
       <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1346,58 +1362,58 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>19000</v>
       </c>
-      <c r="Q6" t="n">
-        <v>120000</v>
-      </c>
       <c r="R6" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="S6" t="n">
-        <v>13500</v>
+        <v>5000</v>
       </c>
       <c r="T6" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="U6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V6" t="n">
         <v>2700</v>
       </c>
-      <c r="V6" t="n">
-        <v>3000</v>
-      </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1410,79 +1426,79 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
-        <v>31</v>
-      </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>152000</v>
       </c>
-      <c r="Q7" t="n">
-        <v>465000</v>
-      </c>
       <c r="R7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T7" t="n">
         <v>8000</v>
       </c>
-      <c r="S7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="T7" t="n">
-        <v>10000</v>
-      </c>
       <c r="U7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V7" t="n">
         <v>2700</v>
       </c>
-      <c r="V7" t="n">
-        <v>1000</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>44000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1495,25 +1511,25 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
-        <v>14</v>
-      </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1534,25 +1550,25 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>95000</v>
       </c>
-      <c r="Q8" t="n">
-        <v>210000</v>
-      </c>
       <c r="R8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S8" t="n">
         <v>5000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2250</v>
       </c>
       <c r="T8" t="n">
         <v>5000</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1580,79 +1596,79 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>13</v>
-      </c>
       <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
-      </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>114000</v>
       </c>
-      <c r="Q9" t="n">
-        <v>195000</v>
-      </c>
       <c r="R9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="T9" t="n">
         <v>6000</v>
       </c>
-      <c r="S9" t="n">
-        <v>15750</v>
-      </c>
-      <c r="T9" t="n">
-        <v>20000</v>
-      </c>
       <c r="U9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="V9" t="n">
         <v>900</v>
       </c>
-      <c r="V9" t="n">
-        <v>4000</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1665,25 +1681,25 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1704,25 +1720,25 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>825000</v>
       </c>
       <c r="Q10" t="n">
-        <v>825000</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="S10" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="T10" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V10" t="n">
         <v>3600</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1000</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1750,25 +1766,25 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1789,25 +1805,25 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Q11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="S11" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="T11" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1835,19 +1851,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1856,58 +1872,58 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>57000</v>
       </c>
-      <c r="Q12" t="n">
-        <v>75000</v>
-      </c>
       <c r="R12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T12" t="n">
         <v>3000</v>
       </c>
-      <c r="S12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2500</v>
-      </c>
       <c r="U12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V12" t="n">
         <v>900</v>
       </c>
-      <c r="V12" t="n">
-        <v>1000</v>
-      </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -1920,19 +1936,19 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
       <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
         <v>12</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1944,55 +1960,55 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
       </c>
       <c r="P13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q13" t="n">
         <v>228000</v>
       </c>
-      <c r="Q13" t="n">
-        <v>90000</v>
-      </c>
       <c r="R13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T13" t="n">
         <v>12000</v>
       </c>
-      <c r="S13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="T13" t="n">
-        <v>10000</v>
-      </c>
       <c r="U13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V13" t="n">
         <v>900</v>
       </c>
-      <c r="V13" t="n">
-        <v>1000</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2005,25 +2021,25 @@
         <v>100</v>
       </c>
       <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
-        <v>19</v>
-      </c>
       <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>10</v>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4</v>
-      </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2044,25 +2060,25 @@
         <v>1650000</v>
       </c>
       <c r="P14" t="n">
+        <v>285000</v>
+      </c>
+      <c r="Q14" t="n">
         <v>190000</v>
       </c>
-      <c r="Q14" t="n">
-        <v>285000</v>
-      </c>
       <c r="R14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="S14" t="n">
         <v>10000</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15750</v>
       </c>
       <c r="T14" t="n">
         <v>10000</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2090,25 +2106,25 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
       <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
-        <v>16</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3</v>
-      </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2129,25 +2145,25 @@
         <v>759000</v>
       </c>
       <c r="P15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q15" t="n">
         <v>38000</v>
       </c>
-      <c r="Q15" t="n">
-        <v>150000</v>
-      </c>
       <c r="R15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T15" t="n">
         <v>2000</v>
       </c>
-      <c r="S15" t="n">
-        <v>36000</v>
-      </c>
-      <c r="T15" t="n">
-        <v>7500</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2175,32 +2191,32 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
-        <v>13</v>
-      </c>
       <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -2208,38 +2224,38 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q16" t="n">
         <v>95000</v>
       </c>
-      <c r="Q16" t="n">
-        <v>195000</v>
-      </c>
       <c r="R16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T16" t="n">
         <v>5000</v>
       </c>
-      <c r="S16" t="n">
-        <v>6750</v>
-      </c>
-      <c r="T16" t="n">
-        <v>15000</v>
-      </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>2000</v>
       </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
@@ -2247,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2260,19 +2276,19 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>61</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
-        <v>61</v>
-      </c>
       <c r="E17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
@@ -2284,55 +2300,55 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>20</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>915000</v>
+      </c>
+      <c r="Q17" t="n">
         <v>38000</v>
       </c>
-      <c r="Q17" t="n">
-        <v>915000</v>
-      </c>
       <c r="R17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="T17" t="n">
         <v>2000</v>
       </c>
-      <c r="S17" t="n">
-        <v>67500</v>
-      </c>
-      <c r="T17" t="n">
-        <v>15000</v>
-      </c>
       <c r="U17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V17" t="n">
         <v>1800</v>
       </c>
-      <c r="V17" t="n">
-        <v>2000</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -2345,25 +2361,25 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2384,25 +2400,25 @@
         <v>462000</v>
       </c>
       <c r="P18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q18" t="n">
         <v>19000</v>
       </c>
-      <c r="Q18" t="n">
-        <v>90000</v>
-      </c>
       <c r="R18" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="S18" t="n">
-        <v>6750</v>
+        <v>7500</v>
       </c>
       <c r="T18" t="n">
-        <v>7500</v>
+        <v>1000</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -2430,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2469,10 +2485,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="Q19" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2515,79 +2531,79 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
-        <v>9</v>
-      </c>
       <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="Q20" t="n">
         <v>95000</v>
       </c>
-      <c r="Q20" t="n">
-        <v>135000</v>
-      </c>
       <c r="R20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>5000</v>
       </c>
-      <c r="S20" t="n">
-        <v>13500</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V20" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2600,79 +2616,79 @@
         <v>70</v>
       </c>
       <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
         <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>22</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
       </c>
       <c r="P21" t="n">
+        <v>330000</v>
+      </c>
+      <c r="Q21" t="n">
         <v>19000</v>
       </c>
-      <c r="Q21" t="n">
-        <v>330000</v>
-      </c>
       <c r="R21" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T21" t="n">
         <v>3000</v>
       </c>
-      <c r="S21" t="n">
-        <v>6750</v>
-      </c>
-      <c r="T21" t="n">
-        <v>5000</v>
-      </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
         <v>1800</v>
       </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2685,25 +2701,25 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
         <v>6</v>
       </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
       <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
         <v>13</v>
       </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2724,26 +2740,26 @@
         <v>363000</v>
       </c>
       <c r="P22" t="n">
+        <v>105000</v>
+      </c>
+      <c r="Q22" t="n">
         <v>114000</v>
       </c>
-      <c r="Q22" t="n">
-        <v>105000</v>
-      </c>
       <c r="R22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T22" t="n">
         <v>13000</v>
       </c>
-      <c r="S22" t="n">
-        <v>9000</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2500</v>
-      </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
         <v>1800</v>
       </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
@@ -2757,6 +2773,91 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>90</v>
+      </c>
+      <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1485000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>510000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>38000</v>
+      </c>
+      <c r="R23" t="n">
+        <v>15750</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V23" t="n">
+        <v>900</v>
+      </c>
+      <c r="W23" t="n">
+        <v>900</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2852,19 +2953,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2173</v>
+      </c>
+      <c r="F2" t="n">
         <v>2202</v>
       </c>
-      <c r="F2" t="n">
-        <v>2205</v>
-      </c>
       <c r="G2" t="n">
-        <v>-3</v>
+        <v>-29</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>45000</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="3">
@@ -2887,19 +2988,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>865</v>
+      </c>
+      <c r="F3" t="n">
         <v>870</v>
       </c>
-      <c r="F3" t="n">
-        <v>874</v>
-      </c>
       <c r="G3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>60000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="4">
@@ -2984,19 +3085,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>375</v>
+      </c>
+      <c r="F6" t="n">
         <v>378</v>
       </c>
-      <c r="F6" t="n">
-        <v>379</v>
-      </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="7">
@@ -3019,19 +3120,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>160</v>
+      </c>
+      <c r="F7" t="n">
         <v>167</v>
       </c>
-      <c r="F7" t="n">
-        <v>171</v>
-      </c>
       <c r="G7" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>9000</v>
+        <v>15750</v>
       </c>
     </row>
     <row r="8">
@@ -3369,19 +3470,19 @@
         <v>900</v>
       </c>
       <c r="E17" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F17" t="n">
         <v>371</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18">
@@ -3474,19 +3575,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
+        <v>688</v>
+      </c>
+      <c r="F20" t="n">
         <v>689</v>
       </c>
-      <c r="F20" t="n">
-        <v>691</v>
-      </c>
       <c r="G20" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -3579,19 +3680,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>886</v>
+      </c>
+      <c r="F23" t="n">
         <v>889</v>
       </c>
-      <c r="F23" t="n">
-        <v>896</v>
-      </c>
       <c r="G23" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="24">
@@ -3614,19 +3715,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>245</v>
+      </c>
+      <c r="F24" t="n">
         <v>247</v>
       </c>
-      <c r="F24" t="n">
-        <v>253</v>
-      </c>
       <c r="G24" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
@@ -3649,19 +3750,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F25" t="n">
         <v>167</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -3684,19 +3785,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>245</v>
+      </c>
+      <c r="F26" t="n">
         <v>247</v>
       </c>
-      <c r="F26" t="n">
-        <v>253</v>
-      </c>
       <c r="G26" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>114000</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="27">
@@ -3719,19 +3820,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>728</v>
+      </c>
+      <c r="F27" t="n">
         <v>751</v>
       </c>
-      <c r="F27" t="n">
-        <v>752</v>
-      </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>-23</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I27" t="n">
-        <v>16500</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="28">
@@ -3754,19 +3855,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F28" t="n">
         <v>316</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="29">
@@ -3789,19 +3890,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>343</v>
+      </c>
+      <c r="F29" t="n">
         <v>348</v>
       </c>
-      <c r="F29" t="n">
-        <v>350</v>
-      </c>
       <c r="G29" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>33000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="30">
@@ -3824,19 +3925,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>449</v>
+      </c>
+      <c r="F30" t="n">
         <v>456</v>
       </c>
-      <c r="F30" t="n">
-        <v>460</v>
-      </c>
       <c r="G30" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="31">
@@ -3859,19 +3960,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>449</v>
+      </c>
+      <c r="F31" t="n">
         <v>456</v>
       </c>
-      <c r="F31" t="n">
-        <v>460</v>
-      </c>
       <c r="G31" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="32">
@@ -3894,19 +3995,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>728</v>
+      </c>
+      <c r="F32" t="n">
         <v>751</v>
       </c>
-      <c r="F32" t="n">
-        <v>752</v>
-      </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-23</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I32" t="n">
-        <v>16500</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="33">
@@ -3929,19 +4030,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F33" t="n">
         <v>316</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="34">
@@ -3964,19 +4065,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>343</v>
+      </c>
+      <c r="F34" t="n">
         <v>348</v>
       </c>
-      <c r="F34" t="n">
-        <v>350</v>
-      </c>
       <c r="G34" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>33000</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="35">
@@ -3999,19 +4100,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>449</v>
+      </c>
+      <c r="F35" t="n">
         <v>456</v>
       </c>
-      <c r="F35" t="n">
-        <v>460</v>
-      </c>
       <c r="G35" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="36">
@@ -4034,19 +4135,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>449</v>
+      </c>
+      <c r="F36" t="n">
         <v>456</v>
       </c>
-      <c r="F36" t="n">
-        <v>460</v>
-      </c>
       <c r="G36" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>66000</v>
+        <v>115500</v>
       </c>
     </row>
   </sheetData>
@@ -4060,7 +4161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I709"/>
+  <dimension ref="A1:I744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30025,6 +30126,1293 @@
         <v>66000</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F710" t="n">
+        <v>2173</v>
+      </c>
+      <c r="G710" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H710" t="n">
+        <v>29</v>
+      </c>
+      <c r="I710" t="n">
+        <v>435000</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F711" t="n">
+        <v>865</v>
+      </c>
+      <c r="G711" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H711" t="n">
+        <v>5</v>
+      </c>
+      <c r="I711" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" t="n">
+        <v>0</v>
+      </c>
+      <c r="H712" t="n">
+        <v>0</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" t="n">
+        <v>0</v>
+      </c>
+      <c r="H713" t="n">
+        <v>0</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F714" t="n">
+        <v>375</v>
+      </c>
+      <c r="G714" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H714" t="n">
+        <v>3</v>
+      </c>
+      <c r="I714" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F715" t="n">
+        <v>160</v>
+      </c>
+      <c r="G715" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H715" t="n">
+        <v>7</v>
+      </c>
+      <c r="I715" t="n">
+        <v>15750</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F716" t="n">
+        <v>822</v>
+      </c>
+      <c r="G716" t="n">
+        <v>0</v>
+      </c>
+      <c r="H716" t="n">
+        <v>0</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F717" t="n">
+        <v>966</v>
+      </c>
+      <c r="G717" t="n">
+        <v>0</v>
+      </c>
+      <c r="H717" t="n">
+        <v>0</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F718" t="n">
+        <v>940</v>
+      </c>
+      <c r="G718" t="n">
+        <v>0</v>
+      </c>
+      <c r="H718" t="n">
+        <v>0</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F719" t="n">
+        <v>356</v>
+      </c>
+      <c r="G719" t="n">
+        <v>0</v>
+      </c>
+      <c r="H719" t="n">
+        <v>0</v>
+      </c>
+      <c r="I719" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F720" t="n">
+        <v>478</v>
+      </c>
+      <c r="G720" t="n">
+        <v>0</v>
+      </c>
+      <c r="H720" t="n">
+        <v>0</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F721" t="n">
+        <v>484</v>
+      </c>
+      <c r="G721" t="n">
+        <v>0</v>
+      </c>
+      <c r="H721" t="n">
+        <v>0</v>
+      </c>
+      <c r="I721" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F722" t="n">
+        <v>341</v>
+      </c>
+      <c r="G722" t="n">
+        <v>0</v>
+      </c>
+      <c r="H722" t="n">
+        <v>0</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F723" t="n">
+        <v>481</v>
+      </c>
+      <c r="G723" t="n">
+        <v>0</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F724" t="n">
+        <v>483</v>
+      </c>
+      <c r="G724" t="n">
+        <v>0</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>900</v>
+      </c>
+      <c r="F725" t="n">
+        <v>370</v>
+      </c>
+      <c r="G725" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H725" t="n">
+        <v>1</v>
+      </c>
+      <c r="I725" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>900</v>
+      </c>
+      <c r="F726" t="n">
+        <v>494</v>
+      </c>
+      <c r="G726" t="n">
+        <v>0</v>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>900</v>
+      </c>
+      <c r="F727" t="n">
+        <v>477</v>
+      </c>
+      <c r="G727" t="n">
+        <v>0</v>
+      </c>
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>900</v>
+      </c>
+      <c r="F728" t="n">
+        <v>688</v>
+      </c>
+      <c r="G728" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H728" t="n">
+        <v>1</v>
+      </c>
+      <c r="I728" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>900</v>
+      </c>
+      <c r="F729" t="n">
+        <v>941</v>
+      </c>
+      <c r="G729" t="n">
+        <v>0</v>
+      </c>
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>900</v>
+      </c>
+      <c r="F730" t="n">
+        <v>953</v>
+      </c>
+      <c r="G730" t="n">
+        <v>0</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F731" t="n">
+        <v>886</v>
+      </c>
+      <c r="G731" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H731" t="n">
+        <v>3</v>
+      </c>
+      <c r="I731" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F732" t="n">
+        <v>245</v>
+      </c>
+      <c r="G732" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H732" t="n">
+        <v>2</v>
+      </c>
+      <c r="I732" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F733" t="n">
+        <v>166</v>
+      </c>
+      <c r="G733" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H733" t="n">
+        <v>1</v>
+      </c>
+      <c r="I733" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F734" t="n">
+        <v>245</v>
+      </c>
+      <c r="G734" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H734" t="n">
+        <v>2</v>
+      </c>
+      <c r="I734" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F735" t="n">
+        <v>728</v>
+      </c>
+      <c r="G735" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H735" t="n">
+        <v>23</v>
+      </c>
+      <c r="I735" t="n">
+        <v>379500</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F736" t="n">
+        <v>313</v>
+      </c>
+      <c r="G736" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H736" t="n">
+        <v>3</v>
+      </c>
+      <c r="I736" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F737" t="n">
+        <v>343</v>
+      </c>
+      <c r="G737" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H737" t="n">
+        <v>5</v>
+      </c>
+      <c r="I737" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F738" t="n">
+        <v>449</v>
+      </c>
+      <c r="G738" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H738" t="n">
+        <v>7</v>
+      </c>
+      <c r="I738" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F739" t="n">
+        <v>449</v>
+      </c>
+      <c r="G739" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H739" t="n">
+        <v>7</v>
+      </c>
+      <c r="I739" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F740" t="n">
+        <v>728</v>
+      </c>
+      <c r="G740" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H740" t="n">
+        <v>23</v>
+      </c>
+      <c r="I740" t="n">
+        <v>379500</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F741" t="n">
+        <v>313</v>
+      </c>
+      <c r="G741" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H741" t="n">
+        <v>3</v>
+      </c>
+      <c r="I741" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F742" t="n">
+        <v>343</v>
+      </c>
+      <c r="G742" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H742" t="n">
+        <v>5</v>
+      </c>
+      <c r="I742" t="n">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F743" t="n">
+        <v>449</v>
+      </c>
+      <c r="G743" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H743" t="n">
+        <v>7</v>
+      </c>
+      <c r="I743" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F744" t="n">
+        <v>449</v>
+      </c>
+      <c r="G744" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H744" t="n">
+        <v>7</v>
+      </c>
+      <c r="I744" t="n">
+        <v>115500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -808,6 +808,22 @@
         <v>2064050</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>82</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1120500</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -822,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -830,28 +846,28 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="55" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="55" customWidth="1" min="27" max="27"/>
+    <col width="48" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -877,54 +893,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -942,52 +958,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1092,34 +1108,34 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
@@ -1131,16 +1147,16 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T3" t="n">
         <v>6750</v>
       </c>
-      <c r="S3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1158,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -1177,19 +1193,19 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -1216,19 +1232,19 @@
         <v>76000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S4" t="n">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>3000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>2700</v>
@@ -1274,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1289,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
@@ -1301,19 +1317,19 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
         <v>2250</v>
       </c>
-      <c r="S5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1000</v>
-      </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1328,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1347,19 +1363,19 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1371,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1386,19 +1402,19 @@
         <v>19000</v>
       </c>
       <c r="R6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T6" t="n">
         <v>13500</v>
       </c>
-      <c r="S6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1000</v>
-      </c>
       <c r="U6" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>900</v>
@@ -1410,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7">
@@ -1432,34 +1448,34 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8</v>
-      </c>
       <c r="H7" t="n">
+        <v>44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1471,34 +1487,34 @@
         <v>152000</v>
       </c>
       <c r="R7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T7" t="n">
         <v>4500</v>
       </c>
-      <c r="S7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8000</v>
-      </c>
       <c r="U7" t="n">
-        <v>1000</v>
+        <v>44000</v>
       </c>
       <c r="V7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2700</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>44000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -1517,34 +1533,34 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>594000</v>
@@ -1556,34 +1572,34 @@
         <v>95000</v>
       </c>
       <c r="R8" t="n">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
         <v>5000</v>
       </c>
       <c r="T8" t="n">
-        <v>5000</v>
+        <v>2250</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>3000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1618,16 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1623,13 +1639,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1641,34 +1657,34 @@
         <v>114000</v>
       </c>
       <c r="R9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T9" t="n">
         <v>15750</v>
       </c>
-      <c r="S9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6000</v>
-      </c>
       <c r="U9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AA9" t="n">
         <v>4000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>900</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1687,34 +1703,34 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>2359500</v>
@@ -1726,34 +1742,34 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>4500</v>
       </c>
-      <c r="S10" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3600</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -1775,31 +1791,31 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>247500</v>
@@ -1811,16 +1827,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>2250</v>
       </c>
-      <c r="S11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1838,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
@@ -1860,13 +1876,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1881,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1896,19 +1912,19 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T12" t="n">
         <v>2250</v>
       </c>
-      <c r="S12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3000</v>
-      </c>
       <c r="U12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="W12" t="n">
         <v>900</v>
@@ -1920,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -1942,34 +1958,34 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
-      </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="N13" t="n">
         <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
@@ -1981,34 +1997,34 @@
         <v>228000</v>
       </c>
       <c r="R13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T13" t="n">
         <v>4500</v>
       </c>
-      <c r="S13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="T13" t="n">
-        <v>12000</v>
-      </c>
       <c r="U13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>900</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -2027,34 +2043,34 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>1650000</v>
@@ -2066,34 +2082,34 @@
         <v>190000</v>
       </c>
       <c r="R14" t="n">
-        <v>15750</v>
+        <v>10000</v>
       </c>
       <c r="S14" t="n">
         <v>10000</v>
       </c>
       <c r="T14" t="n">
-        <v>10000</v>
+        <v>15750</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2112,34 +2128,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>16</v>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>759000</v>
@@ -2151,34 +2167,34 @@
         <v>38000</v>
       </c>
       <c r="R15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T15" t="n">
         <v>36000</v>
       </c>
-      <c r="S15" t="n">
-        <v>7500</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2000</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2197,16 +2213,16 @@
         <v>5</v>
       </c>
       <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2224,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2236,16 +2252,16 @@
         <v>95000</v>
       </c>
       <c r="R16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T16" t="n">
         <v>6750</v>
       </c>
-      <c r="S16" t="n">
-        <v>15000</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5000</v>
-      </c>
       <c r="U16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2263,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17">
@@ -2282,19 +2298,19 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
         <v>30</v>
       </c>
-      <c r="F17" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2303,13 +2319,13 @@
         <v>20</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2321,19 +2337,19 @@
         <v>38000</v>
       </c>
       <c r="R17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T17" t="n">
         <v>67500</v>
       </c>
-      <c r="S17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2000</v>
-      </c>
       <c r="U17" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="V17" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2342,13 +2358,13 @@
         <v>20000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18">
@@ -2370,31 +2386,31 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
         <v>3</v>
       </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>462000</v>
@@ -2406,34 +2422,34 @@
         <v>19000</v>
       </c>
       <c r="R18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T18" t="n">
         <v>6750</v>
       </c>
-      <c r="S18" t="n">
-        <v>7500</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1000</v>
-      </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2000</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2537,34 +2553,34 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2576,34 +2592,34 @@
         <v>95000</v>
       </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T20" t="n">
         <v>13500</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5000</v>
-      </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3000</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2000</v>
       </c>
     </row>
     <row r="21">
@@ -2622,16 +2638,16 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
         <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -2643,13 +2659,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
@@ -2661,34 +2677,34 @@
         <v>19000</v>
       </c>
       <c r="R21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T21" t="n">
         <v>6750</v>
       </c>
-      <c r="S21" t="n">
-        <v>5000</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3000</v>
-      </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
         <v>1800</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2707,31 +2723,31 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
         <v>4</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>13</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2746,31 +2762,31 @@
         <v>114000</v>
       </c>
       <c r="R22" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S22" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T22" t="n">
         <v>9000</v>
       </c>
-      <c r="S22" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T22" t="n">
-        <v>13000</v>
-      </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1800</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -2792,19 +2808,19 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2816,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>1485000</v>
@@ -2831,19 +2847,19 @@
         <v>38000</v>
       </c>
       <c r="R23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T23" t="n">
         <v>15750</v>
       </c>
-      <c r="S23" t="n">
-        <v>7500</v>
-      </c>
-      <c r="T23" t="n">
-        <v>5000</v>
-      </c>
       <c r="U23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>900</v>
@@ -2855,9 +2871,94 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>54</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>891000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>165000</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>38000</v>
+      </c>
+      <c r="R24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2953,19 +3054,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2165</v>
+      </c>
+      <c r="F2" t="n">
         <v>2173</v>
       </c>
-      <c r="F2" t="n">
-        <v>2202</v>
-      </c>
       <c r="G2" t="n">
-        <v>-29</v>
+        <v>-8</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>435000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="3">
@@ -2988,19 +3089,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>862</v>
+      </c>
+      <c r="F3" t="n">
         <v>865</v>
       </c>
-      <c r="F3" t="n">
-        <v>870</v>
-      </c>
       <c r="G3" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>75000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="4">
@@ -3085,19 +3186,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>369</v>
+      </c>
+      <c r="F6" t="n">
         <v>375</v>
       </c>
-      <c r="F6" t="n">
-        <v>378</v>
-      </c>
       <c r="G6" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="7">
@@ -3120,19 +3221,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>158</v>
+      </c>
+      <c r="F7" t="n">
         <v>160</v>
       </c>
-      <c r="F7" t="n">
-        <v>167</v>
-      </c>
       <c r="G7" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>15750</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -3365,19 +3466,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F14" t="n">
         <v>341</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="15">
@@ -3473,16 +3574,16 @@
         <v>370</v>
       </c>
       <c r="F17" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3578,16 +3679,16 @@
         <v>688</v>
       </c>
       <c r="F20" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3680,10 +3781,10 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>883</v>
+      </c>
+      <c r="F23" t="n">
         <v>886</v>
-      </c>
-      <c r="F23" t="n">
-        <v>889</v>
       </c>
       <c r="G23" t="n">
         <v>-3</v>
@@ -3715,10 +3816,10 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>243</v>
+      </c>
+      <c r="F24" t="n">
         <v>245</v>
-      </c>
-      <c r="F24" t="n">
-        <v>247</v>
       </c>
       <c r="G24" t="n">
         <v>-2</v>
@@ -3753,16 +3854,16 @@
         <v>166</v>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3785,10 +3886,10 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>243</v>
+      </c>
+      <c r="F26" t="n">
         <v>245</v>
-      </c>
-      <c r="F26" t="n">
-        <v>247</v>
       </c>
       <c r="G26" t="n">
         <v>-2</v>
@@ -3823,16 +3924,16 @@
         <v>728</v>
       </c>
       <c r="F27" t="n">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="G27" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>379500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3855,19 +3956,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>312</v>
+      </c>
+      <c r="F28" t="n">
         <v>313</v>
       </c>
-      <c r="F28" t="n">
-        <v>316</v>
-      </c>
       <c r="G28" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>49500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="29">
@@ -3890,19 +3991,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>335</v>
+      </c>
+      <c r="F29" t="n">
         <v>343</v>
       </c>
-      <c r="F29" t="n">
-        <v>348</v>
-      </c>
       <c r="G29" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>82500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="30">
@@ -3925,19 +4026,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>440</v>
+      </c>
+      <c r="F30" t="n">
         <v>449</v>
       </c>
-      <c r="F30" t="n">
-        <v>456</v>
-      </c>
       <c r="G30" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>115500</v>
+        <v>148500</v>
       </c>
     </row>
     <row r="31">
@@ -3960,19 +4061,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>440</v>
+      </c>
+      <c r="F31" t="n">
         <v>449</v>
       </c>
-      <c r="F31" t="n">
-        <v>456</v>
-      </c>
       <c r="G31" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>115500</v>
+        <v>148500</v>
       </c>
     </row>
     <row r="32">
@@ -3998,16 +4099,16 @@
         <v>728</v>
       </c>
       <c r="F32" t="n">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="G32" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>379500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4030,19 +4131,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>312</v>
+      </c>
+      <c r="F33" t="n">
         <v>313</v>
       </c>
-      <c r="F33" t="n">
-        <v>316</v>
-      </c>
       <c r="G33" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>49500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="34">
@@ -4065,19 +4166,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>335</v>
+      </c>
+      <c r="F34" t="n">
         <v>343</v>
       </c>
-      <c r="F34" t="n">
-        <v>348</v>
-      </c>
       <c r="G34" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I34" t="n">
-        <v>82500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="35">
@@ -4100,19 +4201,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>440</v>
+      </c>
+      <c r="F35" t="n">
         <v>449</v>
       </c>
-      <c r="F35" t="n">
-        <v>456</v>
-      </c>
       <c r="G35" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>115500</v>
+        <v>148500</v>
       </c>
     </row>
     <row r="36">
@@ -4135,19 +4236,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>440</v>
+      </c>
+      <c r="F36" t="n">
         <v>449</v>
       </c>
-      <c r="F36" t="n">
-        <v>456</v>
-      </c>
       <c r="G36" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>115500</v>
+        <v>148500</v>
       </c>
     </row>
   </sheetData>
@@ -4161,7 +4262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I744"/>
+  <dimension ref="A1:I779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31413,6 +31514,1293 @@
         <v>115500</v>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F745" t="n">
+        <v>2165</v>
+      </c>
+      <c r="G745" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H745" t="n">
+        <v>8</v>
+      </c>
+      <c r="I745" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F746" t="n">
+        <v>862</v>
+      </c>
+      <c r="G746" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H746" t="n">
+        <v>3</v>
+      </c>
+      <c r="I746" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0</v>
+      </c>
+      <c r="G747" t="n">
+        <v>0</v>
+      </c>
+      <c r="H747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I747" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr"/>
+      <c r="E748" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0</v>
+      </c>
+      <c r="G748" t="n">
+        <v>0</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I748" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F749" t="n">
+        <v>369</v>
+      </c>
+      <c r="G749" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H749" t="n">
+        <v>6</v>
+      </c>
+      <c r="I749" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F750" t="n">
+        <v>158</v>
+      </c>
+      <c r="G750" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H750" t="n">
+        <v>2</v>
+      </c>
+      <c r="I750" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F751" t="n">
+        <v>822</v>
+      </c>
+      <c r="G751" t="n">
+        <v>0</v>
+      </c>
+      <c r="H751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I751" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F752" t="n">
+        <v>966</v>
+      </c>
+      <c r="G752" t="n">
+        <v>0</v>
+      </c>
+      <c r="H752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I752" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F753" t="n">
+        <v>940</v>
+      </c>
+      <c r="G753" t="n">
+        <v>0</v>
+      </c>
+      <c r="H753" t="n">
+        <v>0</v>
+      </c>
+      <c r="I753" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F754" t="n">
+        <v>356</v>
+      </c>
+      <c r="G754" t="n">
+        <v>0</v>
+      </c>
+      <c r="H754" t="n">
+        <v>0</v>
+      </c>
+      <c r="I754" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F755" t="n">
+        <v>478</v>
+      </c>
+      <c r="G755" t="n">
+        <v>0</v>
+      </c>
+      <c r="H755" t="n">
+        <v>0</v>
+      </c>
+      <c r="I755" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F756" t="n">
+        <v>484</v>
+      </c>
+      <c r="G756" t="n">
+        <v>0</v>
+      </c>
+      <c r="H756" t="n">
+        <v>0</v>
+      </c>
+      <c r="I756" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F757" t="n">
+        <v>339</v>
+      </c>
+      <c r="G757" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H757" t="n">
+        <v>2</v>
+      </c>
+      <c r="I757" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F758" t="n">
+        <v>481</v>
+      </c>
+      <c r="G758" t="n">
+        <v>0</v>
+      </c>
+      <c r="H758" t="n">
+        <v>0</v>
+      </c>
+      <c r="I758" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F759" t="n">
+        <v>483</v>
+      </c>
+      <c r="G759" t="n">
+        <v>0</v>
+      </c>
+      <c r="H759" t="n">
+        <v>0</v>
+      </c>
+      <c r="I759" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>900</v>
+      </c>
+      <c r="F760" t="n">
+        <v>370</v>
+      </c>
+      <c r="G760" t="n">
+        <v>0</v>
+      </c>
+      <c r="H760" t="n">
+        <v>0</v>
+      </c>
+      <c r="I760" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>900</v>
+      </c>
+      <c r="F761" t="n">
+        <v>494</v>
+      </c>
+      <c r="G761" t="n">
+        <v>0</v>
+      </c>
+      <c r="H761" t="n">
+        <v>0</v>
+      </c>
+      <c r="I761" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>900</v>
+      </c>
+      <c r="F762" t="n">
+        <v>477</v>
+      </c>
+      <c r="G762" t="n">
+        <v>0</v>
+      </c>
+      <c r="H762" t="n">
+        <v>0</v>
+      </c>
+      <c r="I762" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>900</v>
+      </c>
+      <c r="F763" t="n">
+        <v>688</v>
+      </c>
+      <c r="G763" t="n">
+        <v>0</v>
+      </c>
+      <c r="H763" t="n">
+        <v>0</v>
+      </c>
+      <c r="I763" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>900</v>
+      </c>
+      <c r="F764" t="n">
+        <v>941</v>
+      </c>
+      <c r="G764" t="n">
+        <v>0</v>
+      </c>
+      <c r="H764" t="n">
+        <v>0</v>
+      </c>
+      <c r="I764" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>900</v>
+      </c>
+      <c r="F765" t="n">
+        <v>953</v>
+      </c>
+      <c r="G765" t="n">
+        <v>0</v>
+      </c>
+      <c r="H765" t="n">
+        <v>0</v>
+      </c>
+      <c r="I765" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F766" t="n">
+        <v>883</v>
+      </c>
+      <c r="G766" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H766" t="n">
+        <v>3</v>
+      </c>
+      <c r="I766" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F767" t="n">
+        <v>243</v>
+      </c>
+      <c r="G767" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H767" t="n">
+        <v>2</v>
+      </c>
+      <c r="I767" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F768" t="n">
+        <v>166</v>
+      </c>
+      <c r="G768" t="n">
+        <v>0</v>
+      </c>
+      <c r="H768" t="n">
+        <v>0</v>
+      </c>
+      <c r="I768" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F769" t="n">
+        <v>243</v>
+      </c>
+      <c r="G769" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H769" t="n">
+        <v>2</v>
+      </c>
+      <c r="I769" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F770" t="n">
+        <v>728</v>
+      </c>
+      <c r="G770" t="n">
+        <v>0</v>
+      </c>
+      <c r="H770" t="n">
+        <v>0</v>
+      </c>
+      <c r="I770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F771" t="n">
+        <v>312</v>
+      </c>
+      <c r="G771" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H771" t="n">
+        <v>1</v>
+      </c>
+      <c r="I771" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F772" t="n">
+        <v>335</v>
+      </c>
+      <c r="G772" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H772" t="n">
+        <v>8</v>
+      </c>
+      <c r="I772" t="n">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F773" t="n">
+        <v>440</v>
+      </c>
+      <c r="G773" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H773" t="n">
+        <v>9</v>
+      </c>
+      <c r="I773" t="n">
+        <v>148500</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F774" t="n">
+        <v>440</v>
+      </c>
+      <c r="G774" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H774" t="n">
+        <v>9</v>
+      </c>
+      <c r="I774" t="n">
+        <v>148500</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F775" t="n">
+        <v>728</v>
+      </c>
+      <c r="G775" t="n">
+        <v>0</v>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+      <c r="I775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F776" t="n">
+        <v>312</v>
+      </c>
+      <c r="G776" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H776" t="n">
+        <v>1</v>
+      </c>
+      <c r="I776" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F777" t="n">
+        <v>335</v>
+      </c>
+      <c r="G777" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H777" t="n">
+        <v>8</v>
+      </c>
+      <c r="I777" t="n">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F778" t="n">
+        <v>440</v>
+      </c>
+      <c r="G778" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H778" t="n">
+        <v>9</v>
+      </c>
+      <c r="I778" t="n">
+        <v>148500</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F779" t="n">
+        <v>440</v>
+      </c>
+      <c r="G779" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H779" t="n">
+        <v>9</v>
+      </c>
+      <c r="I779" t="n">
+        <v>148500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -824,6 +824,22 @@
         <v>1120500</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>233450</v>
+      </c>
+      <c r="D25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -838,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -847,27 +863,27 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
-    <col width="48" customWidth="1" min="27" max="27"/>
+    <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -893,54 +909,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -958,52 +974,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1124,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1123,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1135,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>231000</v>
@@ -1147,23 +1163,23 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>2500</v>
       </c>
-      <c r="S3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6750</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
@@ -1174,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1193,34 +1209,34 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -1232,34 +1248,34 @@
         <v>76000</v>
       </c>
       <c r="R4" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="V4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="X4" t="n">
         <v>3000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1284,22 +1300,22 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1317,28 +1333,28 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>2500</v>
       </c>
-      <c r="S5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2250</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
         <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1363,34 +1379,34 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1402,34 +1418,34 @@
         <v>19000</v>
       </c>
       <c r="R6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>900</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W6" t="n">
         <v>5000</v>
       </c>
-      <c r="S6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>13500</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>900</v>
-      </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2000</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
       <c r="Z6" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1448,34 +1464,34 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>44</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1487,34 +1503,34 @@
         <v>152000</v>
       </c>
       <c r="R7" t="n">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="S7" t="n">
         <v>8000</v>
       </c>
       <c r="T7" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
         <v>44000</v>
       </c>
-      <c r="V7" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2700</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1533,13 +1549,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1548,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1560,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>594000</v>
@@ -1572,13 +1588,13 @@
         <v>95000</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>2250</v>
       </c>
       <c r="S8" t="n">
         <v>5000</v>
       </c>
       <c r="T8" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1587,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1599,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1618,25 +1634,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1645,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1657,34 +1673,34 @@
         <v>114000</v>
       </c>
       <c r="R9" t="n">
-        <v>20000</v>
+        <v>15750</v>
       </c>
       <c r="S9" t="n">
         <v>6000</v>
       </c>
       <c r="T9" t="n">
-        <v>15750</v>
+        <v>4000</v>
       </c>
       <c r="U9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1703,22 +1719,22 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1727,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>2359500</v>
@@ -1742,23 +1758,23 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3600</v>
+      </c>
+      <c r="W10" t="n">
         <v>2500</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -1766,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1803,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1815,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>247500</v>
@@ -1827,23 +1843,23 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>2250</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
         <v>2500</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2250</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
@@ -1854,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1882,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1891,16 +1907,16 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
@@ -1912,34 +1928,34 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="S12" t="n">
         <v>3000</v>
       </c>
       <c r="T12" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="V12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="W12" t="n">
-        <v>900</v>
+        <v>2500</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1958,34 +1974,34 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
@@ -1997,34 +2013,34 @@
         <v>228000</v>
       </c>
       <c r="R13" t="n">
-        <v>10000</v>
+        <v>4500</v>
       </c>
       <c r="S13" t="n">
         <v>12000</v>
       </c>
       <c r="T13" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>900</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="X13" t="n">
         <v>2000</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2043,13 +2059,13 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2058,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2070,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>1650000</v>
@@ -2082,13 +2098,13 @@
         <v>190000</v>
       </c>
       <c r="R14" t="n">
-        <v>10000</v>
+        <v>15750</v>
       </c>
       <c r="S14" t="n">
         <v>10000</v>
       </c>
       <c r="T14" t="n">
-        <v>15750</v>
+        <v>2000</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2097,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2109,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2128,13 +2144,13 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2143,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2155,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>759000</v>
@@ -2167,13 +2183,13 @@
         <v>38000</v>
       </c>
       <c r="R15" t="n">
-        <v>7500</v>
+        <v>36000</v>
       </c>
       <c r="S15" t="n">
         <v>2000</v>
       </c>
       <c r="T15" t="n">
-        <v>36000</v>
+        <v>2000</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2182,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2194,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2213,13 +2229,13 @@
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2228,19 +2244,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2252,13 +2268,13 @@
         <v>95000</v>
       </c>
       <c r="R16" t="n">
-        <v>15000</v>
+        <v>6750</v>
       </c>
       <c r="S16" t="n">
         <v>5000</v>
       </c>
       <c r="T16" t="n">
-        <v>6750</v>
+        <v>2000</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2267,19 +2283,19 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>2000</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2298,34 +2314,34 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2337,34 +2353,34 @@
         <v>38000</v>
       </c>
       <c r="R17" t="n">
-        <v>15000</v>
+        <v>67500</v>
       </c>
       <c r="S17" t="n">
         <v>2000</v>
       </c>
       <c r="T17" t="n">
-        <v>67500</v>
+        <v>2000</v>
       </c>
       <c r="U17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
         <v>20000</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2389,17 +2405,17 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
@@ -2410,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>462000</v>
@@ -2422,23 +2438,23 @@
         <v>19000</v>
       </c>
       <c r="R18" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>7500</v>
       </c>
-      <c r="S18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6750</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
@@ -2449,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2553,26 +2569,26 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
@@ -2580,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2592,26 +2608,26 @@
         <v>95000</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="S20" t="n">
         <v>5000</v>
       </c>
       <c r="T20" t="n">
-        <v>13500</v>
+        <v>3000</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>2000</v>
       </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
@@ -2619,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2638,31 +2654,31 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2677,31 +2693,31 @@
         <v>19000</v>
       </c>
       <c r="R21" t="n">
-        <v>5000</v>
+        <v>6750</v>
       </c>
       <c r="S21" t="n">
         <v>3000</v>
       </c>
       <c r="T21" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="X21" t="n">
         <v>2000</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2723,22 +2739,22 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2747,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2762,22 +2778,22 @@
         <v>114000</v>
       </c>
       <c r="R22" t="n">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="S22" t="n">
         <v>13000</v>
       </c>
       <c r="T22" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2786,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -2808,22 +2824,22 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2832,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>1485000</v>
@@ -2847,22 +2863,22 @@
         <v>38000</v>
       </c>
       <c r="R23" t="n">
-        <v>7500</v>
+        <v>15750</v>
       </c>
       <c r="S23" t="n">
         <v>5000</v>
       </c>
       <c r="T23" t="n">
-        <v>15750</v>
+        <v>1000</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W23" t="n">
-        <v>900</v>
+        <v>7500</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2871,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2893,31 +2909,31 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2932,33 +2948,118 @@
         <v>38000</v>
       </c>
       <c r="R24" t="n">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="S24" t="n">
         <v>5000</v>
       </c>
       <c r="T24" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2000</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
       <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>132000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>38000</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6750</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="V25" t="n">
+        <v>900</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3054,19 +3155,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2164</v>
+      </c>
+      <c r="F2" t="n">
         <v>2165</v>
       </c>
-      <c r="F2" t="n">
-        <v>2173</v>
-      </c>
       <c r="G2" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="3">
@@ -3089,19 +3190,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>860</v>
+      </c>
+      <c r="F3" t="n">
         <v>862</v>
       </c>
-      <c r="F3" t="n">
-        <v>865</v>
-      </c>
       <c r="G3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -3189,16 +3290,16 @@
         <v>369</v>
       </c>
       <c r="F6" t="n">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G6" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3221,19 +3322,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>155</v>
+      </c>
+      <c r="F7" t="n">
         <v>158</v>
       </c>
-      <c r="F7" t="n">
-        <v>160</v>
-      </c>
       <c r="G7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>4500</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -3469,16 +3570,16 @@
         <v>339</v>
       </c>
       <c r="F14" t="n">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G14" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3606,19 +3707,19 @@
         <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F18" t="n">
         <v>494</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19">
@@ -3641,19 +3742,19 @@
         <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F19" t="n">
         <v>477</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20">
@@ -3676,19 +3777,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F20" t="n">
         <v>688</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -3781,19 +3882,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>879</v>
+      </c>
+      <c r="F23" t="n">
         <v>883</v>
       </c>
-      <c r="F23" t="n">
-        <v>886</v>
-      </c>
       <c r="G23" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24">
@@ -3816,10 +3917,10 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>241</v>
+      </c>
+      <c r="F24" t="n">
         <v>243</v>
-      </c>
-      <c r="F24" t="n">
-        <v>245</v>
       </c>
       <c r="G24" t="n">
         <v>-2</v>
@@ -3851,19 +3952,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F25" t="n">
         <v>166</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="26">
@@ -3886,10 +3987,10 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>241</v>
+      </c>
+      <c r="F26" t="n">
         <v>243</v>
-      </c>
-      <c r="F26" t="n">
-        <v>245</v>
       </c>
       <c r="G26" t="n">
         <v>-2</v>
@@ -3956,10 +4057,10 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>311</v>
+      </c>
+      <c r="F28" t="n">
         <v>312</v>
-      </c>
-      <c r="F28" t="n">
-        <v>313</v>
       </c>
       <c r="G28" t="n">
         <v>-1</v>
@@ -3991,19 +4092,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>334</v>
+      </c>
+      <c r="F29" t="n">
         <v>335</v>
       </c>
-      <c r="F29" t="n">
-        <v>343</v>
-      </c>
       <c r="G29" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>132000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="30">
@@ -4026,19 +4127,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>439</v>
+      </c>
+      <c r="F30" t="n">
         <v>440</v>
       </c>
-      <c r="F30" t="n">
-        <v>449</v>
-      </c>
       <c r="G30" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>148500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="31">
@@ -4061,19 +4162,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>439</v>
+      </c>
+      <c r="F31" t="n">
         <v>440</v>
       </c>
-      <c r="F31" t="n">
-        <v>449</v>
-      </c>
       <c r="G31" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>148500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="32">
@@ -4131,10 +4232,10 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>311</v>
+      </c>
+      <c r="F33" t="n">
         <v>312</v>
-      </c>
-      <c r="F33" t="n">
-        <v>313</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
@@ -4166,19 +4267,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>334</v>
+      </c>
+      <c r="F34" t="n">
         <v>335</v>
       </c>
-      <c r="F34" t="n">
-        <v>343</v>
-      </c>
       <c r="G34" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>132000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="35">
@@ -4201,19 +4302,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>439</v>
+      </c>
+      <c r="F35" t="n">
         <v>440</v>
       </c>
-      <c r="F35" t="n">
-        <v>449</v>
-      </c>
       <c r="G35" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>148500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="36">
@@ -4236,19 +4337,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>439</v>
+      </c>
+      <c r="F36" t="n">
         <v>440</v>
       </c>
-      <c r="F36" t="n">
-        <v>449</v>
-      </c>
       <c r="G36" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>148500</v>
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
@@ -4262,7 +4363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I779"/>
+  <dimension ref="A1:I814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32801,6 +32902,1293 @@
         <v>148500</v>
       </c>
     </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F780" t="n">
+        <v>2164</v>
+      </c>
+      <c r="G780" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H780" t="n">
+        <v>1</v>
+      </c>
+      <c r="I780" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F781" t="n">
+        <v>860</v>
+      </c>
+      <c r="G781" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H781" t="n">
+        <v>2</v>
+      </c>
+      <c r="I781" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr"/>
+      <c r="E782" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F782" t="n">
+        <v>0</v>
+      </c>
+      <c r="G782" t="n">
+        <v>0</v>
+      </c>
+      <c r="H782" t="n">
+        <v>0</v>
+      </c>
+      <c r="I782" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr"/>
+      <c r="E783" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F783" t="n">
+        <v>0</v>
+      </c>
+      <c r="G783" t="n">
+        <v>0</v>
+      </c>
+      <c r="H783" t="n">
+        <v>0</v>
+      </c>
+      <c r="I783" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F784" t="n">
+        <v>369</v>
+      </c>
+      <c r="G784" t="n">
+        <v>0</v>
+      </c>
+      <c r="H784" t="n">
+        <v>0</v>
+      </c>
+      <c r="I784" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F785" t="n">
+        <v>155</v>
+      </c>
+      <c r="G785" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H785" t="n">
+        <v>3</v>
+      </c>
+      <c r="I785" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F786" t="n">
+        <v>822</v>
+      </c>
+      <c r="G786" t="n">
+        <v>0</v>
+      </c>
+      <c r="H786" t="n">
+        <v>0</v>
+      </c>
+      <c r="I786" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F787" t="n">
+        <v>966</v>
+      </c>
+      <c r="G787" t="n">
+        <v>0</v>
+      </c>
+      <c r="H787" t="n">
+        <v>0</v>
+      </c>
+      <c r="I787" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F788" t="n">
+        <v>940</v>
+      </c>
+      <c r="G788" t="n">
+        <v>0</v>
+      </c>
+      <c r="H788" t="n">
+        <v>0</v>
+      </c>
+      <c r="I788" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F789" t="n">
+        <v>356</v>
+      </c>
+      <c r="G789" t="n">
+        <v>0</v>
+      </c>
+      <c r="H789" t="n">
+        <v>0</v>
+      </c>
+      <c r="I789" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F790" t="n">
+        <v>478</v>
+      </c>
+      <c r="G790" t="n">
+        <v>0</v>
+      </c>
+      <c r="H790" t="n">
+        <v>0</v>
+      </c>
+      <c r="I790" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F791" t="n">
+        <v>484</v>
+      </c>
+      <c r="G791" t="n">
+        <v>0</v>
+      </c>
+      <c r="H791" t="n">
+        <v>0</v>
+      </c>
+      <c r="I791" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F792" t="n">
+        <v>339</v>
+      </c>
+      <c r="G792" t="n">
+        <v>0</v>
+      </c>
+      <c r="H792" t="n">
+        <v>0</v>
+      </c>
+      <c r="I792" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F793" t="n">
+        <v>481</v>
+      </c>
+      <c r="G793" t="n">
+        <v>0</v>
+      </c>
+      <c r="H793" t="n">
+        <v>0</v>
+      </c>
+      <c r="I793" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F794" t="n">
+        <v>483</v>
+      </c>
+      <c r="G794" t="n">
+        <v>0</v>
+      </c>
+      <c r="H794" t="n">
+        <v>0</v>
+      </c>
+      <c r="I794" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>900</v>
+      </c>
+      <c r="F795" t="n">
+        <v>370</v>
+      </c>
+      <c r="G795" t="n">
+        <v>0</v>
+      </c>
+      <c r="H795" t="n">
+        <v>0</v>
+      </c>
+      <c r="I795" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>900</v>
+      </c>
+      <c r="F796" t="n">
+        <v>493</v>
+      </c>
+      <c r="G796" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H796" t="n">
+        <v>1</v>
+      </c>
+      <c r="I796" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>900</v>
+      </c>
+      <c r="F797" t="n">
+        <v>476</v>
+      </c>
+      <c r="G797" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H797" t="n">
+        <v>1</v>
+      </c>
+      <c r="I797" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>900</v>
+      </c>
+      <c r="F798" t="n">
+        <v>687</v>
+      </c>
+      <c r="G798" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H798" t="n">
+        <v>1</v>
+      </c>
+      <c r="I798" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>900</v>
+      </c>
+      <c r="F799" t="n">
+        <v>941</v>
+      </c>
+      <c r="G799" t="n">
+        <v>0</v>
+      </c>
+      <c r="H799" t="n">
+        <v>0</v>
+      </c>
+      <c r="I799" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>900</v>
+      </c>
+      <c r="F800" t="n">
+        <v>953</v>
+      </c>
+      <c r="G800" t="n">
+        <v>0</v>
+      </c>
+      <c r="H800" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F801" t="n">
+        <v>879</v>
+      </c>
+      <c r="G801" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H801" t="n">
+        <v>4</v>
+      </c>
+      <c r="I801" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F802" t="n">
+        <v>241</v>
+      </c>
+      <c r="G802" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H802" t="n">
+        <v>2</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F803" t="n">
+        <v>163</v>
+      </c>
+      <c r="G803" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H803" t="n">
+        <v>3</v>
+      </c>
+      <c r="I803" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F804" t="n">
+        <v>241</v>
+      </c>
+      <c r="G804" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H804" t="n">
+        <v>2</v>
+      </c>
+      <c r="I804" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F805" t="n">
+        <v>728</v>
+      </c>
+      <c r="G805" t="n">
+        <v>0</v>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+      <c r="I805" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F806" t="n">
+        <v>311</v>
+      </c>
+      <c r="G806" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H806" t="n">
+        <v>1</v>
+      </c>
+      <c r="I806" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F807" t="n">
+        <v>334</v>
+      </c>
+      <c r="G807" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H807" t="n">
+        <v>1</v>
+      </c>
+      <c r="I807" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F808" t="n">
+        <v>439</v>
+      </c>
+      <c r="G808" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H808" t="n">
+        <v>1</v>
+      </c>
+      <c r="I808" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F809" t="n">
+        <v>439</v>
+      </c>
+      <c r="G809" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H809" t="n">
+        <v>1</v>
+      </c>
+      <c r="I809" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F810" t="n">
+        <v>728</v>
+      </c>
+      <c r="G810" t="n">
+        <v>0</v>
+      </c>
+      <c r="H810" t="n">
+        <v>0</v>
+      </c>
+      <c r="I810" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F811" t="n">
+        <v>311</v>
+      </c>
+      <c r="G811" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H811" t="n">
+        <v>1</v>
+      </c>
+      <c r="I811" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F812" t="n">
+        <v>334</v>
+      </c>
+      <c r="G812" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H812" t="n">
+        <v>1</v>
+      </c>
+      <c r="I812" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F813" t="n">
+        <v>439</v>
+      </c>
+      <c r="G813" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H813" t="n">
+        <v>1</v>
+      </c>
+      <c r="I813" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F814" t="n">
+        <v>439</v>
+      </c>
+      <c r="G814" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H814" t="n">
+        <v>1</v>
+      </c>
+      <c r="I814" t="n">
+        <v>16500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,22 @@
         <v>233450</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" t="n">
+        <v>316500</v>
+      </c>
+      <c r="D26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -854,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -863,26 +879,26 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="48" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="55" customWidth="1" min="26" max="26"/>
+    <col width="48" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -909,54 +925,54 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -974,52 +990,52 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1124,31 +1140,31 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1163,22 +1179,22 @@
         <v>19000</v>
       </c>
       <c r="R3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>6750</v>
       </c>
-      <c r="S3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1187,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1209,7 +1225,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
@@ -1218,13 +1234,13 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -1233,7 +1249,7 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1248,22 +1264,22 @@
         <v>76000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S4" t="n">
         <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="U4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>3000</v>
@@ -1272,7 +1288,7 @@
         <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1303,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -1333,22 +1349,22 @@
         <v>19000</v>
       </c>
       <c r="R5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>2250</v>
       </c>
-      <c r="S5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1379,31 +1395,31 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1418,31 +1434,31 @@
         <v>19000</v>
       </c>
       <c r="R6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>900</v>
+      </c>
+      <c r="U6" t="n">
         <v>13500</v>
       </c>
-      <c r="S6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>900</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="W6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1464,34 +1480,34 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1503,34 +1519,34 @@
         <v>152000</v>
       </c>
       <c r="R7" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="S7" t="n">
         <v>8000</v>
       </c>
       <c r="T7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
         <v>2700</v>
       </c>
-      <c r="W7" t="n">
-        <v>10000</v>
-      </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2000</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
         <v>44000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1549,31 +1565,31 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1588,31 +1604,31 @@
         <v>95000</v>
       </c>
       <c r="R8" t="n">
-        <v>2250</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
         <v>5000</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3000</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1634,34 +1650,34 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="N9" t="n">
         <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1673,34 +1689,34 @@
         <v>114000</v>
       </c>
       <c r="R9" t="n">
-        <v>15750</v>
+        <v>20000</v>
       </c>
       <c r="S9" t="n">
         <v>6000</v>
       </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>900</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
         <v>4000</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>900</v>
-      </c>
-      <c r="W9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1719,31 +1735,31 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1758,23 +1774,23 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>4500</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
         <v>3600</v>
       </c>
-      <c r="W10" t="n">
-        <v>2500</v>
-      </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
@@ -1782,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1810,25 +1826,25 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1843,22 +1859,22 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>2250</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1867,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1901,19 +1917,19 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1928,31 +1944,31 @@
         <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="S12" t="n">
         <v>3000</v>
       </c>
       <c r="T12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>900</v>
       </c>
-      <c r="V12" t="n">
-        <v>900</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2500</v>
-      </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1974,31 +1990,31 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2013,31 +2029,31 @@
         <v>228000</v>
       </c>
       <c r="R13" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="S13" t="n">
         <v>12000</v>
       </c>
       <c r="T13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>900</v>
       </c>
-      <c r="W13" t="n">
-        <v>10000</v>
-      </c>
       <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2000</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2059,31 +2075,31 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2098,31 +2114,31 @@
         <v>190000</v>
       </c>
       <c r="R14" t="n">
-        <v>15750</v>
+        <v>10000</v>
       </c>
       <c r="S14" t="n">
         <v>10000</v>
       </c>
       <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2000</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2144,31 +2160,31 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2183,31 +2199,31 @@
         <v>38000</v>
       </c>
       <c r="R15" t="n">
-        <v>36000</v>
+        <v>7500</v>
       </c>
       <c r="S15" t="n">
         <v>2000</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2000</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>7500</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2229,31 +2245,31 @@
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2268,31 +2284,31 @@
         <v>95000</v>
       </c>
       <c r="R16" t="n">
-        <v>6750</v>
+        <v>15000</v>
       </c>
       <c r="S16" t="n">
         <v>5000</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>2000</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>15000</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2314,34 +2330,34 @@
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>20</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2353,34 +2369,34 @@
         <v>38000</v>
       </c>
       <c r="R17" t="n">
-        <v>67500</v>
+        <v>15000</v>
       </c>
       <c r="S17" t="n">
         <v>2000</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="X17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
         <v>2000</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="W17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -2405,25 +2421,25 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2438,31 +2454,31 @@
         <v>19000</v>
       </c>
       <c r="R18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>6750</v>
       </c>
-      <c r="S18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2000</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>7500</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2569,31 +2585,31 @@
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
         <v>3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2608,31 +2624,31 @@
         <v>95000</v>
       </c>
       <c r="R20" t="n">
-        <v>13500</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>5000</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3000</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2654,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -2663,25 +2679,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
@@ -2693,7 +2709,7 @@
         <v>19000</v>
       </c>
       <c r="R21" t="n">
-        <v>6750</v>
+        <v>5000</v>
       </c>
       <c r="S21" t="n">
         <v>3000</v>
@@ -2702,25 +2718,25 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>1800</v>
       </c>
-      <c r="W21" t="n">
-        <v>5000</v>
-      </c>
       <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>2000</v>
       </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="22">
@@ -2739,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>13</v>
@@ -2748,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2778,7 +2794,7 @@
         <v>114000</v>
       </c>
       <c r="R22" t="n">
-        <v>9000</v>
+        <v>2500</v>
       </c>
       <c r="S22" t="n">
         <v>13000</v>
@@ -2787,13 +2803,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>1800</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2500</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2824,7 +2840,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -2833,22 +2849,22 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2863,23 +2879,23 @@
         <v>38000</v>
       </c>
       <c r="R23" t="n">
-        <v>15750</v>
+        <v>7500</v>
       </c>
       <c r="S23" t="n">
         <v>5000</v>
       </c>
       <c r="T23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="U23" t="n">
+        <v>15750</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>900</v>
       </c>
-      <c r="V23" t="n">
-        <v>900</v>
-      </c>
-      <c r="W23" t="n">
-        <v>7500</v>
-      </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
@@ -2887,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2909,7 +2925,7 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -2918,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2933,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>891000</v>
@@ -2948,7 +2964,7 @@
         <v>38000</v>
       </c>
       <c r="R24" t="n">
-        <v>4500</v>
+        <v>15000</v>
       </c>
       <c r="S24" t="n">
         <v>5000</v>
@@ -2957,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2972,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2994,23 +3010,23 @@
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
@@ -3018,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3033,33 +3049,118 @@
         <v>38000</v>
       </c>
       <c r="R25" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>6000</v>
       </c>
       <c r="T25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="U25" t="n">
+        <v>6750</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>900</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3000</v>
       </c>
-      <c r="U25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="V25" t="n">
-        <v>900</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
       <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>264000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3155,10 +3256,10 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>2163</v>
+      </c>
+      <c r="F2" t="n">
         <v>2164</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2165</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
@@ -3190,19 +3291,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>859</v>
+      </c>
+      <c r="F3" t="n">
         <v>860</v>
       </c>
-      <c r="F3" t="n">
-        <v>862</v>
-      </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4">
@@ -3287,19 +3388,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F6" t="n">
         <v>369</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
@@ -3325,16 +3426,16 @@
         <v>155</v>
       </c>
       <c r="F7" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3710,16 +3811,16 @@
         <v>493</v>
       </c>
       <c r="F18" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3745,16 +3846,16 @@
         <v>476</v>
       </c>
       <c r="F19" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3780,16 +3881,16 @@
         <v>687</v>
       </c>
       <c r="F20" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3885,16 +3986,16 @@
         <v>879</v>
       </c>
       <c r="F23" t="n">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="G23" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3917,19 +4018,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>240</v>
+      </c>
+      <c r="F24" t="n">
         <v>241</v>
       </c>
-      <c r="F24" t="n">
-        <v>243</v>
-      </c>
       <c r="G24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -3955,16 +4056,16 @@
         <v>163</v>
       </c>
       <c r="F25" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3987,19 +4088,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>240</v>
+      </c>
+      <c r="F26" t="n">
         <v>241</v>
       </c>
-      <c r="F26" t="n">
-        <v>243</v>
-      </c>
       <c r="G26" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>38000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -4060,16 +4161,16 @@
         <v>311</v>
       </c>
       <c r="F28" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4092,19 +4193,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>332</v>
+      </c>
+      <c r="F29" t="n">
         <v>334</v>
       </c>
-      <c r="F29" t="n">
-        <v>335</v>
-      </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>16500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="30">
@@ -4127,19 +4228,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>436</v>
+      </c>
+      <c r="F30" t="n">
         <v>439</v>
       </c>
-      <c r="F30" t="n">
-        <v>440</v>
-      </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>16500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="31">
@@ -4162,19 +4263,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>436</v>
+      </c>
+      <c r="F31" t="n">
         <v>439</v>
       </c>
-      <c r="F31" t="n">
-        <v>440</v>
-      </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>16500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="32">
@@ -4235,16 +4336,16 @@
         <v>311</v>
       </c>
       <c r="F33" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4267,19 +4368,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>332</v>
+      </c>
+      <c r="F34" t="n">
         <v>334</v>
       </c>
-      <c r="F34" t="n">
-        <v>335</v>
-      </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>16500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="35">
@@ -4302,19 +4403,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>436</v>
+      </c>
+      <c r="F35" t="n">
         <v>439</v>
       </c>
-      <c r="F35" t="n">
-        <v>440</v>
-      </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>16500</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="36">
@@ -4337,19 +4438,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>436</v>
+      </c>
+      <c r="F36" t="n">
         <v>439</v>
       </c>
-      <c r="F36" t="n">
-        <v>440</v>
-      </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>16500</v>
+        <v>49500</v>
       </c>
     </row>
   </sheetData>
@@ -4363,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I814"/>
+  <dimension ref="A1:I849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -34189,6 +34290,1293 @@
         <v>16500</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F815" t="n">
+        <v>2163</v>
+      </c>
+      <c r="G815" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H815" t="n">
+        <v>1</v>
+      </c>
+      <c r="I815" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F816" t="n">
+        <v>859</v>
+      </c>
+      <c r="G816" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H816" t="n">
+        <v>1</v>
+      </c>
+      <c r="I816" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0</v>
+      </c>
+      <c r="G817" t="n">
+        <v>0</v>
+      </c>
+      <c r="H817" t="n">
+        <v>0</v>
+      </c>
+      <c r="I817" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0</v>
+      </c>
+      <c r="H818" t="n">
+        <v>0</v>
+      </c>
+      <c r="I818" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F819" t="n">
+        <v>368</v>
+      </c>
+      <c r="G819" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H819" t="n">
+        <v>1</v>
+      </c>
+      <c r="I819" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F820" t="n">
+        <v>155</v>
+      </c>
+      <c r="G820" t="n">
+        <v>0</v>
+      </c>
+      <c r="H820" t="n">
+        <v>0</v>
+      </c>
+      <c r="I820" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F821" t="n">
+        <v>822</v>
+      </c>
+      <c r="G821" t="n">
+        <v>0</v>
+      </c>
+      <c r="H821" t="n">
+        <v>0</v>
+      </c>
+      <c r="I821" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F822" t="n">
+        <v>966</v>
+      </c>
+      <c r="G822" t="n">
+        <v>0</v>
+      </c>
+      <c r="H822" t="n">
+        <v>0</v>
+      </c>
+      <c r="I822" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F823" t="n">
+        <v>940</v>
+      </c>
+      <c r="G823" t="n">
+        <v>0</v>
+      </c>
+      <c r="H823" t="n">
+        <v>0</v>
+      </c>
+      <c r="I823" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F824" t="n">
+        <v>356</v>
+      </c>
+      <c r="G824" t="n">
+        <v>0</v>
+      </c>
+      <c r="H824" t="n">
+        <v>0</v>
+      </c>
+      <c r="I824" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F825" t="n">
+        <v>478</v>
+      </c>
+      <c r="G825" t="n">
+        <v>0</v>
+      </c>
+      <c r="H825" t="n">
+        <v>0</v>
+      </c>
+      <c r="I825" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F826" t="n">
+        <v>484</v>
+      </c>
+      <c r="G826" t="n">
+        <v>0</v>
+      </c>
+      <c r="H826" t="n">
+        <v>0</v>
+      </c>
+      <c r="I826" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F827" t="n">
+        <v>339</v>
+      </c>
+      <c r="G827" t="n">
+        <v>0</v>
+      </c>
+      <c r="H827" t="n">
+        <v>0</v>
+      </c>
+      <c r="I827" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F828" t="n">
+        <v>481</v>
+      </c>
+      <c r="G828" t="n">
+        <v>0</v>
+      </c>
+      <c r="H828" t="n">
+        <v>0</v>
+      </c>
+      <c r="I828" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F829" t="n">
+        <v>483</v>
+      </c>
+      <c r="G829" t="n">
+        <v>0</v>
+      </c>
+      <c r="H829" t="n">
+        <v>0</v>
+      </c>
+      <c r="I829" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>900</v>
+      </c>
+      <c r="F830" t="n">
+        <v>370</v>
+      </c>
+      <c r="G830" t="n">
+        <v>0</v>
+      </c>
+      <c r="H830" t="n">
+        <v>0</v>
+      </c>
+      <c r="I830" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E831" t="n">
+        <v>900</v>
+      </c>
+      <c r="F831" t="n">
+        <v>493</v>
+      </c>
+      <c r="G831" t="n">
+        <v>0</v>
+      </c>
+      <c r="H831" t="n">
+        <v>0</v>
+      </c>
+      <c r="I831" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E832" t="n">
+        <v>900</v>
+      </c>
+      <c r="F832" t="n">
+        <v>476</v>
+      </c>
+      <c r="G832" t="n">
+        <v>0</v>
+      </c>
+      <c r="H832" t="n">
+        <v>0</v>
+      </c>
+      <c r="I832" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E833" t="n">
+        <v>900</v>
+      </c>
+      <c r="F833" t="n">
+        <v>687</v>
+      </c>
+      <c r="G833" t="n">
+        <v>0</v>
+      </c>
+      <c r="H833" t="n">
+        <v>0</v>
+      </c>
+      <c r="I833" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E834" t="n">
+        <v>900</v>
+      </c>
+      <c r="F834" t="n">
+        <v>941</v>
+      </c>
+      <c r="G834" t="n">
+        <v>0</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E835" t="n">
+        <v>900</v>
+      </c>
+      <c r="F835" t="n">
+        <v>953</v>
+      </c>
+      <c r="G835" t="n">
+        <v>0</v>
+      </c>
+      <c r="H835" t="n">
+        <v>0</v>
+      </c>
+      <c r="I835" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E836" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F836" t="n">
+        <v>879</v>
+      </c>
+      <c r="G836" t="n">
+        <v>0</v>
+      </c>
+      <c r="H836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I836" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E837" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F837" t="n">
+        <v>240</v>
+      </c>
+      <c r="G837" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H837" t="n">
+        <v>1</v>
+      </c>
+      <c r="I837" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E838" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F838" t="n">
+        <v>163</v>
+      </c>
+      <c r="G838" t="n">
+        <v>0</v>
+      </c>
+      <c r="H838" t="n">
+        <v>0</v>
+      </c>
+      <c r="I838" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E839" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F839" t="n">
+        <v>240</v>
+      </c>
+      <c r="G839" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H839" t="n">
+        <v>1</v>
+      </c>
+      <c r="I839" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E840" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F840" t="n">
+        <v>728</v>
+      </c>
+      <c r="G840" t="n">
+        <v>0</v>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E841" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F841" t="n">
+        <v>311</v>
+      </c>
+      <c r="G841" t="n">
+        <v>0</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E842" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F842" t="n">
+        <v>332</v>
+      </c>
+      <c r="G842" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H842" t="n">
+        <v>2</v>
+      </c>
+      <c r="I842" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E843" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F843" t="n">
+        <v>436</v>
+      </c>
+      <c r="G843" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H843" t="n">
+        <v>3</v>
+      </c>
+      <c r="I843" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F844" t="n">
+        <v>436</v>
+      </c>
+      <c r="G844" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H844" t="n">
+        <v>3</v>
+      </c>
+      <c r="I844" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F845" t="n">
+        <v>728</v>
+      </c>
+      <c r="G845" t="n">
+        <v>0</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F846" t="n">
+        <v>311</v>
+      </c>
+      <c r="G846" t="n">
+        <v>0</v>
+      </c>
+      <c r="H846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F847" t="n">
+        <v>332</v>
+      </c>
+      <c r="G847" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H847" t="n">
+        <v>2</v>
+      </c>
+      <c r="I847" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F848" t="n">
+        <v>436</v>
+      </c>
+      <c r="G848" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H848" t="n">
+        <v>3</v>
+      </c>
+      <c r="I848" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F849" t="n">
+        <v>436</v>
+      </c>
+      <c r="G849" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H849" t="n">
+        <v>3</v>
+      </c>
+      <c r="I849" t="n">
+        <v>49500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -856,6 +856,22 @@
         <v>316500</v>
       </c>
       <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2978</v>
+      </c>
+      <c r="C27" t="n">
+        <v>46118400</v>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -870,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -880,12 +896,12 @@
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
@@ -893,12 +909,12 @@
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="45" customWidth="1" min="19" max="19"/>
     <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
-    <col width="48" customWidth="1" min="26" max="26"/>
+    <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
@@ -935,44 +951,44 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -1000,42 +1016,42 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1164,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1185,10 +1201,10 @@
         <v>1000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="U3" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1203,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1231,28 +1247,28 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -1270,28 +1286,28 @@
         <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="5">
@@ -1316,19 +1332,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -1355,19 +1371,19 @@
         <v>1000</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="U5" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1401,28 +1417,28 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
@@ -1440,28 +1456,28 @@
         <v>1000</v>
       </c>
       <c r="T6" t="n">
+        <v>13500</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>900</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13500</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1486,28 +1502,28 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1525,28 +1541,28 @@
         <v>8000</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U7" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="W7" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="Y7" t="n">
         <v>2000</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1571,10 +1587,10 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1589,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1610,10 +1626,10 @@
         <v>5000</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="U8" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1628,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1656,28 +1672,28 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1695,28 +1711,28 @@
         <v>6000</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>15750</v>
       </c>
       <c r="U9" t="n">
-        <v>15750</v>
+        <v>4000</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1741,16 +1757,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1759,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1780,16 +1796,16 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U10" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="W10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1798,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1826,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1844,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1865,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="U11" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1883,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1917,10 +1933,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1929,10 +1945,10 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
@@ -1950,28 +1966,28 @@
         <v>3000</v>
       </c>
       <c r="T12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V12" t="n">
         <v>900</v>
       </c>
-      <c r="U12" t="n">
-        <v>2250</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>900</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1996,16 +2012,16 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2014,7 +2030,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2035,16 +2051,16 @@
         <v>12000</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U13" t="n">
-        <v>4500</v>
+        <v>1000</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2053,7 +2069,7 @@
         <v>2000</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2081,10 +2097,10 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2099,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2120,10 +2136,10 @@
         <v>10000</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>15750</v>
       </c>
       <c r="U14" t="n">
-        <v>15750</v>
+        <v>2000</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2138,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2166,10 +2182,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2184,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2205,10 +2221,10 @@
         <v>2000</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="U15" t="n">
-        <v>36000</v>
+        <v>2000</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2223,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2251,25 +2267,25 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2290,25 +2306,25 @@
         <v>5000</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="U16" t="n">
-        <v>6750</v>
+        <v>2000</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2336,28 +2352,28 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2375,28 +2391,28 @@
         <v>2000</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>67500</v>
       </c>
       <c r="U17" t="n">
-        <v>67500</v>
+        <v>2000</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W17" t="n">
-        <v>1800</v>
+        <v>20000</v>
       </c>
       <c r="X17" t="n">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2421,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2439,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2460,10 +2476,10 @@
         <v>1000</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="U18" t="n">
-        <v>6750</v>
+        <v>2000</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2478,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2591,10 +2607,10 @@
         <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2609,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2630,10 +2646,10 @@
         <v>5000</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="U20" t="n">
-        <v>13500</v>
+        <v>3000</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2648,7 +2664,7 @@
         <v>2000</v>
       </c>
       <c r="Z20" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2676,19 +2692,19 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
@@ -2697,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
@@ -2715,19 +2731,19 @@
         <v>3000</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="U21" t="n">
-        <v>6750</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W21" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
         <v>2000</v>
@@ -2736,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2761,16 +2777,16 @@
         <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2800,16 +2816,16 @@
         <v>13000</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="U22" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W22" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2846,28 +2862,28 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>7</v>
-      </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>1485000</v>
@@ -2885,28 +2901,28 @@
         <v>5000</v>
       </c>
       <c r="T23" t="n">
+        <v>15750</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V23" t="n">
         <v>900</v>
       </c>
-      <c r="U23" t="n">
-        <v>15750</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>900</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2931,20 +2947,20 @@
         <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
@@ -2952,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>891000</v>
@@ -2970,10 +2986,10 @@
         <v>5000</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="U24" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2982,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2991,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3016,16 +3032,16 @@
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3034,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>132000</v>
@@ -3055,28 +3071,28 @@
         <v>6000</v>
       </c>
       <c r="T25" t="n">
+        <v>6750</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V25" t="n">
+        <v>900</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1800</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6750</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>900</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3161,6 +3177,91 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2084</v>
+      </c>
+      <c r="C27" t="n">
+        <v>649</v>
+      </c>
+      <c r="D27" t="n">
+        <v>91</v>
+      </c>
+      <c r="E27" t="n">
+        <v>73</v>
+      </c>
+      <c r="F27" t="n">
+        <v>74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>34386000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9735000</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="R27" t="n">
+        <v>182500</v>
+      </c>
+      <c r="S27" t="n">
+        <v>74000</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>900</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3256,19 +3357,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>1547</v>
+      </c>
+      <c r="F2" t="n">
         <v>2163</v>
       </c>
-      <c r="F2" t="n">
-        <v>2164</v>
-      </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>-616</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>616</v>
       </c>
       <c r="I2" t="n">
-        <v>15000</v>
+        <v>9240000</v>
       </c>
     </row>
     <row r="3">
@@ -3291,19 +3392,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>826</v>
+      </c>
+      <c r="F3" t="n">
         <v>859</v>
       </c>
-      <c r="F3" t="n">
-        <v>860</v>
-      </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>-33</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I3" t="n">
-        <v>15000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="4">
@@ -3388,19 +3489,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>295</v>
+      </c>
+      <c r="F6" t="n">
         <v>368</v>
       </c>
-      <c r="F6" t="n">
-        <v>369</v>
-      </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-73</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
-        <v>2500</v>
+        <v>182500</v>
       </c>
     </row>
     <row r="7">
@@ -3423,19 +3524,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F7" t="n">
         <v>155</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="8">
@@ -3878,19 +3979,19 @@
         <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F20" t="n">
         <v>687</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
@@ -3983,19 +4084,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
-        <v>879</v>
+        <v>811</v>
       </c>
       <c r="F23" t="n">
         <v>879</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="24">
@@ -4018,19 +4119,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>234</v>
+      </c>
+      <c r="F24" t="n">
         <v>240</v>
       </c>
-      <c r="F24" t="n">
-        <v>241</v>
-      </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="25">
@@ -4053,19 +4154,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F25" t="n">
         <v>163</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
@@ -4088,19 +4189,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>149</v>
+      </c>
+      <c r="F26" t="n">
         <v>240</v>
       </c>
-      <c r="F26" t="n">
-        <v>241</v>
-      </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-91</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="I26" t="n">
-        <v>19000</v>
+        <v>1729000</v>
       </c>
     </row>
     <row r="27">
@@ -4123,19 +4224,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
-        <v>728</v>
+        <v>294</v>
       </c>
       <c r="F27" t="n">
         <v>728</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-434</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7161000</v>
       </c>
     </row>
     <row r="28">
@@ -4158,19 +4259,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F28" t="n">
         <v>311</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="29">
@@ -4193,19 +4294,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>149</v>
+      </c>
+      <c r="F29" t="n">
         <v>332</v>
       </c>
-      <c r="F29" t="n">
-        <v>334</v>
-      </c>
       <c r="G29" t="n">
-        <v>-2</v>
+        <v>-183</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="I29" t="n">
-        <v>33000</v>
+        <v>3019500</v>
       </c>
     </row>
     <row r="30">
@@ -4228,19 +4329,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>224</v>
+      </c>
+      <c r="F30" t="n">
         <v>436</v>
       </c>
-      <c r="F30" t="n">
-        <v>439</v>
-      </c>
       <c r="G30" t="n">
-        <v>-3</v>
+        <v>-212</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="I30" t="n">
-        <v>49500</v>
+        <v>3498000</v>
       </c>
     </row>
     <row r="31">
@@ -4263,19 +4364,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>224</v>
+      </c>
+      <c r="F31" t="n">
         <v>436</v>
       </c>
-      <c r="F31" t="n">
-        <v>439</v>
-      </c>
       <c r="G31" t="n">
-        <v>-3</v>
+        <v>-212</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="I31" t="n">
-        <v>49500</v>
+        <v>3498000</v>
       </c>
     </row>
     <row r="32">
@@ -4298,19 +4399,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
-        <v>728</v>
+        <v>294</v>
       </c>
       <c r="F32" t="n">
         <v>728</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-434</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7161000</v>
       </c>
     </row>
     <row r="33">
@@ -4333,19 +4434,19 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F33" t="n">
         <v>311</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="34">
@@ -4368,19 +4469,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>149</v>
+      </c>
+      <c r="F34" t="n">
         <v>332</v>
       </c>
-      <c r="F34" t="n">
-        <v>334</v>
-      </c>
       <c r="G34" t="n">
-        <v>-2</v>
+        <v>-183</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="I34" t="n">
-        <v>33000</v>
+        <v>3019500</v>
       </c>
     </row>
     <row r="35">
@@ -4403,19 +4504,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>224</v>
+      </c>
+      <c r="F35" t="n">
         <v>436</v>
       </c>
-      <c r="F35" t="n">
-        <v>439</v>
-      </c>
       <c r="G35" t="n">
-        <v>-3</v>
+        <v>-212</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="I35" t="n">
-        <v>49500</v>
+        <v>3498000</v>
       </c>
     </row>
     <row r="36">
@@ -4438,19 +4539,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>224</v>
+      </c>
+      <c r="F36" t="n">
         <v>436</v>
       </c>
-      <c r="F36" t="n">
-        <v>439</v>
-      </c>
       <c r="G36" t="n">
-        <v>-3</v>
+        <v>-212</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="I36" t="n">
-        <v>49500</v>
+        <v>3498000</v>
       </c>
     </row>
   </sheetData>
@@ -4464,7 +4565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I849"/>
+  <dimension ref="A1:I884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -35577,6 +35678,1293 @@
         <v>49500</v>
       </c>
     </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F850" t="n">
+        <v>1547</v>
+      </c>
+      <c r="G850" t="n">
+        <v>-616</v>
+      </c>
+      <c r="H850" t="n">
+        <v>616</v>
+      </c>
+      <c r="I850" t="n">
+        <v>9240000</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F851" t="n">
+        <v>826</v>
+      </c>
+      <c r="G851" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H851" t="n">
+        <v>33</v>
+      </c>
+      <c r="I851" t="n">
+        <v>495000</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0</v>
+      </c>
+      <c r="G852" t="n">
+        <v>0</v>
+      </c>
+      <c r="H852" t="n">
+        <v>0</v>
+      </c>
+      <c r="I852" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F853" t="n">
+        <v>0</v>
+      </c>
+      <c r="G853" t="n">
+        <v>0</v>
+      </c>
+      <c r="H853" t="n">
+        <v>0</v>
+      </c>
+      <c r="I853" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E854" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F854" t="n">
+        <v>295</v>
+      </c>
+      <c r="G854" t="n">
+        <v>-73</v>
+      </c>
+      <c r="H854" t="n">
+        <v>73</v>
+      </c>
+      <c r="I854" t="n">
+        <v>182500</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E855" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F855" t="n">
+        <v>151</v>
+      </c>
+      <c r="G855" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H855" t="n">
+        <v>4</v>
+      </c>
+      <c r="I855" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E856" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F856" t="n">
+        <v>822</v>
+      </c>
+      <c r="G856" t="n">
+        <v>0</v>
+      </c>
+      <c r="H856" t="n">
+        <v>0</v>
+      </c>
+      <c r="I856" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E857" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F857" t="n">
+        <v>966</v>
+      </c>
+      <c r="G857" t="n">
+        <v>0</v>
+      </c>
+      <c r="H857" t="n">
+        <v>0</v>
+      </c>
+      <c r="I857" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E858" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F858" t="n">
+        <v>940</v>
+      </c>
+      <c r="G858" t="n">
+        <v>0</v>
+      </c>
+      <c r="H858" t="n">
+        <v>0</v>
+      </c>
+      <c r="I858" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E859" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F859" t="n">
+        <v>356</v>
+      </c>
+      <c r="G859" t="n">
+        <v>0</v>
+      </c>
+      <c r="H859" t="n">
+        <v>0</v>
+      </c>
+      <c r="I859" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E860" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F860" t="n">
+        <v>478</v>
+      </c>
+      <c r="G860" t="n">
+        <v>0</v>
+      </c>
+      <c r="H860" t="n">
+        <v>0</v>
+      </c>
+      <c r="I860" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E861" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F861" t="n">
+        <v>484</v>
+      </c>
+      <c r="G861" t="n">
+        <v>0</v>
+      </c>
+      <c r="H861" t="n">
+        <v>0</v>
+      </c>
+      <c r="I861" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E862" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F862" t="n">
+        <v>339</v>
+      </c>
+      <c r="G862" t="n">
+        <v>0</v>
+      </c>
+      <c r="H862" t="n">
+        <v>0</v>
+      </c>
+      <c r="I862" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E863" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F863" t="n">
+        <v>481</v>
+      </c>
+      <c r="G863" t="n">
+        <v>0</v>
+      </c>
+      <c r="H863" t="n">
+        <v>0</v>
+      </c>
+      <c r="I863" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E864" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F864" t="n">
+        <v>483</v>
+      </c>
+      <c r="G864" t="n">
+        <v>0</v>
+      </c>
+      <c r="H864" t="n">
+        <v>0</v>
+      </c>
+      <c r="I864" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E865" t="n">
+        <v>900</v>
+      </c>
+      <c r="F865" t="n">
+        <v>370</v>
+      </c>
+      <c r="G865" t="n">
+        <v>0</v>
+      </c>
+      <c r="H865" t="n">
+        <v>0</v>
+      </c>
+      <c r="I865" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E866" t="n">
+        <v>900</v>
+      </c>
+      <c r="F866" t="n">
+        <v>493</v>
+      </c>
+      <c r="G866" t="n">
+        <v>0</v>
+      </c>
+      <c r="H866" t="n">
+        <v>0</v>
+      </c>
+      <c r="I866" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E867" t="n">
+        <v>900</v>
+      </c>
+      <c r="F867" t="n">
+        <v>476</v>
+      </c>
+      <c r="G867" t="n">
+        <v>0</v>
+      </c>
+      <c r="H867" t="n">
+        <v>0</v>
+      </c>
+      <c r="I867" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E868" t="n">
+        <v>900</v>
+      </c>
+      <c r="F868" t="n">
+        <v>686</v>
+      </c>
+      <c r="G868" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H868" t="n">
+        <v>1</v>
+      </c>
+      <c r="I868" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E869" t="n">
+        <v>900</v>
+      </c>
+      <c r="F869" t="n">
+        <v>941</v>
+      </c>
+      <c r="G869" t="n">
+        <v>0</v>
+      </c>
+      <c r="H869" t="n">
+        <v>0</v>
+      </c>
+      <c r="I869" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
+        <v>900</v>
+      </c>
+      <c r="F870" t="n">
+        <v>953</v>
+      </c>
+      <c r="G870" t="n">
+        <v>0</v>
+      </c>
+      <c r="H870" t="n">
+        <v>0</v>
+      </c>
+      <c r="I870" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E871" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F871" t="n">
+        <v>811</v>
+      </c>
+      <c r="G871" t="n">
+        <v>-68</v>
+      </c>
+      <c r="H871" t="n">
+        <v>68</v>
+      </c>
+      <c r="I871" t="n">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F872" t="n">
+        <v>234</v>
+      </c>
+      <c r="G872" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H872" t="n">
+        <v>6</v>
+      </c>
+      <c r="I872" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E873" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F873" t="n">
+        <v>161</v>
+      </c>
+      <c r="G873" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H873" t="n">
+        <v>2</v>
+      </c>
+      <c r="I873" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E874" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F874" t="n">
+        <v>149</v>
+      </c>
+      <c r="G874" t="n">
+        <v>-91</v>
+      </c>
+      <c r="H874" t="n">
+        <v>91</v>
+      </c>
+      <c r="I874" t="n">
+        <v>1729000</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E875" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F875" t="n">
+        <v>294</v>
+      </c>
+      <c r="G875" t="n">
+        <v>-434</v>
+      </c>
+      <c r="H875" t="n">
+        <v>434</v>
+      </c>
+      <c r="I875" t="n">
+        <v>7161000</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E876" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F876" t="n">
+        <v>310</v>
+      </c>
+      <c r="G876" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H876" t="n">
+        <v>1</v>
+      </c>
+      <c r="I876" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E877" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F877" t="n">
+        <v>149</v>
+      </c>
+      <c r="G877" t="n">
+        <v>-183</v>
+      </c>
+      <c r="H877" t="n">
+        <v>183</v>
+      </c>
+      <c r="I877" t="n">
+        <v>3019500</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E878" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F878" t="n">
+        <v>224</v>
+      </c>
+      <c r="G878" t="n">
+        <v>-212</v>
+      </c>
+      <c r="H878" t="n">
+        <v>212</v>
+      </c>
+      <c r="I878" t="n">
+        <v>3498000</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E879" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F879" t="n">
+        <v>224</v>
+      </c>
+      <c r="G879" t="n">
+        <v>-212</v>
+      </c>
+      <c r="H879" t="n">
+        <v>212</v>
+      </c>
+      <c r="I879" t="n">
+        <v>3498000</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E880" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F880" t="n">
+        <v>294</v>
+      </c>
+      <c r="G880" t="n">
+        <v>-434</v>
+      </c>
+      <c r="H880" t="n">
+        <v>434</v>
+      </c>
+      <c r="I880" t="n">
+        <v>7161000</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E881" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F881" t="n">
+        <v>310</v>
+      </c>
+      <c r="G881" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H881" t="n">
+        <v>1</v>
+      </c>
+      <c r="I881" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E882" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F882" t="n">
+        <v>149</v>
+      </c>
+      <c r="G882" t="n">
+        <v>-183</v>
+      </c>
+      <c r="H882" t="n">
+        <v>183</v>
+      </c>
+      <c r="I882" t="n">
+        <v>3019500</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E883" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F883" t="n">
+        <v>224</v>
+      </c>
+      <c r="G883" t="n">
+        <v>-212</v>
+      </c>
+      <c r="H883" t="n">
+        <v>212</v>
+      </c>
+      <c r="I883" t="n">
+        <v>3498000</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E884" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F884" t="n">
+        <v>224</v>
+      </c>
+      <c r="G884" t="n">
+        <v>-212</v>
+      </c>
+      <c r="H884" t="n">
+        <v>212</v>
+      </c>
+      <c r="I884" t="n">
+        <v>3498000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -872,6 +872,22 @@
         <v>46118400</v>
       </c>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>302</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4688500</v>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,16 +902,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA27"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
@@ -904,11 +920,11 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
     <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
@@ -931,14 +947,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
@@ -946,14 +962,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
@@ -961,19 +977,19 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
@@ -981,14 +997,14 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -996,14 +1012,14 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
@@ -1011,14 +1027,14 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
@@ -1026,19 +1042,19 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
@@ -1046,12 +1062,12 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1150,19 +1166,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1189,19 +1205,19 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>45000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>19000</v>
       </c>
       <c r="R3" t="n">
         <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="T3" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
         <v>1000</v>
@@ -1235,19 +1251,19 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1265,28 +1281,28 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>76000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>45000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>76000</v>
       </c>
       <c r="R4" t="n">
         <v>2500</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>4000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>3000</v>
@@ -1304,10 +1320,10 @@
         <v>3000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="AA4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1320,10 +1336,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1359,19 +1375,19 @@
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19000</v>
       </c>
       <c r="R5" t="n">
         <v>2500</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="T5" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1405,79 +1421,79 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>120000</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>19000</v>
       </c>
       <c r="R6" t="n">
         <v>5000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="T6" t="n">
-        <v>13500</v>
+        <v>1000</v>
       </c>
       <c r="U6" t="n">
         <v>3000</v>
       </c>
       <c r="V6" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>2000</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1490,31 +1506,31 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>31</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>44</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -1529,31 +1545,31 @@
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>152000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>465000</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>152000</v>
       </c>
       <c r="R7" t="n">
         <v>10000</v>
       </c>
       <c r="S7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T7" t="n">
         <v>8000</v>
       </c>
-      <c r="T7" t="n">
-        <v>4500</v>
-      </c>
       <c r="U7" t="n">
         <v>1000</v>
       </c>
       <c r="V7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>2700</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>44000</v>
       </c>
       <c r="Y7" t="n">
         <v>2000</v>
@@ -1575,19 +1591,19 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
         <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -1614,19 +1630,19 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>210000</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>95000</v>
       </c>
       <c r="R8" t="n">
         <v>5000</v>
       </c>
       <c r="S8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T8" t="n">
         <v>5000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2250</v>
       </c>
       <c r="U8" t="n">
         <v>3000</v>
@@ -1660,19 +1676,19 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
         <v>13</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1699,31 +1715,31 @@
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>114000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>195000</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>114000</v>
       </c>
       <c r="R9" t="n">
         <v>20000</v>
       </c>
       <c r="S9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T9" t="n">
         <v>6000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>15750</v>
       </c>
       <c r="U9" t="n">
         <v>4000</v>
       </c>
       <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>900</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -1745,31 +1761,31 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>55</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1784,31 +1800,31 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>825000</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>2500</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="T10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>1000</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>3600</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1830,19 +1846,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1869,19 +1885,19 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>30000</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>2500</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="T11" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>1000</v>
@@ -1915,79 +1931,79 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
         <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>57000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>75000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>57000</v>
       </c>
       <c r="R12" t="n">
         <v>2500</v>
       </c>
       <c r="S12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T12" t="n">
         <v>3000</v>
       </c>
-      <c r="T12" t="n">
-        <v>2250</v>
-      </c>
       <c r="U12" t="n">
         <v>1000</v>
       </c>
       <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
         <v>900</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
       <c r="Y12" t="n">
         <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2000,31 +2016,31 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="n">
         <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -2039,31 +2055,31 @@
         <v>528000</v>
       </c>
       <c r="P13" t="n">
+        <v>228000</v>
+      </c>
+      <c r="Q13" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>228000</v>
       </c>
       <c r="R13" t="n">
         <v>10000</v>
       </c>
       <c r="S13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T13" t="n">
         <v>12000</v>
       </c>
-      <c r="T13" t="n">
-        <v>4500</v>
-      </c>
       <c r="U13" t="n">
         <v>1000</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>900</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>2000</v>
@@ -2085,19 +2101,19 @@
         <v>100</v>
       </c>
       <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
         <v>19</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="n">
         <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2124,19 +2140,19 @@
         <v>1650000</v>
       </c>
       <c r="P14" t="n">
+        <v>190000</v>
+      </c>
+      <c r="Q14" t="n">
         <v>285000</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>190000</v>
       </c>
       <c r="R14" t="n">
         <v>10000</v>
       </c>
       <c r="S14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T14" t="n">
         <v>10000</v>
-      </c>
-      <c r="T14" t="n">
-        <v>15750</v>
       </c>
       <c r="U14" t="n">
         <v>2000</v>
@@ -2170,19 +2186,19 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2209,19 +2225,19 @@
         <v>759000</v>
       </c>
       <c r="P15" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q15" t="n">
         <v>150000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>38000</v>
       </c>
       <c r="R15" t="n">
         <v>7500</v>
       </c>
       <c r="S15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T15" t="n">
         <v>2000</v>
-      </c>
-      <c r="T15" t="n">
-        <v>36000</v>
       </c>
       <c r="U15" t="n">
         <v>2000</v>
@@ -2255,19 +2271,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
         <v>13</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>6</v>
       </c>
       <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2294,19 +2310,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q16" t="n">
         <v>195000</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>95000</v>
       </c>
       <c r="R16" t="n">
         <v>15000</v>
       </c>
       <c r="S16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T16" t="n">
         <v>5000</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6750</v>
       </c>
       <c r="U16" t="n">
         <v>2000</v>
@@ -2340,31 +2356,31 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
         <v>61</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
       </c>
       <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2379,31 +2395,31 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q17" t="n">
         <v>915000</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>38000</v>
       </c>
       <c r="R17" t="n">
         <v>15000</v>
       </c>
       <c r="S17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="T17" t="n">
         <v>2000</v>
-      </c>
-      <c r="T17" t="n">
-        <v>67500</v>
       </c>
       <c r="U17" t="n">
         <v>2000</v>
       </c>
       <c r="V17" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="W17" t="n">
         <v>20000</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -2425,19 +2441,19 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
         <v>6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
         <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -2464,19 +2480,19 @@
         <v>462000</v>
       </c>
       <c r="P18" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q18" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>19000</v>
       </c>
       <c r="R18" t="n">
         <v>7500</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="T18" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="U18" t="n">
         <v>2000</v>
@@ -2510,11 +2526,11 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
@@ -2549,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2595,19 +2611,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
         <v>9</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
         <v>5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -2634,19 +2650,19 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>95000</v>
+      </c>
+      <c r="Q20" t="n">
         <v>135000</v>
       </c>
-      <c r="Q20" t="n">
-        <v>95000</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="T20" t="n">
         <v>5000</v>
-      </c>
-      <c r="T20" t="n">
-        <v>13500</v>
       </c>
       <c r="U20" t="n">
         <v>3000</v>
@@ -2680,10 +2696,10 @@
         <v>70</v>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>22</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -2698,13 +2714,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
@@ -2719,31 +2735,31 @@
         <v>1155000</v>
       </c>
       <c r="P21" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q21" t="n">
         <v>330000</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>19000</v>
       </c>
       <c r="R21" t="n">
         <v>5000</v>
       </c>
       <c r="S21" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T21" t="n">
         <v>3000</v>
       </c>
-      <c r="T21" t="n">
-        <v>6750</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>1800</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
       </c>
       <c r="Y21" t="n">
         <v>2000</v>
@@ -2765,31 +2781,31 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
         <v>7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
         <v>13</v>
       </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2804,31 +2820,31 @@
         <v>363000</v>
       </c>
       <c r="P22" t="n">
+        <v>114000</v>
+      </c>
+      <c r="Q22" t="n">
         <v>105000</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>114000</v>
       </c>
       <c r="R22" t="n">
         <v>2500</v>
       </c>
       <c r="S22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T22" t="n">
         <v>13000</v>
       </c>
-      <c r="T22" t="n">
-        <v>9000</v>
-      </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>1800</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2850,79 +2866,79 @@
         <v>90</v>
       </c>
       <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
         <v>34</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
         <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>1485000</v>
       </c>
       <c r="P23" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q23" t="n">
         <v>510000</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>38000</v>
       </c>
       <c r="R23" t="n">
         <v>7500</v>
       </c>
       <c r="S23" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T23" t="n">
         <v>5000</v>
       </c>
-      <c r="T23" t="n">
-        <v>15750</v>
-      </c>
       <c r="U23" t="n">
         <v>1000</v>
       </c>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>900</v>
       </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AA23" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2935,31 +2951,31 @@
         <v>54</v>
       </c>
       <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
         <v>11</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
       <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2974,31 +2990,31 @@
         <v>891000</v>
       </c>
       <c r="P24" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q24" t="n">
         <v>165000</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>38000</v>
       </c>
       <c r="R24" t="n">
         <v>15000</v>
       </c>
       <c r="S24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T24" t="n">
         <v>5000</v>
       </c>
-      <c r="T24" t="n">
-        <v>4500</v>
-      </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3020,79 +3036,79 @@
         <v>8</v>
       </c>
       <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>132000</v>
       </c>
       <c r="P25" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Q25" t="n">
         <v>45000</v>
       </c>
-      <c r="Q25" t="n">
-        <v>38000</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T25" t="n">
         <v>6000</v>
-      </c>
-      <c r="T25" t="n">
-        <v>6750</v>
       </c>
       <c r="U25" t="n">
         <v>3000</v>
       </c>
       <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>900</v>
       </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="AA25" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3105,19 +3121,19 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3144,19 +3160,19 @@
         <v>264000</v>
       </c>
       <c r="P26" t="n">
+        <v>19000</v>
+      </c>
+      <c r="Q26" t="n">
         <v>30000</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>19000</v>
       </c>
       <c r="R26" t="n">
         <v>2500</v>
       </c>
       <c r="S26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3190,31 +3206,31 @@
         <v>2084</v>
       </c>
       <c r="C27" t="n">
+        <v>91</v>
+      </c>
+      <c r="D27" t="n">
         <v>649</v>
-      </c>
-      <c r="D27" t="n">
-        <v>91</v>
       </c>
       <c r="E27" t="n">
         <v>73</v>
       </c>
       <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
         <v>74</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3229,32 +3245,32 @@
         <v>34386000</v>
       </c>
       <c r="P27" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="Q27" t="n">
         <v>9735000</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1729000</v>
       </c>
       <c r="R27" t="n">
         <v>182500</v>
       </c>
       <c r="S27" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T27" t="n">
         <v>74000</v>
-      </c>
-      <c r="T27" t="n">
-        <v>9000</v>
       </c>
       <c r="U27" t="n">
         <v>2000</v>
       </c>
       <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
         <v>900</v>
       </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
@@ -3262,6 +3278,91 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>209</v>
+      </c>
+      <c r="C28" t="n">
+        <v>34</v>
+      </c>
+      <c r="D28" t="n">
+        <v>37</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3448500</v>
+      </c>
+      <c r="P28" t="n">
+        <v>646000</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>555000</v>
+      </c>
+      <c r="R28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3357,19 +3458,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>1514</v>
+      </c>
+      <c r="F2" t="n">
         <v>1547</v>
       </c>
-      <c r="F2" t="n">
-        <v>2163</v>
-      </c>
       <c r="G2" t="n">
-        <v>-616</v>
+        <v>-33</v>
       </c>
       <c r="H2" t="n">
-        <v>616</v>
+        <v>33</v>
       </c>
       <c r="I2" t="n">
-        <v>9240000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="3">
@@ -3392,19 +3493,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>822</v>
+      </c>
+      <c r="F3" t="n">
         <v>826</v>
       </c>
-      <c r="F3" t="n">
-        <v>859</v>
-      </c>
       <c r="G3" t="n">
-        <v>-33</v>
+        <v>-4</v>
       </c>
       <c r="H3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>495000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4">
@@ -3489,19 +3590,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>287</v>
+      </c>
+      <c r="F6" t="n">
         <v>295</v>
       </c>
-      <c r="F6" t="n">
-        <v>368</v>
-      </c>
       <c r="G6" t="n">
-        <v>-73</v>
+        <v>-8</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>182500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="7">
@@ -3524,10 +3625,10 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>147</v>
+      </c>
+      <c r="F7" t="n">
         <v>151</v>
-      </c>
-      <c r="F7" t="n">
-        <v>155</v>
       </c>
       <c r="G7" t="n">
         <v>-4</v>
@@ -3769,19 +3870,19 @@
         <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F14" t="n">
         <v>339</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15">
@@ -3982,16 +4083,16 @@
         <v>686</v>
       </c>
       <c r="F20" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4084,19 +4185,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>806</v>
+      </c>
+      <c r="F23" t="n">
         <v>811</v>
       </c>
-      <c r="F23" t="n">
-        <v>879</v>
-      </c>
       <c r="G23" t="n">
-        <v>-68</v>
+        <v>-5</v>
       </c>
       <c r="H23" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>68000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="24">
@@ -4119,19 +4220,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>232</v>
+      </c>
+      <c r="F24" t="n">
         <v>234</v>
       </c>
-      <c r="F24" t="n">
-        <v>240</v>
-      </c>
       <c r="G24" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
@@ -4154,10 +4255,10 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>159</v>
+      </c>
+      <c r="F25" t="n">
         <v>161</v>
-      </c>
-      <c r="F25" t="n">
-        <v>163</v>
       </c>
       <c r="G25" t="n">
         <v>-2</v>
@@ -4189,19 +4290,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>115</v>
+      </c>
+      <c r="F26" t="n">
         <v>149</v>
       </c>
-      <c r="F26" t="n">
-        <v>240</v>
-      </c>
       <c r="G26" t="n">
-        <v>-91</v>
+        <v>-34</v>
       </c>
       <c r="H26" t="n">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="I26" t="n">
-        <v>1729000</v>
+        <v>646000</v>
       </c>
     </row>
     <row r="27">
@@ -4227,16 +4328,16 @@
         <v>294</v>
       </c>
       <c r="F27" t="n">
-        <v>728</v>
+        <v>294</v>
       </c>
       <c r="G27" t="n">
-        <v>-434</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7161000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4262,16 +4363,16 @@
         <v>310</v>
       </c>
       <c r="F28" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4294,19 +4395,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>115</v>
+      </c>
+      <c r="F29" t="n">
         <v>149</v>
       </c>
-      <c r="F29" t="n">
-        <v>332</v>
-      </c>
       <c r="G29" t="n">
-        <v>-183</v>
+        <v>-34</v>
       </c>
       <c r="H29" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="I29" t="n">
-        <v>3019500</v>
+        <v>561000</v>
       </c>
     </row>
     <row r="30">
@@ -4329,19 +4430,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>189</v>
+      </c>
+      <c r="F30" t="n">
         <v>224</v>
       </c>
-      <c r="F30" t="n">
-        <v>436</v>
-      </c>
       <c r="G30" t="n">
-        <v>-212</v>
+        <v>-35</v>
       </c>
       <c r="H30" t="n">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="I30" t="n">
-        <v>3498000</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="31">
@@ -4364,19 +4465,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>189</v>
+      </c>
+      <c r="F31" t="n">
         <v>224</v>
       </c>
-      <c r="F31" t="n">
-        <v>436</v>
-      </c>
       <c r="G31" t="n">
-        <v>-212</v>
+        <v>-35</v>
       </c>
       <c r="H31" t="n">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="I31" t="n">
-        <v>3498000</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="32">
@@ -4402,16 +4503,16 @@
         <v>294</v>
       </c>
       <c r="F32" t="n">
-        <v>728</v>
+        <v>294</v>
       </c>
       <c r="G32" t="n">
-        <v>-434</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>7161000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4434,10 +4535,10 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>309</v>
+      </c>
+      <c r="F33" t="n">
         <v>310</v>
-      </c>
-      <c r="F33" t="n">
-        <v>311</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
@@ -4469,19 +4570,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>115</v>
+      </c>
+      <c r="F34" t="n">
         <v>149</v>
       </c>
-      <c r="F34" t="n">
-        <v>332</v>
-      </c>
       <c r="G34" t="n">
-        <v>-183</v>
+        <v>-34</v>
       </c>
       <c r="H34" t="n">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="I34" t="n">
-        <v>3019500</v>
+        <v>561000</v>
       </c>
     </row>
     <row r="35">
@@ -4504,19 +4605,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>189</v>
+      </c>
+      <c r="F35" t="n">
         <v>224</v>
       </c>
-      <c r="F35" t="n">
-        <v>436</v>
-      </c>
       <c r="G35" t="n">
-        <v>-212</v>
+        <v>-35</v>
       </c>
       <c r="H35" t="n">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="I35" t="n">
-        <v>3498000</v>
+        <v>577500</v>
       </c>
     </row>
     <row r="36">
@@ -4539,19 +4640,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>189</v>
+      </c>
+      <c r="F36" t="n">
         <v>224</v>
       </c>
-      <c r="F36" t="n">
-        <v>436</v>
-      </c>
       <c r="G36" t="n">
-        <v>-212</v>
+        <v>-35</v>
       </c>
       <c r="H36" t="n">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="I36" t="n">
-        <v>3498000</v>
+        <v>577500</v>
       </c>
     </row>
   </sheetData>
@@ -4565,7 +4666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I884"/>
+  <dimension ref="A1:I919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -36965,6 +37066,1293 @@
         <v>3498000</v>
       </c>
     </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E885" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F885" t="n">
+        <v>1514</v>
+      </c>
+      <c r="G885" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H885" t="n">
+        <v>33</v>
+      </c>
+      <c r="I885" t="n">
+        <v>495000</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E886" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F886" t="n">
+        <v>822</v>
+      </c>
+      <c r="G886" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H886" t="n">
+        <v>4</v>
+      </c>
+      <c r="I886" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0</v>
+      </c>
+      <c r="G887" t="n">
+        <v>0</v>
+      </c>
+      <c r="H887" t="n">
+        <v>0</v>
+      </c>
+      <c r="I887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0</v>
+      </c>
+      <c r="G888" t="n">
+        <v>0</v>
+      </c>
+      <c r="H888" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E889" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F889" t="n">
+        <v>287</v>
+      </c>
+      <c r="G889" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H889" t="n">
+        <v>8</v>
+      </c>
+      <c r="I889" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E890" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F890" t="n">
+        <v>147</v>
+      </c>
+      <c r="G890" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H890" t="n">
+        <v>4</v>
+      </c>
+      <c r="I890" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E891" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F891" t="n">
+        <v>822</v>
+      </c>
+      <c r="G891" t="n">
+        <v>0</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E892" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F892" t="n">
+        <v>966</v>
+      </c>
+      <c r="G892" t="n">
+        <v>0</v>
+      </c>
+      <c r="H892" t="n">
+        <v>0</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E893" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F893" t="n">
+        <v>940</v>
+      </c>
+      <c r="G893" t="n">
+        <v>0</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E894" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F894" t="n">
+        <v>356</v>
+      </c>
+      <c r="G894" t="n">
+        <v>0</v>
+      </c>
+      <c r="H894" t="n">
+        <v>0</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E895" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F895" t="n">
+        <v>478</v>
+      </c>
+      <c r="G895" t="n">
+        <v>0</v>
+      </c>
+      <c r="H895" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E896" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F896" t="n">
+        <v>484</v>
+      </c>
+      <c r="G896" t="n">
+        <v>0</v>
+      </c>
+      <c r="H896" t="n">
+        <v>0</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E897" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F897" t="n">
+        <v>338</v>
+      </c>
+      <c r="G897" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H897" t="n">
+        <v>1</v>
+      </c>
+      <c r="I897" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E898" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F898" t="n">
+        <v>481</v>
+      </c>
+      <c r="G898" t="n">
+        <v>0</v>
+      </c>
+      <c r="H898" t="n">
+        <v>0</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E899" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F899" t="n">
+        <v>483</v>
+      </c>
+      <c r="G899" t="n">
+        <v>0</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E900" t="n">
+        <v>900</v>
+      </c>
+      <c r="F900" t="n">
+        <v>370</v>
+      </c>
+      <c r="G900" t="n">
+        <v>0</v>
+      </c>
+      <c r="H900" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E901" t="n">
+        <v>900</v>
+      </c>
+      <c r="F901" t="n">
+        <v>493</v>
+      </c>
+      <c r="G901" t="n">
+        <v>0</v>
+      </c>
+      <c r="H901" t="n">
+        <v>0</v>
+      </c>
+      <c r="I901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E902" t="n">
+        <v>900</v>
+      </c>
+      <c r="F902" t="n">
+        <v>476</v>
+      </c>
+      <c r="G902" t="n">
+        <v>0</v>
+      </c>
+      <c r="H902" t="n">
+        <v>0</v>
+      </c>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E903" t="n">
+        <v>900</v>
+      </c>
+      <c r="F903" t="n">
+        <v>686</v>
+      </c>
+      <c r="G903" t="n">
+        <v>0</v>
+      </c>
+      <c r="H903" t="n">
+        <v>0</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E904" t="n">
+        <v>900</v>
+      </c>
+      <c r="F904" t="n">
+        <v>941</v>
+      </c>
+      <c r="G904" t="n">
+        <v>0</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E905" t="n">
+        <v>900</v>
+      </c>
+      <c r="F905" t="n">
+        <v>953</v>
+      </c>
+      <c r="G905" t="n">
+        <v>0</v>
+      </c>
+      <c r="H905" t="n">
+        <v>0</v>
+      </c>
+      <c r="I905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E906" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F906" t="n">
+        <v>806</v>
+      </c>
+      <c r="G906" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H906" t="n">
+        <v>5</v>
+      </c>
+      <c r="I906" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E907" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F907" t="n">
+        <v>232</v>
+      </c>
+      <c r="G907" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H907" t="n">
+        <v>2</v>
+      </c>
+      <c r="I907" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E908" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F908" t="n">
+        <v>159</v>
+      </c>
+      <c r="G908" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H908" t="n">
+        <v>2</v>
+      </c>
+      <c r="I908" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E909" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F909" t="n">
+        <v>115</v>
+      </c>
+      <c r="G909" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H909" t="n">
+        <v>34</v>
+      </c>
+      <c r="I909" t="n">
+        <v>646000</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E910" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F910" t="n">
+        <v>294</v>
+      </c>
+      <c r="G910" t="n">
+        <v>0</v>
+      </c>
+      <c r="H910" t="n">
+        <v>0</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E911" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F911" t="n">
+        <v>310</v>
+      </c>
+      <c r="G911" t="n">
+        <v>0</v>
+      </c>
+      <c r="H911" t="n">
+        <v>0</v>
+      </c>
+      <c r="I911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E912" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F912" t="n">
+        <v>115</v>
+      </c>
+      <c r="G912" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H912" t="n">
+        <v>34</v>
+      </c>
+      <c r="I912" t="n">
+        <v>561000</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E913" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F913" t="n">
+        <v>189</v>
+      </c>
+      <c r="G913" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H913" t="n">
+        <v>35</v>
+      </c>
+      <c r="I913" t="n">
+        <v>577500</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E914" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F914" t="n">
+        <v>189</v>
+      </c>
+      <c r="G914" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H914" t="n">
+        <v>35</v>
+      </c>
+      <c r="I914" t="n">
+        <v>577500</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E915" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F915" t="n">
+        <v>294</v>
+      </c>
+      <c r="G915" t="n">
+        <v>0</v>
+      </c>
+      <c r="H915" t="n">
+        <v>0</v>
+      </c>
+      <c r="I915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E916" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F916" t="n">
+        <v>309</v>
+      </c>
+      <c r="G916" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H916" t="n">
+        <v>1</v>
+      </c>
+      <c r="I916" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E917" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F917" t="n">
+        <v>115</v>
+      </c>
+      <c r="G917" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H917" t="n">
+        <v>34</v>
+      </c>
+      <c r="I917" t="n">
+        <v>561000</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E918" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F918" t="n">
+        <v>189</v>
+      </c>
+      <c r="G918" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H918" t="n">
+        <v>35</v>
+      </c>
+      <c r="I918" t="n">
+        <v>577500</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E919" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F919" t="n">
+        <v>189</v>
+      </c>
+      <c r="G919" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H919" t="n">
+        <v>35</v>
+      </c>
+      <c r="I919" t="n">
+        <v>577500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -888,6 +888,22 @@
         <v>4688500</v>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n">
+        <v>244250</v>
+      </c>
+      <c r="D29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,16 +918,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
@@ -920,11 +936,11 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="29" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
     <col width="48" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
@@ -947,14 +963,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Units)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
@@ -962,14 +978,14 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
@@ -977,34 +993,34 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -1012,14 +1028,14 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Extra inq pen (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>inq Student Kit (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Extra inq pen (Rev USD)</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
@@ -1027,14 +1043,14 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
@@ -1042,32 +1058,32 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1166,19 +1182,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1205,19 +1221,19 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>45000</v>
       </c>
       <c r="R3" t="n">
         <v>2500</v>
       </c>
       <c r="S3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T3" t="n">
         <v>6750</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1000</v>
       </c>
       <c r="U3" t="n">
         <v>1000</v>
@@ -1251,19 +1267,19 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1275,34 +1291,34 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
       </c>
       <c r="P4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>76000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>45000</v>
       </c>
       <c r="R4" t="n">
         <v>2500</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T4" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>3000</v>
@@ -1311,19 +1327,19 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X4" t="n">
         <v>3000</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2700</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1336,10 +1352,10 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1357,38 +1373,38 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
       </c>
       <c r="P5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>90000</v>
       </c>
       <c r="R5" t="n">
         <v>2500</v>
       </c>
       <c r="S5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T5" t="n">
         <v>2250</v>
       </c>
-      <c r="T5" t="n">
-        <v>1000</v>
-      </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
@@ -1396,19 +1412,19 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -1421,37 +1437,37 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1460,37 +1476,37 @@
         <v>396000</v>
       </c>
       <c r="P6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Q6" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>120000</v>
       </c>
       <c r="R6" t="n">
         <v>5000</v>
       </c>
       <c r="S6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T6" t="n">
         <v>13500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1000</v>
       </c>
       <c r="U6" t="n">
         <v>3000</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="W6" t="n">
+        <v>900</v>
+      </c>
+      <c r="X6" t="n">
         <v>2000</v>
       </c>
-      <c r="X6" t="n">
-        <v>2700</v>
-      </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1506,79 +1522,79 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
         <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
       </c>
       <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>44</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="Q7" t="n">
         <v>152000</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>465000</v>
       </c>
       <c r="R7" t="n">
         <v>10000</v>
       </c>
       <c r="S7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T7" t="n">
         <v>4500</v>
       </c>
-      <c r="T7" t="n">
-        <v>8000</v>
-      </c>
       <c r="U7" t="n">
         <v>1000</v>
       </c>
       <c r="V7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>44000</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1591,19 +1607,19 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -1630,19 +1646,19 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
+        <v>210000</v>
+      </c>
+      <c r="Q8" t="n">
         <v>95000</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>210000</v>
       </c>
       <c r="R8" t="n">
         <v>5000</v>
       </c>
       <c r="S8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T8" t="n">
         <v>2250</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5000</v>
       </c>
       <c r="U8" t="n">
         <v>3000</v>
@@ -1676,19 +1692,19 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
         <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1700,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1709,37 +1725,37 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
       </c>
       <c r="P9" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q9" t="n">
         <v>114000</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>195000</v>
       </c>
       <c r="R9" t="n">
         <v>20000</v>
       </c>
       <c r="S9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T9" t="n">
         <v>15750</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6000</v>
       </c>
       <c r="U9" t="n">
         <v>4000</v>
       </c>
       <c r="V9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -1748,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -1761,31 +1777,31 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1800,31 +1816,31 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>825000</v>
       </c>
       <c r="Q10" t="n">
-        <v>825000</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>2500</v>
       </c>
       <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>4500</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>1000</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1846,19 +1862,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -1885,19 +1901,19 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Q11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>2500</v>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>2250</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>1000</v>
@@ -1931,79 +1947,79 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
         <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
       </c>
       <c r="P12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="Q12" t="n">
         <v>57000</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>75000</v>
       </c>
       <c r="R12" t="n">
         <v>2500</v>
       </c>
       <c r="S12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T12" t="n">
         <v>2250</v>
       </c>
-      <c r="T12" t="n">
-        <v>3000</v>
-      </c>
       <c r="U12" t="n">
         <v>1000</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
@@ -2016,79 +2032,79 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
         <v>12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
       </c>
       <c r="P13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q13" t="n">
         <v>228000</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>90000</v>
       </c>
       <c r="R13" t="n">
         <v>10000</v>
       </c>
       <c r="S13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T13" t="n">
         <v>4500</v>
       </c>
-      <c r="T13" t="n">
-        <v>12000</v>
-      </c>
       <c r="U13" t="n">
         <v>1000</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2101,19 +2117,19 @@
         <v>100</v>
       </c>
       <c r="C14" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2140,19 +2156,19 @@
         <v>1650000</v>
       </c>
       <c r="P14" t="n">
+        <v>285000</v>
+      </c>
+      <c r="Q14" t="n">
         <v>190000</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>285000</v>
       </c>
       <c r="R14" t="n">
         <v>10000</v>
       </c>
       <c r="S14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T14" t="n">
         <v>15750</v>
-      </c>
-      <c r="T14" t="n">
-        <v>10000</v>
       </c>
       <c r="U14" t="n">
         <v>2000</v>
@@ -2186,19 +2202,19 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
         <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>16</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2225,19 +2241,19 @@
         <v>759000</v>
       </c>
       <c r="P15" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q15" t="n">
         <v>38000</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>150000</v>
       </c>
       <c r="R15" t="n">
         <v>7500</v>
       </c>
       <c r="S15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T15" t="n">
         <v>36000</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2000</v>
       </c>
       <c r="U15" t="n">
         <v>2000</v>
@@ -2271,19 +2287,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>6</v>
       </c>
       <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2292,11 +2308,11 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -2310,19 +2326,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q16" t="n">
         <v>95000</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>195000</v>
       </c>
       <c r="R16" t="n">
         <v>15000</v>
       </c>
       <c r="S16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T16" t="n">
         <v>6750</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5000</v>
       </c>
       <c r="U16" t="n">
         <v>2000</v>
@@ -2331,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
         <v>2000</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2356,31 +2372,31 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
+        <v>61</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>61</v>
       </c>
       <c r="E17" t="n">
         <v>6</v>
       </c>
       <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
         <v>30</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -2389,38 +2405,38 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>915000</v>
+      </c>
+      <c r="Q17" t="n">
         <v>38000</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>915000</v>
       </c>
       <c r="R17" t="n">
         <v>15000</v>
       </c>
       <c r="S17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T17" t="n">
         <v>67500</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2000</v>
       </c>
       <c r="U17" t="n">
         <v>2000</v>
       </c>
       <c r="V17" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>20000</v>
       </c>
-      <c r="X17" t="n">
-        <v>1800</v>
-      </c>
       <c r="Y17" t="n">
         <v>1000</v>
       </c>
@@ -2428,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
@@ -2441,19 +2457,19 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
         <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
         <v>3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -2480,19 +2496,19 @@
         <v>462000</v>
       </c>
       <c r="P18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="Q18" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>90000</v>
       </c>
       <c r="R18" t="n">
         <v>7500</v>
       </c>
       <c r="S18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T18" t="n">
         <v>6750</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1000</v>
       </c>
       <c r="U18" t="n">
         <v>2000</v>
@@ -2526,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2565,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="Q19" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2611,19 +2627,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
-        <v>9</v>
-      </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -2638,31 +2654,31 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>2</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
+        <v>135000</v>
+      </c>
+      <c r="Q20" t="n">
         <v>95000</v>
       </c>
-      <c r="Q20" t="n">
-        <v>135000</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T20" t="n">
         <v>13500</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5000</v>
       </c>
       <c r="U20" t="n">
         <v>3000</v>
@@ -2677,13 +2693,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2696,10 +2712,10 @@
         <v>70</v>
       </c>
       <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
         <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>22</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -2714,61 +2730,61 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
       </c>
       <c r="P21" t="n">
+        <v>330000</v>
+      </c>
+      <c r="Q21" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>330000</v>
       </c>
       <c r="R21" t="n">
         <v>5000</v>
       </c>
       <c r="S21" t="n">
+        <v>3000</v>
+      </c>
+      <c r="T21" t="n">
         <v>6750</v>
       </c>
-      <c r="T21" t="n">
-        <v>3000</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2781,31 +2797,31 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
         <v>6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" t="n">
-        <v>13</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2820,31 +2836,31 @@
         <v>363000</v>
       </c>
       <c r="P22" t="n">
+        <v>105000</v>
+      </c>
+      <c r="Q22" t="n">
         <v>114000</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>105000</v>
       </c>
       <c r="R22" t="n">
         <v>2500</v>
       </c>
       <c r="S22" t="n">
+        <v>13000</v>
+      </c>
+      <c r="T22" t="n">
         <v>9000</v>
       </c>
-      <c r="T22" t="n">
-        <v>13000</v>
-      </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2866,37 +2882,37 @@
         <v>90</v>
       </c>
       <c r="C23" t="n">
+        <v>34</v>
+      </c>
+      <c r="D23" t="n">
         <v>2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
         <v>7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2905,37 +2921,37 @@
         <v>1485000</v>
       </c>
       <c r="P23" t="n">
+        <v>510000</v>
+      </c>
+      <c r="Q23" t="n">
         <v>38000</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>510000</v>
       </c>
       <c r="R23" t="n">
         <v>7500</v>
       </c>
       <c r="S23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T23" t="n">
         <v>15750</v>
       </c>
-      <c r="T23" t="n">
-        <v>5000</v>
-      </c>
       <c r="U23" t="n">
         <v>1000</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X23" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2951,34 +2967,34 @@
         <v>54</v>
       </c>
       <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="n">
         <v>2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
       <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
         <v>2</v>
       </c>
-      <c r="G24" t="n">
-        <v>5</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2990,34 +3006,34 @@
         <v>891000</v>
       </c>
       <c r="P24" t="n">
+        <v>165000</v>
+      </c>
+      <c r="Q24" t="n">
         <v>38000</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>165000</v>
       </c>
       <c r="R24" t="n">
         <v>15000</v>
       </c>
       <c r="S24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T24" t="n">
         <v>4500</v>
       </c>
-      <c r="T24" t="n">
-        <v>5000</v>
-      </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>2000</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3036,37 +3052,37 @@
         <v>8</v>
       </c>
       <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3075,37 +3091,37 @@
         <v>132000</v>
       </c>
       <c r="P25" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Q25" t="n">
         <v>38000</v>
       </c>
-      <c r="Q25" t="n">
-        <v>45000</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T25" t="n">
         <v>6750</v>
-      </c>
-      <c r="T25" t="n">
-        <v>6000</v>
       </c>
       <c r="U25" t="n">
         <v>3000</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="X25" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3121,19 +3137,19 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
         <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3160,19 +3176,19 @@
         <v>264000</v>
       </c>
       <c r="P26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q26" t="n">
         <v>19000</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>30000</v>
       </c>
       <c r="R26" t="n">
         <v>2500</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3206,31 +3222,31 @@
         <v>2084</v>
       </c>
       <c r="C27" t="n">
+        <v>649</v>
+      </c>
+      <c r="D27" t="n">
         <v>91</v>
-      </c>
-      <c r="D27" t="n">
-        <v>649</v>
       </c>
       <c r="E27" t="n">
         <v>73</v>
       </c>
       <c r="F27" t="n">
+        <v>74</v>
+      </c>
+      <c r="G27" t="n">
         <v>4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>74</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3245,31 +3261,31 @@
         <v>34386000</v>
       </c>
       <c r="P27" t="n">
+        <v>9735000</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1729000</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9735000</v>
       </c>
       <c r="R27" t="n">
         <v>182500</v>
       </c>
       <c r="S27" t="n">
+        <v>74000</v>
+      </c>
+      <c r="T27" t="n">
         <v>9000</v>
-      </c>
-      <c r="T27" t="n">
-        <v>74000</v>
       </c>
       <c r="U27" t="n">
         <v>2000</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -3291,34 +3307,34 @@
         <v>209</v>
       </c>
       <c r="C28" t="n">
+        <v>37</v>
+      </c>
+      <c r="D28" t="n">
         <v>34</v>
-      </c>
-      <c r="D28" t="n">
-        <v>37</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
       </c>
       <c r="F28" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" t="n">
         <v>4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>7</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3330,25 +3346,25 @@
         <v>3448500</v>
       </c>
       <c r="P28" t="n">
+        <v>555000</v>
+      </c>
+      <c r="Q28" t="n">
         <v>646000</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>555000</v>
       </c>
       <c r="R28" t="n">
         <v>20000</v>
       </c>
       <c r="S28" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T28" t="n">
         <v>9000</v>
-      </c>
-      <c r="T28" t="n">
-        <v>7000</v>
       </c>
       <c r="U28" t="n">
         <v>2000</v>
       </c>
       <c r="V28" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3357,12 +3373,97 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>148500</v>
+      </c>
+      <c r="P29" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>19000</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6000</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2250</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3458,19 +3559,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>1511</v>
+      </c>
+      <c r="F2" t="n">
         <v>1514</v>
       </c>
-      <c r="F2" t="n">
-        <v>1547</v>
-      </c>
       <c r="G2" t="n">
-        <v>-33</v>
+        <v>-3</v>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>495000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="3">
@@ -3493,19 +3594,19 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>821</v>
+      </c>
+      <c r="F3" t="n">
         <v>822</v>
       </c>
-      <c r="F3" t="n">
-        <v>826</v>
-      </c>
       <c r="G3" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>60000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="4">
@@ -3590,19 +3691,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>284</v>
+      </c>
+      <c r="F6" t="n">
         <v>287</v>
       </c>
-      <c r="F6" t="n">
-        <v>295</v>
-      </c>
       <c r="G6" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>20000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="7">
@@ -3625,19 +3726,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>146</v>
+      </c>
+      <c r="F7" t="n">
         <v>147</v>
       </c>
-      <c r="F7" t="n">
-        <v>151</v>
-      </c>
       <c r="G7" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>9000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -3873,16 +3974,16 @@
         <v>338</v>
       </c>
       <c r="F14" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4185,19 +4286,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>802</v>
+      </c>
+      <c r="F23" t="n">
         <v>806</v>
       </c>
-      <c r="F23" t="n">
-        <v>811</v>
-      </c>
       <c r="G23" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24">
@@ -4220,10 +4321,10 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>230</v>
+      </c>
+      <c r="F24" t="n">
         <v>232</v>
-      </c>
-      <c r="F24" t="n">
-        <v>234</v>
       </c>
       <c r="G24" t="n">
         <v>-2</v>
@@ -4255,19 +4356,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
+        <v>158</v>
+      </c>
+      <c r="F25" t="n">
         <v>159</v>
       </c>
-      <c r="F25" t="n">
-        <v>161</v>
-      </c>
       <c r="G25" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -4290,19 +4391,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>114</v>
+      </c>
+      <c r="F26" t="n">
         <v>115</v>
       </c>
-      <c r="F26" t="n">
-        <v>149</v>
-      </c>
       <c r="G26" t="n">
-        <v>-34</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>646000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="27">
@@ -4360,19 +4461,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F28" t="n">
         <v>310</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="29">
@@ -4395,19 +4496,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>114</v>
+      </c>
+      <c r="F29" t="n">
         <v>115</v>
       </c>
-      <c r="F29" t="n">
-        <v>149</v>
-      </c>
       <c r="G29" t="n">
-        <v>-34</v>
+        <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>561000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="30">
@@ -4430,19 +4531,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>188</v>
+      </c>
+      <c r="F30" t="n">
         <v>189</v>
       </c>
-      <c r="F30" t="n">
-        <v>224</v>
-      </c>
       <c r="G30" t="n">
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>577500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="31">
@@ -4465,19 +4566,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>188</v>
+      </c>
+      <c r="F31" t="n">
         <v>189</v>
       </c>
-      <c r="F31" t="n">
-        <v>224</v>
-      </c>
       <c r="G31" t="n">
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>577500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="32">
@@ -4535,10 +4636,10 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>308</v>
+      </c>
+      <c r="F33" t="n">
         <v>309</v>
-      </c>
-      <c r="F33" t="n">
-        <v>310</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
@@ -4570,19 +4671,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>114</v>
+      </c>
+      <c r="F34" t="n">
         <v>115</v>
       </c>
-      <c r="F34" t="n">
-        <v>149</v>
-      </c>
       <c r="G34" t="n">
-        <v>-34</v>
+        <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>561000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="35">
@@ -4605,19 +4706,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>188</v>
+      </c>
+      <c r="F35" t="n">
         <v>189</v>
       </c>
-      <c r="F35" t="n">
-        <v>224</v>
-      </c>
       <c r="G35" t="n">
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>577500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="36">
@@ -4640,19 +4741,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>188</v>
+      </c>
+      <c r="F36" t="n">
         <v>189</v>
       </c>
-      <c r="F36" t="n">
-        <v>224</v>
-      </c>
       <c r="G36" t="n">
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>577500</v>
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
@@ -4666,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I919"/>
+  <dimension ref="A1:I954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -38353,6 +38454,1293 @@
         <v>577500</v>
       </c>
     </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E920" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F920" t="n">
+        <v>1511</v>
+      </c>
+      <c r="G920" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H920" t="n">
+        <v>3</v>
+      </c>
+      <c r="I920" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E921" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F921" t="n">
+        <v>821</v>
+      </c>
+      <c r="G921" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H921" t="n">
+        <v>1</v>
+      </c>
+      <c r="I921" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0</v>
+      </c>
+      <c r="G922" t="n">
+        <v>0</v>
+      </c>
+      <c r="H922" t="n">
+        <v>0</v>
+      </c>
+      <c r="I922" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr"/>
+      <c r="E923" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0</v>
+      </c>
+      <c r="G923" t="n">
+        <v>0</v>
+      </c>
+      <c r="H923" t="n">
+        <v>0</v>
+      </c>
+      <c r="I923" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E924" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F924" t="n">
+        <v>284</v>
+      </c>
+      <c r="G924" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H924" t="n">
+        <v>3</v>
+      </c>
+      <c r="I924" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E925" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F925" t="n">
+        <v>146</v>
+      </c>
+      <c r="G925" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H925" t="n">
+        <v>1</v>
+      </c>
+      <c r="I925" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E926" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F926" t="n">
+        <v>822</v>
+      </c>
+      <c r="G926" t="n">
+        <v>0</v>
+      </c>
+      <c r="H926" t="n">
+        <v>0</v>
+      </c>
+      <c r="I926" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E927" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F927" t="n">
+        <v>966</v>
+      </c>
+      <c r="G927" t="n">
+        <v>0</v>
+      </c>
+      <c r="H927" t="n">
+        <v>0</v>
+      </c>
+      <c r="I927" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E928" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F928" t="n">
+        <v>940</v>
+      </c>
+      <c r="G928" t="n">
+        <v>0</v>
+      </c>
+      <c r="H928" t="n">
+        <v>0</v>
+      </c>
+      <c r="I928" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E929" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F929" t="n">
+        <v>356</v>
+      </c>
+      <c r="G929" t="n">
+        <v>0</v>
+      </c>
+      <c r="H929" t="n">
+        <v>0</v>
+      </c>
+      <c r="I929" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E930" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F930" t="n">
+        <v>478</v>
+      </c>
+      <c r="G930" t="n">
+        <v>0</v>
+      </c>
+      <c r="H930" t="n">
+        <v>0</v>
+      </c>
+      <c r="I930" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E931" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F931" t="n">
+        <v>484</v>
+      </c>
+      <c r="G931" t="n">
+        <v>0</v>
+      </c>
+      <c r="H931" t="n">
+        <v>0</v>
+      </c>
+      <c r="I931" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E932" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F932" t="n">
+        <v>338</v>
+      </c>
+      <c r="G932" t="n">
+        <v>0</v>
+      </c>
+      <c r="H932" t="n">
+        <v>0</v>
+      </c>
+      <c r="I932" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E933" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F933" t="n">
+        <v>481</v>
+      </c>
+      <c r="G933" t="n">
+        <v>0</v>
+      </c>
+      <c r="H933" t="n">
+        <v>0</v>
+      </c>
+      <c r="I933" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E934" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F934" t="n">
+        <v>483</v>
+      </c>
+      <c r="G934" t="n">
+        <v>0</v>
+      </c>
+      <c r="H934" t="n">
+        <v>0</v>
+      </c>
+      <c r="I934" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E935" t="n">
+        <v>900</v>
+      </c>
+      <c r="F935" t="n">
+        <v>370</v>
+      </c>
+      <c r="G935" t="n">
+        <v>0</v>
+      </c>
+      <c r="H935" t="n">
+        <v>0</v>
+      </c>
+      <c r="I935" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E936" t="n">
+        <v>900</v>
+      </c>
+      <c r="F936" t="n">
+        <v>493</v>
+      </c>
+      <c r="G936" t="n">
+        <v>0</v>
+      </c>
+      <c r="H936" t="n">
+        <v>0</v>
+      </c>
+      <c r="I936" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E937" t="n">
+        <v>900</v>
+      </c>
+      <c r="F937" t="n">
+        <v>476</v>
+      </c>
+      <c r="G937" t="n">
+        <v>0</v>
+      </c>
+      <c r="H937" t="n">
+        <v>0</v>
+      </c>
+      <c r="I937" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E938" t="n">
+        <v>900</v>
+      </c>
+      <c r="F938" t="n">
+        <v>686</v>
+      </c>
+      <c r="G938" t="n">
+        <v>0</v>
+      </c>
+      <c r="H938" t="n">
+        <v>0</v>
+      </c>
+      <c r="I938" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E939" t="n">
+        <v>900</v>
+      </c>
+      <c r="F939" t="n">
+        <v>941</v>
+      </c>
+      <c r="G939" t="n">
+        <v>0</v>
+      </c>
+      <c r="H939" t="n">
+        <v>0</v>
+      </c>
+      <c r="I939" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E940" t="n">
+        <v>900</v>
+      </c>
+      <c r="F940" t="n">
+        <v>953</v>
+      </c>
+      <c r="G940" t="n">
+        <v>0</v>
+      </c>
+      <c r="H940" t="n">
+        <v>0</v>
+      </c>
+      <c r="I940" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E941" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F941" t="n">
+        <v>802</v>
+      </c>
+      <c r="G941" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H941" t="n">
+        <v>4</v>
+      </c>
+      <c r="I941" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E942" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F942" t="n">
+        <v>230</v>
+      </c>
+      <c r="G942" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H942" t="n">
+        <v>2</v>
+      </c>
+      <c r="I942" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E943" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F943" t="n">
+        <v>158</v>
+      </c>
+      <c r="G943" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H943" t="n">
+        <v>1</v>
+      </c>
+      <c r="I943" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E944" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F944" t="n">
+        <v>114</v>
+      </c>
+      <c r="G944" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H944" t="n">
+        <v>1</v>
+      </c>
+      <c r="I944" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E945" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F945" t="n">
+        <v>294</v>
+      </c>
+      <c r="G945" t="n">
+        <v>0</v>
+      </c>
+      <c r="H945" t="n">
+        <v>0</v>
+      </c>
+      <c r="I945" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E946" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F946" t="n">
+        <v>308</v>
+      </c>
+      <c r="G946" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H946" t="n">
+        <v>2</v>
+      </c>
+      <c r="I946" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E947" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F947" t="n">
+        <v>114</v>
+      </c>
+      <c r="G947" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H947" t="n">
+        <v>1</v>
+      </c>
+      <c r="I947" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E948" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F948" t="n">
+        <v>188</v>
+      </c>
+      <c r="G948" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H948" t="n">
+        <v>1</v>
+      </c>
+      <c r="I948" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E949" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F949" t="n">
+        <v>188</v>
+      </c>
+      <c r="G949" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H949" t="n">
+        <v>1</v>
+      </c>
+      <c r="I949" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E950" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F950" t="n">
+        <v>294</v>
+      </c>
+      <c r="G950" t="n">
+        <v>0</v>
+      </c>
+      <c r="H950" t="n">
+        <v>0</v>
+      </c>
+      <c r="I950" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E951" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F951" t="n">
+        <v>308</v>
+      </c>
+      <c r="G951" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H951" t="n">
+        <v>1</v>
+      </c>
+      <c r="I951" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E952" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F952" t="n">
+        <v>114</v>
+      </c>
+      <c r="G952" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H952" t="n">
+        <v>1</v>
+      </c>
+      <c r="I952" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E953" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F953" t="n">
+        <v>188</v>
+      </c>
+      <c r="G953" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H953" t="n">
+        <v>1</v>
+      </c>
+      <c r="I953" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E954" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F954" t="n">
+        <v>188</v>
+      </c>
+      <c r="G954" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H954" t="n">
+        <v>1</v>
+      </c>
+      <c r="I954" t="n">
+        <v>16500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -904,6 +904,22 @@
         <v>244250</v>
       </c>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>86</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1252250</v>
+      </c>
+      <c r="D30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -926,12 +942,12 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
@@ -939,12 +955,12 @@
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="29" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
-    <col width="45" customWidth="1" min="19" max="19"/>
-    <col width="55" customWidth="1" min="20" max="20"/>
-    <col width="48" customWidth="1" min="21" max="21"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
-    <col width="55" customWidth="1" min="24" max="24"/>
+    <col width="48" customWidth="1" min="24" max="24"/>
     <col width="55" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
@@ -978,49 +994,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>inq writing set (Rev USD)</t>
@@ -1043,47 +1059,47 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Rev USD)</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1207,22 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1230,13 +1246,13 @@
         <v>2500</v>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="T3" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="U3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -1245,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1276,10 +1292,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1297,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>198000</v>
@@ -1315,19 +1331,19 @@
         <v>2500</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>4000</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
+        <v>2700</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>3000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2700</v>
       </c>
       <c r="X4" t="n">
         <v>3000</v>
@@ -1336,10 +1352,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1373,19 +1389,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>528000</v>
@@ -1400,10 +1416,10 @@
         <v>2500</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>2250</v>
       </c>
       <c r="T5" t="n">
-        <v>2250</v>
+        <v>1000</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1412,19 +1428,19 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1446,25 +1462,25 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1485,25 +1501,25 @@
         <v>5000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="T6" t="n">
-        <v>13500</v>
+        <v>1000</v>
       </c>
       <c r="U6" t="n">
+        <v>900</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="X6" t="n">
         <v>3000</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>2700</v>
-      </c>
-      <c r="W6" t="n">
-        <v>900</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1531,31 +1547,31 @@
         <v>4</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>8</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>44</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1782000</v>
@@ -1570,31 +1586,31 @@
         <v>10000</v>
       </c>
       <c r="S7" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T7" t="n">
         <v>8000</v>
       </c>
-      <c r="T7" t="n">
-        <v>4500</v>
-      </c>
       <c r="U7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
+        <v>44000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2700</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>44000</v>
-      </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1616,22 +1632,22 @@
         <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1655,22 +1671,22 @@
         <v>5000</v>
       </c>
       <c r="S8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T8" t="n">
         <v>5000</v>
       </c>
-      <c r="T8" t="n">
-        <v>2250</v>
-      </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
         <v>3000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1701,13 +1717,13 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1716,16 +1732,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>792000</v>
@@ -1740,31 +1756,31 @@
         <v>20000</v>
       </c>
       <c r="S9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T9" t="n">
         <v>6000</v>
       </c>
-      <c r="T9" t="n">
-        <v>15750</v>
-      </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>4000</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>900</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1786,25 +1802,25 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1825,25 +1841,25 @@
         <v>2500</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="T10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
         <v>3600</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1871,22 +1887,22 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1910,13 +1926,13 @@
         <v>2500</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="T11" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1925,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1956,31 +1972,31 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
         <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>297000</v>
@@ -1995,31 +2011,31 @@
         <v>2500</v>
       </c>
       <c r="S12" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T12" t="n">
         <v>3000</v>
       </c>
-      <c r="T12" t="n">
-        <v>2250</v>
-      </c>
       <c r="U12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
         <v>900</v>
       </c>
-      <c r="W12" t="n">
-        <v>900</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2041,31 +2057,31 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>12</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>528000</v>
@@ -2080,31 +2096,31 @@
         <v>10000</v>
       </c>
       <c r="S13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T13" t="n">
         <v>12000</v>
       </c>
-      <c r="T13" t="n">
-        <v>4500</v>
-      </c>
       <c r="U13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
         <v>900</v>
       </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2126,22 +2142,22 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="n">
         <v>10</v>
       </c>
-      <c r="G14" t="n">
-        <v>7</v>
-      </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2165,22 +2181,22 @@
         <v>10000</v>
       </c>
       <c r="S14" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T14" t="n">
         <v>10000</v>
       </c>
-      <c r="T14" t="n">
-        <v>15750</v>
-      </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
         <v>2000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2211,22 +2227,22 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
+        <v>16</v>
+      </c>
+      <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="n">
-        <v>16</v>
-      </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2250,22 +2266,22 @@
         <v>7500</v>
       </c>
       <c r="S15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T15" t="n">
         <v>2000</v>
       </c>
-      <c r="T15" t="n">
-        <v>36000</v>
-      </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>2000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2296,19 +2312,19 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -2335,19 +2351,19 @@
         <v>15000</v>
       </c>
       <c r="S16" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T16" t="n">
         <v>5000</v>
       </c>
-      <c r="T16" t="n">
-        <v>6750</v>
-      </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>2000</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>2000</v>
@@ -2381,31 +2397,31 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>30</v>
-      </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2420,31 +2436,31 @@
         <v>15000</v>
       </c>
       <c r="S17" t="n">
+        <v>67500</v>
+      </c>
+      <c r="T17" t="n">
         <v>2000</v>
       </c>
-      <c r="T17" t="n">
-        <v>67500</v>
-      </c>
       <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="X17" t="n">
         <v>2000</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>1800</v>
       </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>20000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2466,22 +2482,22 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2505,22 +2521,22 @@
         <v>7500</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>6750</v>
       </c>
       <c r="T18" t="n">
-        <v>6750</v>
+        <v>1000</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
         <v>2000</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2636,31 +2652,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
         <v>5</v>
       </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2675,31 +2691,31 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>13500</v>
+      </c>
+      <c r="T20" t="n">
         <v>5000</v>
       </c>
-      <c r="T20" t="n">
-        <v>13500</v>
-      </c>
       <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>3000</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA20" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2730,22 +2746,22 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1155000</v>
@@ -2760,31 +2776,31 @@
         <v>5000</v>
       </c>
       <c r="S21" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T21" t="n">
         <v>3000</v>
       </c>
-      <c r="T21" t="n">
-        <v>6750</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1800</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA21" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2806,25 +2822,25 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
         <v>13</v>
       </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2845,25 +2861,25 @@
         <v>2500</v>
       </c>
       <c r="S22" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T22" t="n">
         <v>13000</v>
       </c>
-      <c r="T22" t="n">
-        <v>9000</v>
-      </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1800</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2891,25 +2907,25 @@
         <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
         <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2930,25 +2946,25 @@
         <v>7500</v>
       </c>
       <c r="S23" t="n">
+        <v>15750</v>
+      </c>
+      <c r="T23" t="n">
         <v>5000</v>
       </c>
-      <c r="T23" t="n">
-        <v>15750</v>
-      </c>
       <c r="U23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
         <v>900</v>
-      </c>
-      <c r="W23" t="n">
-        <v>900</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -2976,17 +2992,17 @@
         <v>6</v>
       </c>
       <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
@@ -2994,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3015,16 +3031,16 @@
         <v>15000</v>
       </c>
       <c r="S24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="T24" t="n">
         <v>5000</v>
       </c>
-      <c r="T24" t="n">
-        <v>4500</v>
-      </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -3033,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3061,25 +3077,25 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
         <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3100,25 +3116,25 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T25" t="n">
         <v>6000</v>
       </c>
-      <c r="T25" t="n">
-        <v>6750</v>
-      </c>
       <c r="U25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>3000</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>900</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3146,10 +3162,10 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3185,10 +3201,10 @@
         <v>2500</v>
       </c>
       <c r="S26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3231,25 +3247,25 @@
         <v>73</v>
       </c>
       <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
         <v>74</v>
       </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="L27" t="n">
         <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3270,25 +3286,25 @@
         <v>182500</v>
       </c>
       <c r="S27" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T27" t="n">
         <v>74000</v>
       </c>
-      <c r="T27" t="n">
-        <v>9000</v>
-      </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
         <v>2000</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>900</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3316,25 +3332,25 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
         <v>7</v>
       </c>
-      <c r="G28" t="n">
-        <v>4</v>
-      </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3355,25 +3371,25 @@
         <v>20000</v>
       </c>
       <c r="S28" t="n">
+        <v>9000</v>
+      </c>
+      <c r="T28" t="n">
         <v>7000</v>
       </c>
-      <c r="T28" t="n">
-        <v>9000</v>
-      </c>
       <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>2000</v>
       </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3401,22 +3417,22 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
         <v>6</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3440,13 +3456,13 @@
         <v>7500</v>
       </c>
       <c r="S29" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T29" t="n">
         <v>6000</v>
       </c>
-      <c r="T29" t="n">
-        <v>2250</v>
-      </c>
       <c r="U29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3455,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -3464,6 +3480,91 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>56</v>
+      </c>
+      <c r="C30" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>924000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>114000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7500</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6750</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3559,19 +3660,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F2" t="n">
         <v>1511</v>
       </c>
-      <c r="F2" t="n">
-        <v>1514</v>
-      </c>
       <c r="G2" t="n">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>45000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="3">
@@ -3594,10 +3695,10 @@
         <v>15000</v>
       </c>
       <c r="E3" t="n">
+        <v>820</v>
+      </c>
+      <c r="F3" t="n">
         <v>821</v>
-      </c>
-      <c r="F3" t="n">
-        <v>822</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
@@ -3691,10 +3792,10 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>281</v>
+      </c>
+      <c r="F6" t="n">
         <v>284</v>
-      </c>
-      <c r="F6" t="n">
-        <v>287</v>
       </c>
       <c r="G6" t="n">
         <v>-3</v>
@@ -3726,19 +3827,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>143</v>
+      </c>
+      <c r="F7" t="n">
         <v>146</v>
       </c>
-      <c r="F7" t="n">
-        <v>147</v>
-      </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>2250</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="8">
@@ -4286,10 +4387,10 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>798</v>
+      </c>
+      <c r="F23" t="n">
         <v>802</v>
-      </c>
-      <c r="F23" t="n">
-        <v>806</v>
       </c>
       <c r="G23" t="n">
         <v>-4</v>
@@ -4321,19 +4422,19 @@
         <v>1000</v>
       </c>
       <c r="E24" t="n">
+        <v>229</v>
+      </c>
+      <c r="F24" t="n">
         <v>230</v>
       </c>
-      <c r="F24" t="n">
-        <v>232</v>
-      </c>
       <c r="G24" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -4359,16 +4460,16 @@
         <v>158</v>
       </c>
       <c r="F25" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4391,19 +4492,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>108</v>
+      </c>
+      <c r="F26" t="n">
         <v>114</v>
       </c>
-      <c r="F26" t="n">
-        <v>115</v>
-      </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>19000</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="27">
@@ -4426,19 +4527,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F27" t="n">
         <v>294</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="28">
@@ -4461,19 +4562,19 @@
         <v>16500</v>
       </c>
       <c r="E28" t="n">
+        <v>307</v>
+      </c>
+      <c r="F28" t="n">
         <v>308</v>
       </c>
-      <c r="F28" t="n">
-        <v>310</v>
-      </c>
       <c r="G28" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>33000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="29">
@@ -4496,19 +4597,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>108</v>
+      </c>
+      <c r="F29" t="n">
         <v>114</v>
       </c>
-      <c r="F29" t="n">
-        <v>115</v>
-      </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>16500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="30">
@@ -4531,19 +4632,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>181</v>
+      </c>
+      <c r="F30" t="n">
         <v>188</v>
       </c>
-      <c r="F30" t="n">
-        <v>189</v>
-      </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>16500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="31">
@@ -4566,19 +4667,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>181</v>
+      </c>
+      <c r="F31" t="n">
         <v>188</v>
       </c>
-      <c r="F31" t="n">
-        <v>189</v>
-      </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>16500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="32">
@@ -4601,19 +4702,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F32" t="n">
         <v>294</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="33">
@@ -4636,10 +4737,10 @@
         <v>16500</v>
       </c>
       <c r="E33" t="n">
+        <v>307</v>
+      </c>
+      <c r="F33" t="n">
         <v>308</v>
-      </c>
-      <c r="F33" t="n">
-        <v>309</v>
       </c>
       <c r="G33" t="n">
         <v>-1</v>
@@ -4671,19 +4772,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>108</v>
+      </c>
+      <c r="F34" t="n">
         <v>114</v>
       </c>
-      <c r="F34" t="n">
-        <v>115</v>
-      </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>16500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="35">
@@ -4706,19 +4807,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>181</v>
+      </c>
+      <c r="F35" t="n">
         <v>188</v>
       </c>
-      <c r="F35" t="n">
-        <v>189</v>
-      </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>16500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="36">
@@ -4741,19 +4842,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>181</v>
+      </c>
+      <c r="F36" t="n">
         <v>188</v>
       </c>
-      <c r="F36" t="n">
-        <v>189</v>
-      </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>16500</v>
+        <v>115500</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I954"/>
+  <dimension ref="A1:I989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -39741,6 +39842,1293 @@
         <v>16500</v>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E955" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F955" t="n">
+        <v>1499</v>
+      </c>
+      <c r="G955" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H955" t="n">
+        <v>12</v>
+      </c>
+      <c r="I955" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E956" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F956" t="n">
+        <v>820</v>
+      </c>
+      <c r="G956" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H956" t="n">
+        <v>1</v>
+      </c>
+      <c r="I956" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr"/>
+      <c r="E957" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>0</v>
+      </c>
+      <c r="H957" t="n">
+        <v>0</v>
+      </c>
+      <c r="I957" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr"/>
+      <c r="E958" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>0</v>
+      </c>
+      <c r="H958" t="n">
+        <v>0</v>
+      </c>
+      <c r="I958" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E959" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F959" t="n">
+        <v>281</v>
+      </c>
+      <c r="G959" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H959" t="n">
+        <v>3</v>
+      </c>
+      <c r="I959" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E960" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F960" t="n">
+        <v>143</v>
+      </c>
+      <c r="G960" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H960" t="n">
+        <v>3</v>
+      </c>
+      <c r="I960" t="n">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E961" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F961" t="n">
+        <v>822</v>
+      </c>
+      <c r="G961" t="n">
+        <v>0</v>
+      </c>
+      <c r="H961" t="n">
+        <v>0</v>
+      </c>
+      <c r="I961" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E962" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F962" t="n">
+        <v>966</v>
+      </c>
+      <c r="G962" t="n">
+        <v>0</v>
+      </c>
+      <c r="H962" t="n">
+        <v>0</v>
+      </c>
+      <c r="I962" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E963" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F963" t="n">
+        <v>940</v>
+      </c>
+      <c r="G963" t="n">
+        <v>0</v>
+      </c>
+      <c r="H963" t="n">
+        <v>0</v>
+      </c>
+      <c r="I963" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V1</t>
+        </is>
+      </c>
+      <c r="E964" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F964" t="n">
+        <v>356</v>
+      </c>
+      <c r="G964" t="n">
+        <v>0</v>
+      </c>
+      <c r="H964" t="n">
+        <v>0</v>
+      </c>
+      <c r="I964" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V2</t>
+        </is>
+      </c>
+      <c r="E965" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F965" t="n">
+        <v>478</v>
+      </c>
+      <c r="G965" t="n">
+        <v>0</v>
+      </c>
+      <c r="H965" t="n">
+        <v>0</v>
+      </c>
+      <c r="I965" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange)</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-ORG-V3</t>
+        </is>
+      </c>
+      <c r="E966" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F966" t="n">
+        <v>484</v>
+      </c>
+      <c r="G966" t="n">
+        <v>0</v>
+      </c>
+      <c r="H966" t="n">
+        <v>0</v>
+      </c>
+      <c r="I966" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E967" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F967" t="n">
+        <v>338</v>
+      </c>
+      <c r="G967" t="n">
+        <v>0</v>
+      </c>
+      <c r="H967" t="n">
+        <v>0</v>
+      </c>
+      <c r="I967" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E968" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F968" t="n">
+        <v>481</v>
+      </c>
+      <c r="G968" t="n">
+        <v>0</v>
+      </c>
+      <c r="H968" t="n">
+        <v>0</v>
+      </c>
+      <c r="I968" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E969" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F969" t="n">
+        <v>483</v>
+      </c>
+      <c r="G969" t="n">
+        <v>0</v>
+      </c>
+      <c r="H969" t="n">
+        <v>0</v>
+      </c>
+      <c r="I969" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V1</t>
+        </is>
+      </c>
+      <c r="E970" t="n">
+        <v>900</v>
+      </c>
+      <c r="F970" t="n">
+        <v>370</v>
+      </c>
+      <c r="G970" t="n">
+        <v>0</v>
+      </c>
+      <c r="H970" t="n">
+        <v>0</v>
+      </c>
+      <c r="I970" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V2</t>
+        </is>
+      </c>
+      <c r="E971" t="n">
+        <v>900</v>
+      </c>
+      <c r="F971" t="n">
+        <v>493</v>
+      </c>
+      <c r="G971" t="n">
+        <v>0</v>
+      </c>
+      <c r="H971" t="n">
+        <v>0</v>
+      </c>
+      <c r="I971" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V3</t>
+        </is>
+      </c>
+      <c r="E972" t="n">
+        <v>900</v>
+      </c>
+      <c r="F972" t="n">
+        <v>476</v>
+      </c>
+      <c r="G972" t="n">
+        <v>0</v>
+      </c>
+      <c r="H972" t="n">
+        <v>0</v>
+      </c>
+      <c r="I972" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V1</t>
+        </is>
+      </c>
+      <c r="E973" t="n">
+        <v>900</v>
+      </c>
+      <c r="F973" t="n">
+        <v>686</v>
+      </c>
+      <c r="G973" t="n">
+        <v>0</v>
+      </c>
+      <c r="H973" t="n">
+        <v>0</v>
+      </c>
+      <c r="I973" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V2</t>
+        </is>
+      </c>
+      <c r="E974" t="n">
+        <v>900</v>
+      </c>
+      <c r="F974" t="n">
+        <v>941</v>
+      </c>
+      <c r="G974" t="n">
+        <v>0</v>
+      </c>
+      <c r="H974" t="n">
+        <v>0</v>
+      </c>
+      <c r="I974" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White)</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-WHT-V3</t>
+        </is>
+      </c>
+      <c r="E975" t="n">
+        <v>900</v>
+      </c>
+      <c r="F975" t="n">
+        <v>953</v>
+      </c>
+      <c r="G975" t="n">
+        <v>0</v>
+      </c>
+      <c r="H975" t="n">
+        <v>0</v>
+      </c>
+      <c r="I975" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLK-05</t>
+        </is>
+      </c>
+      <c r="E976" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F976" t="n">
+        <v>798</v>
+      </c>
+      <c r="G976" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H976" t="n">
+        <v>4</v>
+      </c>
+      <c r="I976" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>INQ-RFL-BLU-05</t>
+        </is>
+      </c>
+      <c r="E977" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F977" t="n">
+        <v>229</v>
+      </c>
+      <c r="G977" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H977" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>INQ-RFL-PCL-01</t>
+        </is>
+      </c>
+      <c r="E978" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F978" t="n">
+        <v>158</v>
+      </c>
+      <c r="G978" t="n">
+        <v>0</v>
+      </c>
+      <c r="H978" t="n">
+        <v>0</v>
+      </c>
+      <c r="I978" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>inq Student Kit</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>BINQ-STUDENTKIT-LTR-MX1</t>
+        </is>
+      </c>
+      <c r="E979" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F979" t="n">
+        <v>108</v>
+      </c>
+      <c r="G979" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H979" t="n">
+        <v>6</v>
+      </c>
+      <c r="I979" t="n">
+        <v>114000</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E980" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F980" t="n">
+        <v>287</v>
+      </c>
+      <c r="G980" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H980" t="n">
+        <v>7</v>
+      </c>
+      <c r="I980" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Black Velvet / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>BINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E981" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F981" t="n">
+        <v>307</v>
+      </c>
+      <c r="G981" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H981" t="n">
+        <v>1</v>
+      </c>
+      <c r="I981" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E982" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F982" t="n">
+        <v>108</v>
+      </c>
+      <c r="G982" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H982" t="n">
+        <v>6</v>
+      </c>
+      <c r="I982" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E983" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F983" t="n">
+        <v>181</v>
+      </c>
+      <c r="G983" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H983" t="n">
+        <v>7</v>
+      </c>
+      <c r="I983" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Black Velvet / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>BINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E984" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F984" t="n">
+        <v>181</v>
+      </c>
+      <c r="G984" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H984" t="n">
+        <v>7</v>
+      </c>
+      <c r="I984" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / Black</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-BLK</t>
+        </is>
+      </c>
+      <c r="E985" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F985" t="n">
+        <v>287</v>
+      </c>
+      <c r="G985" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H985" t="n">
+        <v>7</v>
+      </c>
+      <c r="I985" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Moon White / A5 - 5.8" x 8.3" / White</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>WINQ-A5W-WHT</t>
+        </is>
+      </c>
+      <c r="E986" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F986" t="n">
+        <v>307</v>
+      </c>
+      <c r="G986" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H986" t="n">
+        <v>1</v>
+      </c>
+      <c r="I986" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Black</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-BLK</t>
+        </is>
+      </c>
+      <c r="E987" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F987" t="n">
+        <v>108</v>
+      </c>
+      <c r="G987" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H987" t="n">
+        <v>6</v>
+      </c>
+      <c r="I987" t="n">
+        <v>99000</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / Orange</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-ORG</t>
+        </is>
+      </c>
+      <c r="E988" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F988" t="n">
+        <v>181</v>
+      </c>
+      <c r="G988" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H988" t="n">
+        <v>7</v>
+      </c>
+      <c r="I988" t="n">
+        <v>115500</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>inq writing set</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Moon White / Letter - 8.5" x 11" / White</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>WINQ-LTR-WHT</t>
+        </is>
+      </c>
+      <c r="E989" t="n">
+        <v>16500</v>
+      </c>
+      <c r="F989" t="n">
+        <v>181</v>
+      </c>
+      <c r="G989" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H989" t="n">
+        <v>7</v>
+      </c>
+      <c r="I989" t="n">
+        <v>115500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_inventory.xlsx
+++ b/data/anoto_inventory.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -921,6 +921,22 @@
       </c>
       <c r="D30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>46</v>
+      </c>
+      <c r="C31" t="n">
+        <v>618250</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -934,34 +950,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="55" customWidth="1" min="19" max="19"/>
-    <col width="45" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="20" max="20"/>
     <col width="55" customWidth="1" min="21" max="21"/>
     <col width="55" customWidth="1" min="22" max="22"/>
     <col width="55" customWidth="1" min="23" max="23"/>
-    <col width="48" customWidth="1" min="24" max="24"/>
-    <col width="55" customWidth="1" min="25" max="25"/>
+    <col width="55" customWidth="1" min="24" max="24"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
     <col width="55" customWidth="1" min="26" max="26"/>
     <col width="55" customWidth="1" min="27" max="27"/>
   </cols>
@@ -979,59 +995,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Units)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Units)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Units)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Units)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Units)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Units)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Units)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Units)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Units)</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages (Units)</t>
@@ -1044,57 +1060,57 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>inq Student Kit (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Extra inq pen (Rev USD)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>inq Student Kit (Rev USD)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>inq PEN Kit - 5-pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Black) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>inq PENCIL Kit - 5-Pack D1 Refills (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook A5 5.8" x 8.3" 156 Pages (White) (Rev USD)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Spiral Notebook 8.5" x 11" College Ruled 190 Pages (Orange) (Rev USD)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -1198,7 +1214,7 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -1222,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1237,10 +1253,10 @@
         <v>231000</v>
       </c>
       <c r="P3" t="n">
-        <v>45000</v>
+        <v>19000</v>
       </c>
       <c r="Q3" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="R3" t="n">
         <v>2500</v>
@@ -1261,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1283,7 +1299,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -1295,22 +1311,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
         <v>3</v>
@@ -1322,10 +1338,10 @@
         <v>198000</v>
       </c>
       <c r="P4" t="n">
-        <v>45000</v>
+        <v>76000</v>
       </c>
       <c r="Q4" t="n">
-        <v>76000</v>
+        <v>4000</v>
       </c>
       <c r="R4" t="n">
         <v>2500</v>
@@ -1334,25 +1350,25 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="U4" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="W4" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>3000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1368,7 +1384,7 @@
         <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1380,25 +1396,25 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1407,10 +1423,10 @@
         <v>528000</v>
       </c>
       <c r="P5" t="n">
-        <v>90000</v>
+        <v>19000</v>
       </c>
       <c r="Q5" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="R5" t="n">
         <v>2500</v>
@@ -1419,25 +1435,25 @@
         <v>2250</v>
       </c>
       <c r="T5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1453,7 +1469,7 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -1465,25 +1481,25 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1492,10 +1508,10 @@
         <v>396000</v>
       </c>
       <c r="P6" t="n">
-        <v>120000</v>
+        <v>19000</v>
       </c>
       <c r="Q6" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="R6" t="n">
         <v>5000</v>
@@ -1504,25 +1520,25 @@
         <v>13500</v>
       </c>
       <c r="T6" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Z6" t="n">
         <v>900</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2700</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1538,7 +1554,7 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -1550,25 +1566,25 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1577,10 +1593,10 @@
         <v>1782000</v>
       </c>
       <c r="P7" t="n">
-        <v>465000</v>
+        <v>152000</v>
       </c>
       <c r="Q7" t="n">
-        <v>152000</v>
+        <v>8000</v>
       </c>
       <c r="R7" t="n">
         <v>10000</v>
@@ -1589,25 +1605,25 @@
         <v>4500</v>
       </c>
       <c r="T7" t="n">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="V7" t="n">
-        <v>44000</v>
+        <v>2000</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2700</v>
+        <v>465000</v>
       </c>
       <c r="Z7" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1623,7 +1639,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -1635,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1647,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1662,10 +1678,10 @@
         <v>594000</v>
       </c>
       <c r="P8" t="n">
-        <v>210000</v>
+        <v>95000</v>
       </c>
       <c r="Q8" t="n">
-        <v>95000</v>
+        <v>5000</v>
       </c>
       <c r="R8" t="n">
         <v>5000</v>
@@ -1674,7 +1690,7 @@
         <v>2250</v>
       </c>
       <c r="T8" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1686,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1708,7 +1724,7 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -1720,25 +1736,25 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1747,10 +1763,10 @@
         <v>792000</v>
       </c>
       <c r="P9" t="n">
-        <v>195000</v>
+        <v>114000</v>
       </c>
       <c r="Q9" t="n">
-        <v>114000</v>
+        <v>6000</v>
       </c>
       <c r="R9" t="n">
         <v>20000</v>
@@ -1759,25 +1775,25 @@
         <v>15750</v>
       </c>
       <c r="T9" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V9" t="n">
         <v>1000</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X9" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>900</v>
+        <v>195000</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1793,7 +1809,7 @@
         <v>143</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1805,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1814,13 +1830,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1832,7 +1848,7 @@
         <v>2359500</v>
       </c>
       <c r="P10" t="n">
-        <v>825000</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1844,7 +1860,7 @@
         <v>4500</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1853,13 +1869,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>3600</v>
+        <v>825000</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1878,7 +1894,7 @@
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1890,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1902,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1917,7 +1933,7 @@
         <v>247500</v>
       </c>
       <c r="P11" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1929,7 +1945,7 @@
         <v>2250</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1941,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -1963,7 +1979,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -1975,22 +1991,22 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -2002,10 +2018,10 @@
         <v>297000</v>
       </c>
       <c r="P12" t="n">
-        <v>75000</v>
+        <v>57000</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3000</v>
       </c>
       <c r="R12" t="n">
         <v>2500</v>
@@ -2014,25 +2030,25 @@
         <v>2250</v>
       </c>
       <c r="T12" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W12" t="n">
         <v>900</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="Z12" t="n">
         <v>900</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2048,7 +2064,7 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
@@ -2060,25 +2076,25 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2087,10 +2103,10 @@
         <v>528000</v>
       </c>
       <c r="P13" t="n">
-        <v>90000</v>
+        <v>228000</v>
       </c>
       <c r="Q13" t="n">
-        <v>228000</v>
+        <v>12000</v>
       </c>
       <c r="R13" t="n">
         <v>10000</v>
@@ -2099,25 +2115,25 @@
         <v>4500</v>
       </c>
       <c r="T13" t="n">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>900</v>
+        <v>90000</v>
       </c>
       <c r="Z13" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2133,7 +2149,7 @@
         <v>100</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
@@ -2145,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2157,10 +2173,10 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2172,10 +2188,10 @@
         <v>1650000</v>
       </c>
       <c r="P14" t="n">
-        <v>285000</v>
+        <v>190000</v>
       </c>
       <c r="Q14" t="n">
-        <v>190000</v>
+        <v>10000</v>
       </c>
       <c r="R14" t="n">
         <v>10000</v>
@@ -2184,7 +2200,7 @@
         <v>15750</v>
       </c>
       <c r="T14" t="n">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2196,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2218,7 +2234,7 @@
         <v>46</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -2242,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2257,10 +2273,10 @@
         <v>759000</v>
       </c>
       <c r="P15" t="n">
-        <v>150000</v>
+        <v>38000</v>
       </c>
       <c r="Q15" t="n">
-        <v>38000</v>
+        <v>2000</v>
       </c>
       <c r="R15" t="n">
         <v>7500</v>
@@ -2281,10 +2297,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2303,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -2315,7 +2331,7 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2324,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2342,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>195000</v>
+        <v>95000</v>
       </c>
       <c r="Q16" t="n">
-        <v>95000</v>
+        <v>5000</v>
       </c>
       <c r="R16" t="n">
         <v>15000</v>
@@ -2354,7 +2370,7 @@
         <v>6750</v>
       </c>
       <c r="T16" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2363,13 +2379,13 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>2000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2388,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -2403,22 +2419,22 @@
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
         <v>20</v>
       </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2427,10 +2443,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>915000</v>
+        <v>38000</v>
       </c>
       <c r="Q17" t="n">
-        <v>38000</v>
+        <v>2000</v>
       </c>
       <c r="R17" t="n">
         <v>15000</v>
@@ -2442,22 +2458,22 @@
         <v>2000</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V17" t="n">
         <v>1000</v>
       </c>
       <c r="W17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="X17" t="n">
         <v>20000</v>
       </c>
-      <c r="X17" t="n">
-        <v>2000</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1800</v>
+        <v>915000</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2473,7 +2489,7 @@
         <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -2485,7 +2501,7 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2497,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2512,10 +2528,10 @@
         <v>462000</v>
       </c>
       <c r="P18" t="n">
-        <v>90000</v>
+        <v>19000</v>
       </c>
       <c r="Q18" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="R18" t="n">
         <v>7500</v>
@@ -2524,7 +2540,7 @@
         <v>6750</v>
       </c>
       <c r="T18" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2536,10 +2552,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -2558,35 +2574,35 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2597,34 +2613,34 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>90000</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2643,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>5</v>
@@ -2655,25 +2671,25 @@
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2682,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>135000</v>
+        <v>95000</v>
       </c>
       <c r="Q20" t="n">
-        <v>95000</v>
+        <v>5000</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2694,25 +2710,25 @@
         <v>13500</v>
       </c>
       <c r="T20" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="Z20" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2728,10 +2744,10 @@
         <v>70</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -2740,25 +2756,25 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2767,10 +2783,10 @@
         <v>1155000</v>
       </c>
       <c r="P21" t="n">
-        <v>330000</v>
+        <v>19000</v>
       </c>
       <c r="Q21" t="n">
-        <v>19000</v>
+        <v>3000</v>
       </c>
       <c r="R21" t="n">
         <v>5000</v>
@@ -2779,25 +2795,25 @@
         <v>6750</v>
       </c>
       <c r="T21" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V21" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1800</v>
+        <v>330000</v>
       </c>
       <c r="Z21" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2813,10 +2829,10 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -2825,7 +2841,7 @@
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2834,13 +2850,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2852,10 +2868,10 @@
         <v>363000</v>
       </c>
       <c r="P22" t="n">
-        <v>105000</v>
+        <v>114000</v>
       </c>
       <c r="Q22" t="n">
-        <v>114000</v>
+        <v>13000</v>
       </c>
       <c r="R22" t="n">
         <v>2500</v>
@@ -2864,7 +2880,7 @@
         <v>9000</v>
       </c>
       <c r="T22" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2873,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1800</v>
+        <v>105000</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2898,10 +2914,10 @@
         <v>90</v>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -2910,25 +2926,25 @@
         <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>34</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2937,10 +2953,10 @@
         <v>1485000</v>
       </c>
       <c r="P23" t="n">
-        <v>510000</v>
+        <v>38000</v>
       </c>
       <c r="Q23" t="n">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="R23" t="n">
         <v>7500</v>
@@ -2949,25 +2965,25 @@
         <v>15750</v>
       </c>
       <c r="T23" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
         <v>900</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
+        <v>510000</v>
+      </c>
+      <c r="Z23" t="n">
         <v>900</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2983,10 +2999,10 @@
         <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
@@ -2995,13 +3011,13 @@
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3010,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3022,10 +3038,10 @@
         <v>891000</v>
       </c>
       <c r="P24" t="n">
-        <v>165000</v>
+        <v>38000</v>
       </c>
       <c r="Q24" t="n">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="R24" t="n">
         <v>15000</v>
@@ -3034,13 +3050,13 @@
         <v>4500</v>
       </c>
       <c r="T24" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V24" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -3049,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>165000</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3068,10 +3084,10 @@
         <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -3080,25 +3096,25 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
         <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3107,10 +3123,10 @@
         <v>132000</v>
       </c>
       <c r="P25" t="n">
-        <v>45000</v>
+        <v>38000</v>
       </c>
       <c r="Q25" t="n">
-        <v>38000</v>
+        <v>6000</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3119,25 +3135,25 @@
         <v>6750</v>
       </c>
       <c r="T25" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>900</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1800</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>900</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3153,7 +3169,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -3165,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3180,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3192,10 +3208,10 @@
         <v>264000</v>
       </c>
       <c r="P26" t="n">
-        <v>30000</v>
+        <v>19000</v>
       </c>
       <c r="Q26" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="R26" t="n">
         <v>2500</v>
@@ -3204,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3219,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3238,10 +3254,10 @@
         <v>2084</v>
       </c>
       <c r="C27" t="n">
-        <v>649</v>
+        <v>91</v>
       </c>
       <c r="D27" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
         <v>73</v>
@@ -3250,7 +3266,7 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3259,13 +3275,13 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3277,10 +3293,10 @@
         <v>34386000</v>
       </c>
       <c r="P27" t="n">
-        <v>9735000</v>
+        <v>1729000</v>
       </c>
       <c r="Q27" t="n">
-        <v>1729000</v>
+        <v>74000</v>
       </c>
       <c r="R27" t="n">
         <v>182500</v>
@@ -3289,7 +3305,7 @@
         <v>9000</v>
       </c>
       <c r="T27" t="n">
-        <v>74000</v>
+        <v>2000</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3298,13 +3314,13 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X27" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>900</v>
+        <v>9735000</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -3323,10 +3339,10 @@
         <v>209</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
@@ -3335,22 +3351,22 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3362,10 +3378,10 @@
         <v>3448500</v>
       </c>
       <c r="P28" t="n">
-        <v>555000</v>
+        <v>646000</v>
       </c>
       <c r="Q28" t="n">
-        <v>646000</v>
+        <v>7000</v>
       </c>
       <c r="R28" t="n">
         <v>20000</v>
@@ -3374,22 +3390,22 @@
         <v>9000</v>
       </c>
       <c r="T28" t="n">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V28" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>555000</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -3408,10 +3424,10 @@
         <v>9</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -3420,7 +3436,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3432,10 +3448,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3447,10 +3463,10 @@
         <v>148500</v>
       </c>
       <c r="P29" t="n">
-        <v>60000</v>
+        <v>19000</v>
       </c>
       <c r="Q29" t="n">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="R29" t="n">
         <v>7500</v>
@@ -3459,7 +3475,7 @@
         <v>2250</v>
       </c>
       <c r="T29" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3471,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3493,10 +3509,10 @@
         <v>56</v>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -3505,7 +3521,7 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3520,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3532,10 +3548,10 @@
         <v>924000</v>
       </c>
       <c r="P30" t="n">
-        <v>195000</v>
+        <v>114000</v>
       </c>
       <c r="Q30" t="n">
-        <v>114000</v>
+        <v>5000</v>
       </c>
       <c r="R30" t="n">
         <v>7500</v>
@@ -3544,27 +3560,112 @@
         <v>6750</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>195000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>32</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>528000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>76000</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6000</v>
+      </c>
+      <c r="R31" t="n">
         <v>5000</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="S31" t="n">
+        <v>2250</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3660,19 +3761,19 @@
         <v>15000</v>
       </c>
       <c r="E2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="F2" t="n">
         <v>1499</v>
       </c>
-      <c r="F2" t="n">
-        <v>1511</v>
-      </c>
       <c r="G2" t="n">
-        <v>-12</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3698,16 +3799,16 @@
         <v>820</v>
       </c>
       <c r="F3" t="n">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3792,19 +3893,19 @@
         <v>2500</v>
       </c>
       <c r="E6" t="n">
+        <v>279</v>
+      </c>
+      <c r="F6" t="n">
         <v>281</v>
       </c>
-      <c r="F6" t="n">
-        <v>284</v>
-      </c>
       <c r="G6" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="7">
@@ -3827,19 +3928,19 @@
         <v>2250</v>
       </c>
       <c r="E7" t="n">
+        <v>142</v>
+      </c>
+      <c r="F7" t="n">
         <v>143</v>
       </c>
-      <c r="F7" t="n">
-        <v>146</v>
-      </c>
       <c r="G7" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="8">
@@ -4387,19 +4488,19 @@
         <v>1000</v>
       </c>
       <c r="E23" t="n">
+        <v>792</v>
+      </c>
+      <c r="F23" t="n">
         <v>798</v>
       </c>
-      <c r="F23" t="n">
-        <v>802</v>
-      </c>
       <c r="G23" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="24">
@@ -4425,16 +4526,16 @@
         <v>229</v>
       </c>
       <c r="F24" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4457,19 +4558,19 @@
         <v>1000</v>
       </c>
       <c r="E25" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F25" t="n">
         <v>158</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="26">
@@ -4492,19 +4593,19 @@
         <v>19000</v>
       </c>
       <c r="E26" t="n">
+        <v>104</v>
+      </c>
+      <c r="F26" t="n">
         <v>108</v>
       </c>
-      <c r="F26" t="n">
-        <v>114</v>
-      </c>
       <c r="G26" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>114000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="27">
@@ -4527,19 +4628,19 @@
         <v>16500</v>
       </c>
       <c r="E27" t="n">
+        <v>320</v>
+      </c>
+      <c r="F27" t="n">
         <v>287</v>
       </c>
-      <c r="F27" t="n">
-        <v>294</v>
-      </c>
       <c r="G27" t="n">
-        <v>-7</v>
+        <v>33</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>115500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4565,16 +4666,16 @@
         <v>307</v>
       </c>
       <c r="F28" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4597,19 +4698,19 @@
         <v>16500</v>
       </c>
       <c r="E29" t="n">
+        <v>104</v>
+      </c>
+      <c r="F29" t="n">
         <v>108</v>
       </c>
-      <c r="F29" t="n">
-        <v>114</v>
-      </c>
       <c r="G29" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="30">
@@ -4632,19 +4733,19 @@
         <v>16500</v>
       </c>
       <c r="E30" t="n">
+        <v>175</v>
+      </c>
+      <c r="F30" t="n">
         <v>181</v>
       </c>
-      <c r="F30" t="n">
-        <v>188</v>
-      </c>
       <c r="G30" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>115500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="31">
@@ -4667,19 +4768,19 @@
         <v>16500</v>
       </c>
       <c r="E31" t="n">
+        <v>175</v>
+      </c>
+      <c r="F31" t="n">
         <v>181</v>
       </c>
-      <c r="F31" t="n">
-        <v>188</v>
-      </c>
       <c r="G31" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>115500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="32">
@@ -4702,19 +4803,19 @@
         <v>16500</v>
       </c>
       <c r="E32" t="n">
+        <v>320</v>
+      </c>
+      <c r="F32" t="n">
         <v>287</v>
       </c>
-      <c r="F32" t="n">
-        <v>294</v>
-      </c>
       <c r="G32" t="n">
-        <v>-7</v>
+        <v>33</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>115500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4740,16 +4841,16 @@
         <v>307</v>
       </c>
       <c r="F33" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>16500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4772,19 +4873,19 @@
         <v>16500</v>
       </c>
       <c r="E34" t="n">
+        <v>104</v>
+      </c>
+      <c r="F34" t="n">
         <v>108</v>
       </c>
-      <c r="F34" t="n">
-        <v>114</v>
-      </c>
       <c r="G34" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>99000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="35">
@@ -4807,19 +4908,19 @@
         <v>16500</v>
       </c>
       <c r="E35" t="n">
+        <v>175</v>
+      </c>
+      <c r="F35" t="n">
         <v>181</v>
       </c>
-      <c r="F35" t="n">
-        <v>188</v>
-      </c>
       <c r="G35" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>115500</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="36">
@@ -4842,19 +4943,19 @@
         <v>16500</v>
       </c>
       <c r="E36" t="n">
+        <v>175</v>
+      </c>
+      <c r="F36" t="n">
         <v>181</v>
       </c>
-      <c r="F36" t="n">
-        <v>188</v>
-      </c>
       <c r="G36" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>115500</v>
+        <v>99000</v>
       </c>
     </row>
   </sheetData>
@@ -4868,7 +4969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I989"/>
+  <dimension ref="A1:I1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -41129,6 +41230,1293 @@
         <v>115500</v>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Black Velvet</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>INQ-001-BLK</t>
+        </is>
+      </c>
+      <c r="E990" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F990" t="n">
+        <v>1526</v>
+      </c>
+      <c r="G990" t="n">
+        <v>27</v>
+      </c>
+      <c r="H990" t="n">
+        <v>0</v>
+      </c>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Extra inq pen</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Moon White</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>INQ-001-WHT</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F991" t="n">
+        <v>820</v>
+      </c>
+      <c r="G991" t="n">
+        <v>0</v>
+      </c>
+      <c r="H991" t="n">
+        <v>0</v>
+      </c>
+      <c r="I991" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Linen Black</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr"/>
+      <c r="E992" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F992" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" t="n">
+        <v>0</v>
+      </c>
+      <c r="H992" t="n">
+        <v>0</v>
+      </c>
+      <c r="I992" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Hardcover Notebook A5 5.8" x 8.3" 190 pages</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Linen Light Grey</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr"/>
+      <c r="E993" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F993" t="n">
+        <v>0</v>
+      </c>
+      <c r="G993" t="n">
+        <v>0</v>
+      </c>
+      <c r="H993" t="n">
+        <v>0</v>
+      </c>
+      <c r="I993" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack 8.5" x 11" College Ruled 190 Pages (Variety)</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>INQ-USL-SP01-MX1-V123</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F994" t="n">
+        <v>279</v>
+      </c>
+      <c r="G994" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H994" t="n">
+        <v>2</v>
+      </c>
+      <c r="I994" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Spiral Notebook 3-Pack A5 5.8" x 8.3" 156 Pages (Black)</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Default Title</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>INQ-A5-SP01-BLK-V123</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F995" t="n">
+        <v>142</v>
+      </c>
+      <c r="G995" t="n">
+        <v>-1</v>
+      </c>
+      